--- a/datos/hechos/td_admin.xlsx
+++ b/datos/hechos/td_admin.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F985"/>
+  <dimension ref="A1:F993"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -24076,6 +24076,198 @@
         </is>
       </c>
     </row>
+    <row r="986">
+      <c r="A986" t="inlineStr">
+        <is>
+          <t>62d5bd9ad8106d3355b5bdc1</t>
+        </is>
+      </c>
+      <c r="B986" t="n">
+        <v>8988626</v>
+      </c>
+      <c r="C986" t="n">
+        <v>1</v>
+      </c>
+      <c r="D986" t="n">
+        <v>2</v>
+      </c>
+      <c r="E986" t="n">
+        <v>1</v>
+      </c>
+      <c r="F986" t="inlineStr">
+        <is>
+          <t>2026-09-07</t>
+        </is>
+      </c>
+    </row>
+    <row r="987">
+      <c r="A987" t="inlineStr">
+        <is>
+          <t>5f45324dec331549297ee971</t>
+        </is>
+      </c>
+      <c r="B987" t="n">
+        <v>1881621</v>
+      </c>
+      <c r="C987" t="n">
+        <v>1</v>
+      </c>
+      <c r="D987" t="n">
+        <v>2</v>
+      </c>
+      <c r="E987" t="n">
+        <v>1</v>
+      </c>
+      <c r="F987" t="inlineStr">
+        <is>
+          <t>2026-09-07</t>
+        </is>
+      </c>
+    </row>
+    <row r="988">
+      <c r="A988" t="inlineStr">
+        <is>
+          <t>5f4531e9764e7d491e029746</t>
+        </is>
+      </c>
+      <c r="B988" t="n">
+        <v>1174503</v>
+      </c>
+      <c r="C988" t="n">
+        <v>0</v>
+      </c>
+      <c r="D988" t="n">
+        <v>0</v>
+      </c>
+      <c r="E988" t="n">
+        <v>0</v>
+      </c>
+      <c r="F988" t="inlineStr">
+        <is>
+          <t>2026-09-07</t>
+        </is>
+      </c>
+    </row>
+    <row r="989">
+      <c r="A989" t="inlineStr">
+        <is>
+          <t>5f452f5e66dd374930eb2b71</t>
+        </is>
+      </c>
+      <c r="B989" t="n">
+        <v>-3659619</v>
+      </c>
+      <c r="C989" t="n">
+        <v>3</v>
+      </c>
+      <c r="D989" t="n">
+        <v>4</v>
+      </c>
+      <c r="E989" t="n">
+        <v>4</v>
+      </c>
+      <c r="F989" t="inlineStr">
+        <is>
+          <t>2026-09-07</t>
+        </is>
+      </c>
+    </row>
+    <row r="990">
+      <c r="A990" t="inlineStr">
+        <is>
+          <t>5f47ab5b9e2edb0bb831c703</t>
+        </is>
+      </c>
+      <c r="B990" t="n">
+        <v>9810134</v>
+      </c>
+      <c r="C990" t="n">
+        <v>0</v>
+      </c>
+      <c r="D990" t="n">
+        <v>1</v>
+      </c>
+      <c r="E990" t="n">
+        <v>0</v>
+      </c>
+      <c r="F990" t="inlineStr">
+        <is>
+          <t>2026-09-07</t>
+        </is>
+      </c>
+    </row>
+    <row r="991">
+      <c r="A991" t="inlineStr">
+        <is>
+          <t>5f453062ec331549297ee6b8</t>
+        </is>
+      </c>
+      <c r="B991" t="n">
+        <v>10971</v>
+      </c>
+      <c r="C991" t="n">
+        <v>1</v>
+      </c>
+      <c r="D991" t="n">
+        <v>3</v>
+      </c>
+      <c r="E991" t="n">
+        <v>0</v>
+      </c>
+      <c r="F991" t="inlineStr">
+        <is>
+          <t>2026-09-07</t>
+        </is>
+      </c>
+    </row>
+    <row r="992">
+      <c r="A992" t="inlineStr">
+        <is>
+          <t>5f47aeb6c387a50bca03dd55</t>
+        </is>
+      </c>
+      <c r="B992" t="n">
+        <v>737534</v>
+      </c>
+      <c r="C992" t="n">
+        <v>0</v>
+      </c>
+      <c r="D992" t="n">
+        <v>2</v>
+      </c>
+      <c r="E992" t="n">
+        <v>0</v>
+      </c>
+      <c r="F992" t="inlineStr">
+        <is>
+          <t>2026-09-07</t>
+        </is>
+      </c>
+    </row>
+    <row r="993">
+      <c r="A993" t="inlineStr">
+        <is>
+          <t>5f4530beec331549297ee6d6</t>
+        </is>
+      </c>
+      <c r="B993" t="n">
+        <v>-774747</v>
+      </c>
+      <c r="C993" t="n">
+        <v>0</v>
+      </c>
+      <c r="D993" t="n">
+        <v>3</v>
+      </c>
+      <c r="E993" t="n">
+        <v>0</v>
+      </c>
+      <c r="F993" t="inlineStr">
+        <is>
+          <t>2026-09-07</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/datos/hechos/td_admin.xlsx
+++ b/datos/hechos/td_admin.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F993"/>
+  <dimension ref="A1:F1001"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -24268,6 +24268,198 @@
         </is>
       </c>
     </row>
+    <row r="994">
+      <c r="A994" t="inlineStr">
+        <is>
+          <t>5f45324dec331549297ee971</t>
+        </is>
+      </c>
+      <c r="B994" t="n">
+        <v>4586621</v>
+      </c>
+      <c r="C994" t="n">
+        <v>1</v>
+      </c>
+      <c r="D994" t="n">
+        <v>2</v>
+      </c>
+      <c r="E994" t="n">
+        <v>1</v>
+      </c>
+      <c r="F994" t="inlineStr">
+        <is>
+          <t>2026-09-08</t>
+        </is>
+      </c>
+    </row>
+    <row r="995">
+      <c r="A995" t="inlineStr">
+        <is>
+          <t>62d5bd9ad8106d3355b5bdc1</t>
+        </is>
+      </c>
+      <c r="B995" t="n">
+        <v>29328253</v>
+      </c>
+      <c r="C995" t="n">
+        <v>1</v>
+      </c>
+      <c r="D995" t="n">
+        <v>2</v>
+      </c>
+      <c r="E995" t="n">
+        <v>1</v>
+      </c>
+      <c r="F995" t="inlineStr">
+        <is>
+          <t>2026-09-08</t>
+        </is>
+      </c>
+    </row>
+    <row r="996">
+      <c r="A996" t="inlineStr">
+        <is>
+          <t>5f4531e9764e7d491e029746</t>
+        </is>
+      </c>
+      <c r="B996" t="n">
+        <v>3613503</v>
+      </c>
+      <c r="C996" t="n">
+        <v>0</v>
+      </c>
+      <c r="D996" t="n">
+        <v>0</v>
+      </c>
+      <c r="E996" t="n">
+        <v>0</v>
+      </c>
+      <c r="F996" t="inlineStr">
+        <is>
+          <t>2026-09-08</t>
+        </is>
+      </c>
+    </row>
+    <row r="997">
+      <c r="A997" t="inlineStr">
+        <is>
+          <t>5f453062ec331549297ee6b8</t>
+        </is>
+      </c>
+      <c r="B997" t="n">
+        <v>-18678086</v>
+      </c>
+      <c r="C997" t="n">
+        <v>1</v>
+      </c>
+      <c r="D997" t="n">
+        <v>3</v>
+      </c>
+      <c r="E997" t="n">
+        <v>0</v>
+      </c>
+      <c r="F997" t="inlineStr">
+        <is>
+          <t>2026-09-08</t>
+        </is>
+      </c>
+    </row>
+    <row r="998">
+      <c r="A998" t="inlineStr">
+        <is>
+          <t>5f47ab5b9e2edb0bb831c703</t>
+        </is>
+      </c>
+      <c r="B998" t="n">
+        <v>12431134</v>
+      </c>
+      <c r="C998" t="n">
+        <v>0</v>
+      </c>
+      <c r="D998" t="n">
+        <v>1</v>
+      </c>
+      <c r="E998" t="n">
+        <v>0</v>
+      </c>
+      <c r="F998" t="inlineStr">
+        <is>
+          <t>2026-09-08</t>
+        </is>
+      </c>
+    </row>
+    <row r="999">
+      <c r="A999" t="inlineStr">
+        <is>
+          <t>5f452f5e66dd374930eb2b71</t>
+        </is>
+      </c>
+      <c r="B999" t="n">
+        <v>-1320619</v>
+      </c>
+      <c r="C999" t="n">
+        <v>3</v>
+      </c>
+      <c r="D999" t="n">
+        <v>4</v>
+      </c>
+      <c r="E999" t="n">
+        <v>4</v>
+      </c>
+      <c r="F999" t="inlineStr">
+        <is>
+          <t>2026-09-08</t>
+        </is>
+      </c>
+    </row>
+    <row r="1000">
+      <c r="A1000" t="inlineStr">
+        <is>
+          <t>5f47aeb6c387a50bca03dd55</t>
+        </is>
+      </c>
+      <c r="B1000" t="n">
+        <v>4033534</v>
+      </c>
+      <c r="C1000" t="n">
+        <v>0</v>
+      </c>
+      <c r="D1000" t="n">
+        <v>2</v>
+      </c>
+      <c r="E1000" t="n">
+        <v>0</v>
+      </c>
+      <c r="F1000" t="inlineStr">
+        <is>
+          <t>2026-09-08</t>
+        </is>
+      </c>
+    </row>
+    <row r="1001">
+      <c r="A1001" t="inlineStr">
+        <is>
+          <t>5f4530beec331549297ee6d6</t>
+        </is>
+      </c>
+      <c r="B1001" t="n">
+        <v>4575240</v>
+      </c>
+      <c r="C1001" t="n">
+        <v>0</v>
+      </c>
+      <c r="D1001" t="n">
+        <v>3</v>
+      </c>
+      <c r="E1001" t="n">
+        <v>0</v>
+      </c>
+      <c r="F1001" t="inlineStr">
+        <is>
+          <t>2026-09-08</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/datos/hechos/td_admin.xlsx
+++ b/datos/hechos/td_admin.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F1001"/>
+  <dimension ref="A1:F1009"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -24460,6 +24460,198 @@
         </is>
       </c>
     </row>
+    <row r="1002">
+      <c r="A1002" t="inlineStr">
+        <is>
+          <t>5f45324dec331549297ee971</t>
+        </is>
+      </c>
+      <c r="B1002" t="n">
+        <v>3086621</v>
+      </c>
+      <c r="C1002" t="n">
+        <v>1</v>
+      </c>
+      <c r="D1002" t="n">
+        <v>2</v>
+      </c>
+      <c r="E1002" t="n">
+        <v>1</v>
+      </c>
+      <c r="F1002" t="inlineStr">
+        <is>
+          <t>2026-09-09</t>
+        </is>
+      </c>
+    </row>
+    <row r="1003">
+      <c r="A1003" t="inlineStr">
+        <is>
+          <t>62d5bd9ad8106d3355b5bdc1</t>
+        </is>
+      </c>
+      <c r="B1003" t="n">
+        <v>-971746</v>
+      </c>
+      <c r="C1003" t="n">
+        <v>1</v>
+      </c>
+      <c r="D1003" t="n">
+        <v>2</v>
+      </c>
+      <c r="E1003" t="n">
+        <v>1</v>
+      </c>
+      <c r="F1003" t="inlineStr">
+        <is>
+          <t>2026-09-09</t>
+        </is>
+      </c>
+    </row>
+    <row r="1004">
+      <c r="A1004" t="inlineStr">
+        <is>
+          <t>5f4531e9764e7d491e029746</t>
+        </is>
+      </c>
+      <c r="B1004" t="n">
+        <v>3613503</v>
+      </c>
+      <c r="C1004" t="n">
+        <v>0</v>
+      </c>
+      <c r="D1004" t="n">
+        <v>0</v>
+      </c>
+      <c r="E1004" t="n">
+        <v>0</v>
+      </c>
+      <c r="F1004" t="inlineStr">
+        <is>
+          <t>2026-09-09</t>
+        </is>
+      </c>
+    </row>
+    <row r="1005">
+      <c r="A1005" t="inlineStr">
+        <is>
+          <t>5f453062ec331549297ee6b8</t>
+        </is>
+      </c>
+      <c r="B1005" t="n">
+        <v>735962</v>
+      </c>
+      <c r="C1005" t="n">
+        <v>1</v>
+      </c>
+      <c r="D1005" t="n">
+        <v>3</v>
+      </c>
+      <c r="E1005" t="n">
+        <v>0</v>
+      </c>
+      <c r="F1005" t="inlineStr">
+        <is>
+          <t>2026-09-09</t>
+        </is>
+      </c>
+    </row>
+    <row r="1006">
+      <c r="A1006" t="inlineStr">
+        <is>
+          <t>5f47ab5b9e2edb0bb831c703</t>
+        </is>
+      </c>
+      <c r="B1006" t="n">
+        <v>9413033</v>
+      </c>
+      <c r="C1006" t="n">
+        <v>0</v>
+      </c>
+      <c r="D1006" t="n">
+        <v>1</v>
+      </c>
+      <c r="E1006" t="n">
+        <v>0</v>
+      </c>
+      <c r="F1006" t="inlineStr">
+        <is>
+          <t>2026-09-09</t>
+        </is>
+      </c>
+    </row>
+    <row r="1007">
+      <c r="A1007" t="inlineStr">
+        <is>
+          <t>5f452f5e66dd374930eb2b71</t>
+        </is>
+      </c>
+      <c r="B1007" t="n">
+        <v>6271527</v>
+      </c>
+      <c r="C1007" t="n">
+        <v>3</v>
+      </c>
+      <c r="D1007" t="n">
+        <v>4</v>
+      </c>
+      <c r="E1007" t="n">
+        <v>4</v>
+      </c>
+      <c r="F1007" t="inlineStr">
+        <is>
+          <t>2026-09-09</t>
+        </is>
+      </c>
+    </row>
+    <row r="1008">
+      <c r="A1008" t="inlineStr">
+        <is>
+          <t>5f47aeb6c387a50bca03dd55</t>
+        </is>
+      </c>
+      <c r="B1008" t="n">
+        <v>5315390</v>
+      </c>
+      <c r="C1008" t="n">
+        <v>0</v>
+      </c>
+      <c r="D1008" t="n">
+        <v>2</v>
+      </c>
+      <c r="E1008" t="n">
+        <v>0</v>
+      </c>
+      <c r="F1008" t="inlineStr">
+        <is>
+          <t>2026-09-09</t>
+        </is>
+      </c>
+    </row>
+    <row r="1009">
+      <c r="A1009" t="inlineStr">
+        <is>
+          <t>5f4530beec331549297ee6d6</t>
+        </is>
+      </c>
+      <c r="B1009" t="n">
+        <v>4575240</v>
+      </c>
+      <c r="C1009" t="n">
+        <v>0</v>
+      </c>
+      <c r="D1009" t="n">
+        <v>3</v>
+      </c>
+      <c r="E1009" t="n">
+        <v>0</v>
+      </c>
+      <c r="F1009" t="inlineStr">
+        <is>
+          <t>2026-09-09</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/datos/hechos/td_admin.xlsx
+++ b/datos/hechos/td_admin.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F1009"/>
+  <dimension ref="A1:F1017"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -24652,6 +24652,198 @@
         </is>
       </c>
     </row>
+    <row r="1010">
+      <c r="A1010" t="inlineStr">
+        <is>
+          <t>5f45324dec331549297ee971</t>
+        </is>
+      </c>
+      <c r="B1010" t="n">
+        <v>3086621</v>
+      </c>
+      <c r="C1010" t="n">
+        <v>1</v>
+      </c>
+      <c r="D1010" t="n">
+        <v>2</v>
+      </c>
+      <c r="E1010" t="n">
+        <v>1</v>
+      </c>
+      <c r="F1010" t="inlineStr">
+        <is>
+          <t>2026-09-10</t>
+        </is>
+      </c>
+    </row>
+    <row r="1011">
+      <c r="A1011" t="inlineStr">
+        <is>
+          <t>62d5bd9ad8106d3355b5bdc1</t>
+        </is>
+      </c>
+      <c r="B1011" t="n">
+        <v>-971746</v>
+      </c>
+      <c r="C1011" t="n">
+        <v>1</v>
+      </c>
+      <c r="D1011" t="n">
+        <v>2</v>
+      </c>
+      <c r="E1011" t="n">
+        <v>1</v>
+      </c>
+      <c r="F1011" t="inlineStr">
+        <is>
+          <t>2026-09-10</t>
+        </is>
+      </c>
+    </row>
+    <row r="1012">
+      <c r="A1012" t="inlineStr">
+        <is>
+          <t>5f4531e9764e7d491e029746</t>
+        </is>
+      </c>
+      <c r="B1012" t="n">
+        <v>3613503</v>
+      </c>
+      <c r="C1012" t="n">
+        <v>0</v>
+      </c>
+      <c r="D1012" t="n">
+        <v>0</v>
+      </c>
+      <c r="E1012" t="n">
+        <v>0</v>
+      </c>
+      <c r="F1012" t="inlineStr">
+        <is>
+          <t>2026-09-10</t>
+        </is>
+      </c>
+    </row>
+    <row r="1013">
+      <c r="A1013" t="inlineStr">
+        <is>
+          <t>5f453062ec331549297ee6b8</t>
+        </is>
+      </c>
+      <c r="B1013" t="n">
+        <v>735962</v>
+      </c>
+      <c r="C1013" t="n">
+        <v>1</v>
+      </c>
+      <c r="D1013" t="n">
+        <v>3</v>
+      </c>
+      <c r="E1013" t="n">
+        <v>0</v>
+      </c>
+      <c r="F1013" t="inlineStr">
+        <is>
+          <t>2026-09-10</t>
+        </is>
+      </c>
+    </row>
+    <row r="1014">
+      <c r="A1014" t="inlineStr">
+        <is>
+          <t>5f47ab5b9e2edb0bb831c703</t>
+        </is>
+      </c>
+      <c r="B1014" t="n">
+        <v>9413033</v>
+      </c>
+      <c r="C1014" t="n">
+        <v>0</v>
+      </c>
+      <c r="D1014" t="n">
+        <v>1</v>
+      </c>
+      <c r="E1014" t="n">
+        <v>0</v>
+      </c>
+      <c r="F1014" t="inlineStr">
+        <is>
+          <t>2026-09-10</t>
+        </is>
+      </c>
+    </row>
+    <row r="1015">
+      <c r="A1015" t="inlineStr">
+        <is>
+          <t>5f452f5e66dd374930eb2b71</t>
+        </is>
+      </c>
+      <c r="B1015" t="n">
+        <v>6271527</v>
+      </c>
+      <c r="C1015" t="n">
+        <v>3</v>
+      </c>
+      <c r="D1015" t="n">
+        <v>4</v>
+      </c>
+      <c r="E1015" t="n">
+        <v>4</v>
+      </c>
+      <c r="F1015" t="inlineStr">
+        <is>
+          <t>2026-09-10</t>
+        </is>
+      </c>
+    </row>
+    <row r="1016">
+      <c r="A1016" t="inlineStr">
+        <is>
+          <t>5f47aeb6c387a50bca03dd55</t>
+        </is>
+      </c>
+      <c r="B1016" t="n">
+        <v>1515390</v>
+      </c>
+      <c r="C1016" t="n">
+        <v>0</v>
+      </c>
+      <c r="D1016" t="n">
+        <v>2</v>
+      </c>
+      <c r="E1016" t="n">
+        <v>0</v>
+      </c>
+      <c r="F1016" t="inlineStr">
+        <is>
+          <t>2026-09-10</t>
+        </is>
+      </c>
+    </row>
+    <row r="1017">
+      <c r="A1017" t="inlineStr">
+        <is>
+          <t>5f4530beec331549297ee6d6</t>
+        </is>
+      </c>
+      <c r="B1017" t="n">
+        <v>4575240</v>
+      </c>
+      <c r="C1017" t="n">
+        <v>0</v>
+      </c>
+      <c r="D1017" t="n">
+        <v>3</v>
+      </c>
+      <c r="E1017" t="n">
+        <v>0</v>
+      </c>
+      <c r="F1017" t="inlineStr">
+        <is>
+          <t>2026-09-10</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/datos/hechos/td_admin.xlsx
+++ b/datos/hechos/td_admin.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F1017"/>
+  <dimension ref="A1:F1025"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -24844,6 +24844,198 @@
         </is>
       </c>
     </row>
+    <row r="1018">
+      <c r="A1018" t="inlineStr">
+        <is>
+          <t>5f45324dec331549297ee971</t>
+        </is>
+      </c>
+      <c r="B1018" t="n">
+        <v>3086621</v>
+      </c>
+      <c r="C1018" t="n">
+        <v>1</v>
+      </c>
+      <c r="D1018" t="n">
+        <v>2</v>
+      </c>
+      <c r="E1018" t="n">
+        <v>1</v>
+      </c>
+      <c r="F1018" t="inlineStr">
+        <is>
+          <t>2026-09-11</t>
+        </is>
+      </c>
+    </row>
+    <row r="1019">
+      <c r="A1019" t="inlineStr">
+        <is>
+          <t>62d5bd9ad8106d3355b5bdc1</t>
+        </is>
+      </c>
+      <c r="B1019" t="n">
+        <v>-971746</v>
+      </c>
+      <c r="C1019" t="n">
+        <v>1</v>
+      </c>
+      <c r="D1019" t="n">
+        <v>2</v>
+      </c>
+      <c r="E1019" t="n">
+        <v>1</v>
+      </c>
+      <c r="F1019" t="inlineStr">
+        <is>
+          <t>2026-09-11</t>
+        </is>
+      </c>
+    </row>
+    <row r="1020">
+      <c r="A1020" t="inlineStr">
+        <is>
+          <t>5f4531e9764e7d491e029746</t>
+        </is>
+      </c>
+      <c r="B1020" t="n">
+        <v>3613503</v>
+      </c>
+      <c r="C1020" t="n">
+        <v>0</v>
+      </c>
+      <c r="D1020" t="n">
+        <v>0</v>
+      </c>
+      <c r="E1020" t="n">
+        <v>0</v>
+      </c>
+      <c r="F1020" t="inlineStr">
+        <is>
+          <t>2026-09-11</t>
+        </is>
+      </c>
+    </row>
+    <row r="1021">
+      <c r="A1021" t="inlineStr">
+        <is>
+          <t>5f453062ec331549297ee6b8</t>
+        </is>
+      </c>
+      <c r="B1021" t="n">
+        <v>846053</v>
+      </c>
+      <c r="C1021" t="n">
+        <v>1</v>
+      </c>
+      <c r="D1021" t="n">
+        <v>3</v>
+      </c>
+      <c r="E1021" t="n">
+        <v>0</v>
+      </c>
+      <c r="F1021" t="inlineStr">
+        <is>
+          <t>2026-09-11</t>
+        </is>
+      </c>
+    </row>
+    <row r="1022">
+      <c r="A1022" t="inlineStr">
+        <is>
+          <t>5f47ab5b9e2edb0bb831c703</t>
+        </is>
+      </c>
+      <c r="B1022" t="n">
+        <v>9413033</v>
+      </c>
+      <c r="C1022" t="n">
+        <v>0</v>
+      </c>
+      <c r="D1022" t="n">
+        <v>1</v>
+      </c>
+      <c r="E1022" t="n">
+        <v>0</v>
+      </c>
+      <c r="F1022" t="inlineStr">
+        <is>
+          <t>2026-09-11</t>
+        </is>
+      </c>
+    </row>
+    <row r="1023">
+      <c r="A1023" t="inlineStr">
+        <is>
+          <t>5f452f5e66dd374930eb2b71</t>
+        </is>
+      </c>
+      <c r="B1023" t="n">
+        <v>271518</v>
+      </c>
+      <c r="C1023" t="n">
+        <v>3</v>
+      </c>
+      <c r="D1023" t="n">
+        <v>4</v>
+      </c>
+      <c r="E1023" t="n">
+        <v>4</v>
+      </c>
+      <c r="F1023" t="inlineStr">
+        <is>
+          <t>2026-09-11</t>
+        </is>
+      </c>
+    </row>
+    <row r="1024">
+      <c r="A1024" t="inlineStr">
+        <is>
+          <t>5f47aeb6c387a50bca03dd55</t>
+        </is>
+      </c>
+      <c r="B1024" t="n">
+        <v>1515390</v>
+      </c>
+      <c r="C1024" t="n">
+        <v>0</v>
+      </c>
+      <c r="D1024" t="n">
+        <v>2</v>
+      </c>
+      <c r="E1024" t="n">
+        <v>0</v>
+      </c>
+      <c r="F1024" t="inlineStr">
+        <is>
+          <t>2026-09-11</t>
+        </is>
+      </c>
+    </row>
+    <row r="1025">
+      <c r="A1025" t="inlineStr">
+        <is>
+          <t>5f4530beec331549297ee6d6</t>
+        </is>
+      </c>
+      <c r="B1025" t="n">
+        <v>-14825760</v>
+      </c>
+      <c r="C1025" t="n">
+        <v>0</v>
+      </c>
+      <c r="D1025" t="n">
+        <v>3</v>
+      </c>
+      <c r="E1025" t="n">
+        <v>0</v>
+      </c>
+      <c r="F1025" t="inlineStr">
+        <is>
+          <t>2026-09-11</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/datos/hechos/td_admin.xlsx
+++ b/datos/hechos/td_admin.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F1025"/>
+  <dimension ref="A1:F1033"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -25036,6 +25036,198 @@
         </is>
       </c>
     </row>
+    <row r="1026">
+      <c r="A1026" t="inlineStr">
+        <is>
+          <t>5f45324dec331549297ee971</t>
+        </is>
+      </c>
+      <c r="B1026" t="n">
+        <v>3086621</v>
+      </c>
+      <c r="C1026" t="n">
+        <v>1</v>
+      </c>
+      <c r="D1026" t="n">
+        <v>2</v>
+      </c>
+      <c r="E1026" t="n">
+        <v>1</v>
+      </c>
+      <c r="F1026" t="inlineStr">
+        <is>
+          <t>2026-09-12</t>
+        </is>
+      </c>
+    </row>
+    <row r="1027">
+      <c r="A1027" t="inlineStr">
+        <is>
+          <t>62d5bd9ad8106d3355b5bdc1</t>
+        </is>
+      </c>
+      <c r="B1027" t="n">
+        <v>-4271745</v>
+      </c>
+      <c r="C1027" t="n">
+        <v>1</v>
+      </c>
+      <c r="D1027" t="n">
+        <v>2</v>
+      </c>
+      <c r="E1027" t="n">
+        <v>1</v>
+      </c>
+      <c r="F1027" t="inlineStr">
+        <is>
+          <t>2026-09-12</t>
+        </is>
+      </c>
+    </row>
+    <row r="1028">
+      <c r="A1028" t="inlineStr">
+        <is>
+          <t>5f4531e9764e7d491e029746</t>
+        </is>
+      </c>
+      <c r="B1028" t="n">
+        <v>3613503</v>
+      </c>
+      <c r="C1028" t="n">
+        <v>0</v>
+      </c>
+      <c r="D1028" t="n">
+        <v>0</v>
+      </c>
+      <c r="E1028" t="n">
+        <v>0</v>
+      </c>
+      <c r="F1028" t="inlineStr">
+        <is>
+          <t>2026-09-12</t>
+        </is>
+      </c>
+    </row>
+    <row r="1029">
+      <c r="A1029" t="inlineStr">
+        <is>
+          <t>5f453062ec331549297ee6b8</t>
+        </is>
+      </c>
+      <c r="B1029" t="n">
+        <v>-20264048</v>
+      </c>
+      <c r="C1029" t="n">
+        <v>1</v>
+      </c>
+      <c r="D1029" t="n">
+        <v>3</v>
+      </c>
+      <c r="E1029" t="n">
+        <v>0</v>
+      </c>
+      <c r="F1029" t="inlineStr">
+        <is>
+          <t>2026-09-12</t>
+        </is>
+      </c>
+    </row>
+    <row r="1030">
+      <c r="A1030" t="inlineStr">
+        <is>
+          <t>5f47ab5b9e2edb0bb831c703</t>
+        </is>
+      </c>
+      <c r="B1030" t="n">
+        <v>10413033</v>
+      </c>
+      <c r="C1030" t="n">
+        <v>0</v>
+      </c>
+      <c r="D1030" t="n">
+        <v>1</v>
+      </c>
+      <c r="E1030" t="n">
+        <v>0</v>
+      </c>
+      <c r="F1030" t="inlineStr">
+        <is>
+          <t>2026-09-12</t>
+        </is>
+      </c>
+    </row>
+    <row r="1031">
+      <c r="A1031" t="inlineStr">
+        <is>
+          <t>5f452f5e66dd374930eb2b71</t>
+        </is>
+      </c>
+      <c r="B1031" t="n">
+        <v>271518</v>
+      </c>
+      <c r="C1031" t="n">
+        <v>3</v>
+      </c>
+      <c r="D1031" t="n">
+        <v>4</v>
+      </c>
+      <c r="E1031" t="n">
+        <v>4</v>
+      </c>
+      <c r="F1031" t="inlineStr">
+        <is>
+          <t>2026-09-12</t>
+        </is>
+      </c>
+    </row>
+    <row r="1032">
+      <c r="A1032" t="inlineStr">
+        <is>
+          <t>5f47aeb6c387a50bca03dd55</t>
+        </is>
+      </c>
+      <c r="B1032" t="n">
+        <v>1515390</v>
+      </c>
+      <c r="C1032" t="n">
+        <v>0</v>
+      </c>
+      <c r="D1032" t="n">
+        <v>2</v>
+      </c>
+      <c r="E1032" t="n">
+        <v>0</v>
+      </c>
+      <c r="F1032" t="inlineStr">
+        <is>
+          <t>2026-09-12</t>
+        </is>
+      </c>
+    </row>
+    <row r="1033">
+      <c r="A1033" t="inlineStr">
+        <is>
+          <t>5f4530beec331549297ee6d6</t>
+        </is>
+      </c>
+      <c r="B1033" t="n">
+        <v>3918128</v>
+      </c>
+      <c r="C1033" t="n">
+        <v>0</v>
+      </c>
+      <c r="D1033" t="n">
+        <v>3</v>
+      </c>
+      <c r="E1033" t="n">
+        <v>0</v>
+      </c>
+      <c r="F1033" t="inlineStr">
+        <is>
+          <t>2026-09-12</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/datos/hechos/td_admin.xlsx
+++ b/datos/hechos/td_admin.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F1033"/>
+  <dimension ref="A1:F1041"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -25228,6 +25228,198 @@
         </is>
       </c>
     </row>
+    <row r="1034">
+      <c r="A1034" t="inlineStr">
+        <is>
+          <t>5f45324dec331549297ee971</t>
+        </is>
+      </c>
+      <c r="B1034" t="n">
+        <v>3086621</v>
+      </c>
+      <c r="C1034" t="n">
+        <v>1</v>
+      </c>
+      <c r="D1034" t="n">
+        <v>2</v>
+      </c>
+      <c r="E1034" t="n">
+        <v>1</v>
+      </c>
+      <c r="F1034" t="inlineStr">
+        <is>
+          <t>2026-09-13</t>
+        </is>
+      </c>
+    </row>
+    <row r="1035">
+      <c r="A1035" t="inlineStr">
+        <is>
+          <t>62d5bd9ad8106d3355b5bdc1</t>
+        </is>
+      </c>
+      <c r="B1035" t="n">
+        <v>-4271745</v>
+      </c>
+      <c r="C1035" t="n">
+        <v>1</v>
+      </c>
+      <c r="D1035" t="n">
+        <v>2</v>
+      </c>
+      <c r="E1035" t="n">
+        <v>1</v>
+      </c>
+      <c r="F1035" t="inlineStr">
+        <is>
+          <t>2026-09-13</t>
+        </is>
+      </c>
+    </row>
+    <row r="1036">
+      <c r="A1036" t="inlineStr">
+        <is>
+          <t>5f4531e9764e7d491e029746</t>
+        </is>
+      </c>
+      <c r="B1036" t="n">
+        <v>3613503</v>
+      </c>
+      <c r="C1036" t="n">
+        <v>0</v>
+      </c>
+      <c r="D1036" t="n">
+        <v>0</v>
+      </c>
+      <c r="E1036" t="n">
+        <v>0</v>
+      </c>
+      <c r="F1036" t="inlineStr">
+        <is>
+          <t>2026-09-13</t>
+        </is>
+      </c>
+    </row>
+    <row r="1037">
+      <c r="A1037" t="inlineStr">
+        <is>
+          <t>5f453062ec331549297ee6b8</t>
+        </is>
+      </c>
+      <c r="B1037" t="n">
+        <v>-20264048</v>
+      </c>
+      <c r="C1037" t="n">
+        <v>1</v>
+      </c>
+      <c r="D1037" t="n">
+        <v>3</v>
+      </c>
+      <c r="E1037" t="n">
+        <v>0</v>
+      </c>
+      <c r="F1037" t="inlineStr">
+        <is>
+          <t>2026-09-13</t>
+        </is>
+      </c>
+    </row>
+    <row r="1038">
+      <c r="A1038" t="inlineStr">
+        <is>
+          <t>5f47ab5b9e2edb0bb831c703</t>
+        </is>
+      </c>
+      <c r="B1038" t="n">
+        <v>441395</v>
+      </c>
+      <c r="C1038" t="n">
+        <v>0</v>
+      </c>
+      <c r="D1038" t="n">
+        <v>1</v>
+      </c>
+      <c r="E1038" t="n">
+        <v>0</v>
+      </c>
+      <c r="F1038" t="inlineStr">
+        <is>
+          <t>2026-09-13</t>
+        </is>
+      </c>
+    </row>
+    <row r="1039">
+      <c r="A1039" t="inlineStr">
+        <is>
+          <t>5f452f5e66dd374930eb2b71</t>
+        </is>
+      </c>
+      <c r="B1039" t="n">
+        <v>55158024</v>
+      </c>
+      <c r="C1039" t="n">
+        <v>3</v>
+      </c>
+      <c r="D1039" t="n">
+        <v>4</v>
+      </c>
+      <c r="E1039" t="n">
+        <v>4</v>
+      </c>
+      <c r="F1039" t="inlineStr">
+        <is>
+          <t>2026-09-13</t>
+        </is>
+      </c>
+    </row>
+    <row r="1040">
+      <c r="A1040" t="inlineStr">
+        <is>
+          <t>5f47aeb6c387a50bca03dd55</t>
+        </is>
+      </c>
+      <c r="B1040" t="n">
+        <v>-384610</v>
+      </c>
+      <c r="C1040" t="n">
+        <v>0</v>
+      </c>
+      <c r="D1040" t="n">
+        <v>2</v>
+      </c>
+      <c r="E1040" t="n">
+        <v>0</v>
+      </c>
+      <c r="F1040" t="inlineStr">
+        <is>
+          <t>2026-09-13</t>
+        </is>
+      </c>
+    </row>
+    <row r="1041">
+      <c r="A1041" t="inlineStr">
+        <is>
+          <t>5f4530beec331549297ee6d6</t>
+        </is>
+      </c>
+      <c r="B1041" t="n">
+        <v>18398300</v>
+      </c>
+      <c r="C1041" t="n">
+        <v>0</v>
+      </c>
+      <c r="D1041" t="n">
+        <v>3</v>
+      </c>
+      <c r="E1041" t="n">
+        <v>0</v>
+      </c>
+      <c r="F1041" t="inlineStr">
+        <is>
+          <t>2026-09-13</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/datos/hechos/td_admin.xlsx
+++ b/datos/hechos/td_admin.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F1041"/>
+  <dimension ref="A1:F1049"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -25420,6 +25420,198 @@
         </is>
       </c>
     </row>
+    <row r="1042">
+      <c r="A1042" t="inlineStr">
+        <is>
+          <t>5f45324dec331549297ee971</t>
+        </is>
+      </c>
+      <c r="B1042" t="n">
+        <v>-8813379</v>
+      </c>
+      <c r="C1042" t="n">
+        <v>1</v>
+      </c>
+      <c r="D1042" t="n">
+        <v>2</v>
+      </c>
+      <c r="E1042" t="n">
+        <v>1</v>
+      </c>
+      <c r="F1042" t="inlineStr">
+        <is>
+          <t>2026-09-14</t>
+        </is>
+      </c>
+    </row>
+    <row r="1043">
+      <c r="A1043" t="inlineStr">
+        <is>
+          <t>62d5bd9ad8106d3355b5bdc1</t>
+        </is>
+      </c>
+      <c r="B1043" t="n">
+        <v>-65740</v>
+      </c>
+      <c r="C1043" t="n">
+        <v>1</v>
+      </c>
+      <c r="D1043" t="n">
+        <v>2</v>
+      </c>
+      <c r="E1043" t="n">
+        <v>1</v>
+      </c>
+      <c r="F1043" t="inlineStr">
+        <is>
+          <t>2026-09-14</t>
+        </is>
+      </c>
+    </row>
+    <row r="1044">
+      <c r="A1044" t="inlineStr">
+        <is>
+          <t>5f4531e9764e7d491e029746</t>
+        </is>
+      </c>
+      <c r="B1044" t="n">
+        <v>3613503</v>
+      </c>
+      <c r="C1044" t="n">
+        <v>0</v>
+      </c>
+      <c r="D1044" t="n">
+        <v>0</v>
+      </c>
+      <c r="E1044" t="n">
+        <v>0</v>
+      </c>
+      <c r="F1044" t="inlineStr">
+        <is>
+          <t>2026-09-14</t>
+        </is>
+      </c>
+    </row>
+    <row r="1045">
+      <c r="A1045" t="inlineStr">
+        <is>
+          <t>5f453062ec331549297ee6b8</t>
+        </is>
+      </c>
+      <c r="B1045" t="n">
+        <v>21152940</v>
+      </c>
+      <c r="C1045" t="n">
+        <v>1</v>
+      </c>
+      <c r="D1045" t="n">
+        <v>3</v>
+      </c>
+      <c r="E1045" t="n">
+        <v>0</v>
+      </c>
+      <c r="F1045" t="inlineStr">
+        <is>
+          <t>2026-09-14</t>
+        </is>
+      </c>
+    </row>
+    <row r="1046">
+      <c r="A1046" t="inlineStr">
+        <is>
+          <t>5f47ab5b9e2edb0bb831c703</t>
+        </is>
+      </c>
+      <c r="B1046" t="n">
+        <v>-4061667</v>
+      </c>
+      <c r="C1046" t="n">
+        <v>0</v>
+      </c>
+      <c r="D1046" t="n">
+        <v>1</v>
+      </c>
+      <c r="E1046" t="n">
+        <v>0</v>
+      </c>
+      <c r="F1046" t="inlineStr">
+        <is>
+          <t>2026-09-14</t>
+        </is>
+      </c>
+    </row>
+    <row r="1047">
+      <c r="A1047" t="inlineStr">
+        <is>
+          <t>5f452f5e66dd374930eb2b71</t>
+        </is>
+      </c>
+      <c r="B1047" t="n">
+        <v>54158023</v>
+      </c>
+      <c r="C1047" t="n">
+        <v>3</v>
+      </c>
+      <c r="D1047" t="n">
+        <v>4</v>
+      </c>
+      <c r="E1047" t="n">
+        <v>4</v>
+      </c>
+      <c r="F1047" t="inlineStr">
+        <is>
+          <t>2026-09-14</t>
+        </is>
+      </c>
+    </row>
+    <row r="1048">
+      <c r="A1048" t="inlineStr">
+        <is>
+          <t>5f47aeb6c387a50bca03dd55</t>
+        </is>
+      </c>
+      <c r="B1048" t="n">
+        <v>2759250</v>
+      </c>
+      <c r="C1048" t="n">
+        <v>0</v>
+      </c>
+      <c r="D1048" t="n">
+        <v>2</v>
+      </c>
+      <c r="E1048" t="n">
+        <v>0</v>
+      </c>
+      <c r="F1048" t="inlineStr">
+        <is>
+          <t>2026-09-14</t>
+        </is>
+      </c>
+    </row>
+    <row r="1049">
+      <c r="A1049" t="inlineStr">
+        <is>
+          <t>5f4530beec331549297ee6d6</t>
+        </is>
+      </c>
+      <c r="B1049" t="n">
+        <v>18398300</v>
+      </c>
+      <c r="C1049" t="n">
+        <v>0</v>
+      </c>
+      <c r="D1049" t="n">
+        <v>3</v>
+      </c>
+      <c r="E1049" t="n">
+        <v>0</v>
+      </c>
+      <c r="F1049" t="inlineStr">
+        <is>
+          <t>2026-09-14</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/datos/hechos/td_admin.xlsx
+++ b/datos/hechos/td_admin.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F1049"/>
+  <dimension ref="A1:F1057"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -25612,6 +25612,198 @@
         </is>
       </c>
     </row>
+    <row r="1050">
+      <c r="A1050" t="inlineStr">
+        <is>
+          <t>5f45324dec331549297ee971</t>
+        </is>
+      </c>
+      <c r="B1050" t="n">
+        <v>6127847</v>
+      </c>
+      <c r="C1050" t="n">
+        <v>1</v>
+      </c>
+      <c r="D1050" t="n">
+        <v>2</v>
+      </c>
+      <c r="E1050" t="n">
+        <v>1</v>
+      </c>
+      <c r="F1050" t="inlineStr">
+        <is>
+          <t>2026-09-15</t>
+        </is>
+      </c>
+    </row>
+    <row r="1051">
+      <c r="A1051" t="inlineStr">
+        <is>
+          <t>5f4531e9764e7d491e029746</t>
+        </is>
+      </c>
+      <c r="B1051" t="n">
+        <v>5611503</v>
+      </c>
+      <c r="C1051" t="n">
+        <v>0</v>
+      </c>
+      <c r="D1051" t="n">
+        <v>0</v>
+      </c>
+      <c r="E1051" t="n">
+        <v>0</v>
+      </c>
+      <c r="F1051" t="inlineStr">
+        <is>
+          <t>2026-09-15</t>
+        </is>
+      </c>
+    </row>
+    <row r="1052">
+      <c r="A1052" t="inlineStr">
+        <is>
+          <t>62d5bd9ad8106d3355b5bdc1</t>
+        </is>
+      </c>
+      <c r="B1052" t="n">
+        <v>32359711</v>
+      </c>
+      <c r="C1052" t="n">
+        <v>1</v>
+      </c>
+      <c r="D1052" t="n">
+        <v>2</v>
+      </c>
+      <c r="E1052" t="n">
+        <v>1</v>
+      </c>
+      <c r="F1052" t="inlineStr">
+        <is>
+          <t>2026-09-15</t>
+        </is>
+      </c>
+    </row>
+    <row r="1053">
+      <c r="A1053" t="inlineStr">
+        <is>
+          <t>5f453062ec331549297ee6b8</t>
+        </is>
+      </c>
+      <c r="B1053" t="n">
+        <v>-18367061</v>
+      </c>
+      <c r="C1053" t="n">
+        <v>1</v>
+      </c>
+      <c r="D1053" t="n">
+        <v>3</v>
+      </c>
+      <c r="E1053" t="n">
+        <v>0</v>
+      </c>
+      <c r="F1053" t="inlineStr">
+        <is>
+          <t>2026-09-15</t>
+        </is>
+      </c>
+    </row>
+    <row r="1054">
+      <c r="A1054" t="inlineStr">
+        <is>
+          <t>5f47aeb6c387a50bca03dd55</t>
+        </is>
+      </c>
+      <c r="B1054" t="n">
+        <v>4856250</v>
+      </c>
+      <c r="C1054" t="n">
+        <v>0</v>
+      </c>
+      <c r="D1054" t="n">
+        <v>2</v>
+      </c>
+      <c r="E1054" t="n">
+        <v>0</v>
+      </c>
+      <c r="F1054" t="inlineStr">
+        <is>
+          <t>2026-09-15</t>
+        </is>
+      </c>
+    </row>
+    <row r="1055">
+      <c r="A1055" t="inlineStr">
+        <is>
+          <t>5f47ab5b9e2edb0bb831c703</t>
+        </is>
+      </c>
+      <c r="B1055" t="n">
+        <v>2818892</v>
+      </c>
+      <c r="C1055" t="n">
+        <v>0</v>
+      </c>
+      <c r="D1055" t="n">
+        <v>1</v>
+      </c>
+      <c r="E1055" t="n">
+        <v>0</v>
+      </c>
+      <c r="F1055" t="inlineStr">
+        <is>
+          <t>2026-09-15</t>
+        </is>
+      </c>
+    </row>
+    <row r="1056">
+      <c r="A1056" t="inlineStr">
+        <is>
+          <t>5f452f5e66dd374930eb2b71</t>
+        </is>
+      </c>
+      <c r="B1056" t="n">
+        <v>55536023</v>
+      </c>
+      <c r="C1056" t="n">
+        <v>3</v>
+      </c>
+      <c r="D1056" t="n">
+        <v>4</v>
+      </c>
+      <c r="E1056" t="n">
+        <v>4</v>
+      </c>
+      <c r="F1056" t="inlineStr">
+        <is>
+          <t>2026-09-15</t>
+        </is>
+      </c>
+    </row>
+    <row r="1057">
+      <c r="A1057" t="inlineStr">
+        <is>
+          <t>5f4530beec331549297ee6d6</t>
+        </is>
+      </c>
+      <c r="B1057" t="n">
+        <v>21139300</v>
+      </c>
+      <c r="C1057" t="n">
+        <v>0</v>
+      </c>
+      <c r="D1057" t="n">
+        <v>3</v>
+      </c>
+      <c r="E1057" t="n">
+        <v>0</v>
+      </c>
+      <c r="F1057" t="inlineStr">
+        <is>
+          <t>2026-09-15</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/datos/hechos/td_admin.xlsx
+++ b/datos/hechos/td_admin.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F1057"/>
+  <dimension ref="A1:F1065"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -25804,6 +25804,198 @@
         </is>
       </c>
     </row>
+    <row r="1058">
+      <c r="A1058" t="inlineStr">
+        <is>
+          <t>5f45324dec331549297ee971</t>
+        </is>
+      </c>
+      <c r="B1058" t="n">
+        <v>6127847</v>
+      </c>
+      <c r="C1058" t="n">
+        <v>1</v>
+      </c>
+      <c r="D1058" t="n">
+        <v>2</v>
+      </c>
+      <c r="E1058" t="n">
+        <v>1</v>
+      </c>
+      <c r="F1058" t="inlineStr">
+        <is>
+          <t>2026-09-16</t>
+        </is>
+      </c>
+    </row>
+    <row r="1059">
+      <c r="A1059" t="inlineStr">
+        <is>
+          <t>5f4531e9764e7d491e029746</t>
+        </is>
+      </c>
+      <c r="B1059" t="n">
+        <v>5611503</v>
+      </c>
+      <c r="C1059" t="n">
+        <v>0</v>
+      </c>
+      <c r="D1059" t="n">
+        <v>0</v>
+      </c>
+      <c r="E1059" t="n">
+        <v>0</v>
+      </c>
+      <c r="F1059" t="inlineStr">
+        <is>
+          <t>2026-09-16</t>
+        </is>
+      </c>
+    </row>
+    <row r="1060">
+      <c r="A1060" t="inlineStr">
+        <is>
+          <t>62d5bd9ad8106d3355b5bdc1</t>
+        </is>
+      </c>
+      <c r="B1060" t="n">
+        <v>32359711</v>
+      </c>
+      <c r="C1060" t="n">
+        <v>1</v>
+      </c>
+      <c r="D1060" t="n">
+        <v>2</v>
+      </c>
+      <c r="E1060" t="n">
+        <v>1</v>
+      </c>
+      <c r="F1060" t="inlineStr">
+        <is>
+          <t>2026-09-16</t>
+        </is>
+      </c>
+    </row>
+    <row r="1061">
+      <c r="A1061" t="inlineStr">
+        <is>
+          <t>5f453062ec331549297ee6b8</t>
+        </is>
+      </c>
+      <c r="B1061" t="n">
+        <v>-8391291</v>
+      </c>
+      <c r="C1061" t="n">
+        <v>1</v>
+      </c>
+      <c r="D1061" t="n">
+        <v>3</v>
+      </c>
+      <c r="E1061" t="n">
+        <v>0</v>
+      </c>
+      <c r="F1061" t="inlineStr">
+        <is>
+          <t>2026-09-16</t>
+        </is>
+      </c>
+    </row>
+    <row r="1062">
+      <c r="A1062" t="inlineStr">
+        <is>
+          <t>5f47aeb6c387a50bca03dd55</t>
+        </is>
+      </c>
+      <c r="B1062" t="n">
+        <v>4856250</v>
+      </c>
+      <c r="C1062" t="n">
+        <v>0</v>
+      </c>
+      <c r="D1062" t="n">
+        <v>2</v>
+      </c>
+      <c r="E1062" t="n">
+        <v>0</v>
+      </c>
+      <c r="F1062" t="inlineStr">
+        <is>
+          <t>2026-09-16</t>
+        </is>
+      </c>
+    </row>
+    <row r="1063">
+      <c r="A1063" t="inlineStr">
+        <is>
+          <t>5f47ab5b9e2edb0bb831c703</t>
+        </is>
+      </c>
+      <c r="B1063" t="n">
+        <v>-2292712</v>
+      </c>
+      <c r="C1063" t="n">
+        <v>0</v>
+      </c>
+      <c r="D1063" t="n">
+        <v>1</v>
+      </c>
+      <c r="E1063" t="n">
+        <v>0</v>
+      </c>
+      <c r="F1063" t="inlineStr">
+        <is>
+          <t>2026-09-16</t>
+        </is>
+      </c>
+    </row>
+    <row r="1064">
+      <c r="A1064" t="inlineStr">
+        <is>
+          <t>5f452f5e66dd374930eb2b71</t>
+        </is>
+      </c>
+      <c r="B1064" t="n">
+        <v>36178989</v>
+      </c>
+      <c r="C1064" t="n">
+        <v>3</v>
+      </c>
+      <c r="D1064" t="n">
+        <v>4</v>
+      </c>
+      <c r="E1064" t="n">
+        <v>4</v>
+      </c>
+      <c r="F1064" t="inlineStr">
+        <is>
+          <t>2026-09-16</t>
+        </is>
+      </c>
+    </row>
+    <row r="1065">
+      <c r="A1065" t="inlineStr">
+        <is>
+          <t>5f4530beec331549297ee6d6</t>
+        </is>
+      </c>
+      <c r="B1065" t="n">
+        <v>21139300</v>
+      </c>
+      <c r="C1065" t="n">
+        <v>0</v>
+      </c>
+      <c r="D1065" t="n">
+        <v>3</v>
+      </c>
+      <c r="E1065" t="n">
+        <v>0</v>
+      </c>
+      <c r="F1065" t="inlineStr">
+        <is>
+          <t>2026-09-16</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/datos/hechos/td_admin.xlsx
+++ b/datos/hechos/td_admin.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F1065"/>
+  <dimension ref="A1:F1073"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -25996,6 +25996,198 @@
         </is>
       </c>
     </row>
+    <row r="1066">
+      <c r="A1066" t="inlineStr">
+        <is>
+          <t>5f45324dec331549297ee971</t>
+        </is>
+      </c>
+      <c r="B1066" t="n">
+        <v>6127847</v>
+      </c>
+      <c r="C1066" t="n">
+        <v>1</v>
+      </c>
+      <c r="D1066" t="n">
+        <v>2</v>
+      </c>
+      <c r="E1066" t="n">
+        <v>1</v>
+      </c>
+      <c r="F1066" t="inlineStr">
+        <is>
+          <t>2026-09-17</t>
+        </is>
+      </c>
+    </row>
+    <row r="1067">
+      <c r="A1067" t="inlineStr">
+        <is>
+          <t>5f4531e9764e7d491e029746</t>
+        </is>
+      </c>
+      <c r="B1067" t="n">
+        <v>5611503</v>
+      </c>
+      <c r="C1067" t="n">
+        <v>0</v>
+      </c>
+      <c r="D1067" t="n">
+        <v>0</v>
+      </c>
+      <c r="E1067" t="n">
+        <v>0</v>
+      </c>
+      <c r="F1067" t="inlineStr">
+        <is>
+          <t>2026-09-17</t>
+        </is>
+      </c>
+    </row>
+    <row r="1068">
+      <c r="A1068" t="inlineStr">
+        <is>
+          <t>62d5bd9ad8106d3355b5bdc1</t>
+        </is>
+      </c>
+      <c r="B1068" t="n">
+        <v>50111446</v>
+      </c>
+      <c r="C1068" t="n">
+        <v>1</v>
+      </c>
+      <c r="D1068" t="n">
+        <v>2</v>
+      </c>
+      <c r="E1068" t="n">
+        <v>1</v>
+      </c>
+      <c r="F1068" t="inlineStr">
+        <is>
+          <t>2026-09-17</t>
+        </is>
+      </c>
+    </row>
+    <row r="1069">
+      <c r="A1069" t="inlineStr">
+        <is>
+          <t>5f453062ec331549297ee6b8</t>
+        </is>
+      </c>
+      <c r="B1069" t="n">
+        <v>32533570</v>
+      </c>
+      <c r="C1069" t="n">
+        <v>1</v>
+      </c>
+      <c r="D1069" t="n">
+        <v>3</v>
+      </c>
+      <c r="E1069" t="n">
+        <v>0</v>
+      </c>
+      <c r="F1069" t="inlineStr">
+        <is>
+          <t>2026-09-17</t>
+        </is>
+      </c>
+    </row>
+    <row r="1070">
+      <c r="A1070" t="inlineStr">
+        <is>
+          <t>5f47aeb6c387a50bca03dd55</t>
+        </is>
+      </c>
+      <c r="B1070" t="n">
+        <v>4856250</v>
+      </c>
+      <c r="C1070" t="n">
+        <v>0</v>
+      </c>
+      <c r="D1070" t="n">
+        <v>2</v>
+      </c>
+      <c r="E1070" t="n">
+        <v>0</v>
+      </c>
+      <c r="F1070" t="inlineStr">
+        <is>
+          <t>2026-09-17</t>
+        </is>
+      </c>
+    </row>
+    <row r="1071">
+      <c r="A1071" t="inlineStr">
+        <is>
+          <t>5f47ab5b9e2edb0bb831c703</t>
+        </is>
+      </c>
+      <c r="B1071" t="n">
+        <v>-2292712</v>
+      </c>
+      <c r="C1071" t="n">
+        <v>0</v>
+      </c>
+      <c r="D1071" t="n">
+        <v>1</v>
+      </c>
+      <c r="E1071" t="n">
+        <v>0</v>
+      </c>
+      <c r="F1071" t="inlineStr">
+        <is>
+          <t>2026-09-17</t>
+        </is>
+      </c>
+    </row>
+    <row r="1072">
+      <c r="A1072" t="inlineStr">
+        <is>
+          <t>5f452f5e66dd374930eb2b71</t>
+        </is>
+      </c>
+      <c r="B1072" t="n">
+        <v>36178989</v>
+      </c>
+      <c r="C1072" t="n">
+        <v>3</v>
+      </c>
+      <c r="D1072" t="n">
+        <v>4</v>
+      </c>
+      <c r="E1072" t="n">
+        <v>4</v>
+      </c>
+      <c r="F1072" t="inlineStr">
+        <is>
+          <t>2026-09-17</t>
+        </is>
+      </c>
+    </row>
+    <row r="1073">
+      <c r="A1073" t="inlineStr">
+        <is>
+          <t>5f4530beec331549297ee6d6</t>
+        </is>
+      </c>
+      <c r="B1073" t="n">
+        <v>21139300</v>
+      </c>
+      <c r="C1073" t="n">
+        <v>0</v>
+      </c>
+      <c r="D1073" t="n">
+        <v>3</v>
+      </c>
+      <c r="E1073" t="n">
+        <v>0</v>
+      </c>
+      <c r="F1073" t="inlineStr">
+        <is>
+          <t>2026-09-17</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/datos/hechos/td_admin.xlsx
+++ b/datos/hechos/td_admin.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F1073"/>
+  <dimension ref="A1:F1081"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -26188,6 +26188,198 @@
         </is>
       </c>
     </row>
+    <row r="1074">
+      <c r="A1074" t="inlineStr">
+        <is>
+          <t>5f45324dec331549297ee971</t>
+        </is>
+      </c>
+      <c r="B1074" t="n">
+        <v>13377218</v>
+      </c>
+      <c r="C1074" t="n">
+        <v>1</v>
+      </c>
+      <c r="D1074" t="n">
+        <v>2</v>
+      </c>
+      <c r="E1074" t="n">
+        <v>1</v>
+      </c>
+      <c r="F1074" t="inlineStr">
+        <is>
+          <t>2026-09-18</t>
+        </is>
+      </c>
+    </row>
+    <row r="1075">
+      <c r="A1075" t="inlineStr">
+        <is>
+          <t>62d5bd9ad8106d3355b5bdc1</t>
+        </is>
+      </c>
+      <c r="B1075" t="n">
+        <v>15452449</v>
+      </c>
+      <c r="C1075" t="n">
+        <v>1</v>
+      </c>
+      <c r="D1075" t="n">
+        <v>2</v>
+      </c>
+      <c r="E1075" t="n">
+        <v>1</v>
+      </c>
+      <c r="F1075" t="inlineStr">
+        <is>
+          <t>2026-09-18</t>
+        </is>
+      </c>
+    </row>
+    <row r="1076">
+      <c r="A1076" t="inlineStr">
+        <is>
+          <t>5f453062ec331549297ee6b8</t>
+        </is>
+      </c>
+      <c r="B1076" t="n">
+        <v>-15191937</v>
+      </c>
+      <c r="C1076" t="n">
+        <v>1</v>
+      </c>
+      <c r="D1076" t="n">
+        <v>3</v>
+      </c>
+      <c r="E1076" t="n">
+        <v>0</v>
+      </c>
+      <c r="F1076" t="inlineStr">
+        <is>
+          <t>2026-09-18</t>
+        </is>
+      </c>
+    </row>
+    <row r="1077">
+      <c r="A1077" t="inlineStr">
+        <is>
+          <t>5f4531e9764e7d491e029746</t>
+        </is>
+      </c>
+      <c r="B1077" t="n">
+        <v>6493503</v>
+      </c>
+      <c r="C1077" t="n">
+        <v>0</v>
+      </c>
+      <c r="D1077" t="n">
+        <v>0</v>
+      </c>
+      <c r="E1077" t="n">
+        <v>0</v>
+      </c>
+      <c r="F1077" t="inlineStr">
+        <is>
+          <t>2026-09-18</t>
+        </is>
+      </c>
+    </row>
+    <row r="1078">
+      <c r="A1078" t="inlineStr">
+        <is>
+          <t>5f47aeb6c387a50bca03dd55</t>
+        </is>
+      </c>
+      <c r="B1078" t="n">
+        <v>6323250</v>
+      </c>
+      <c r="C1078" t="n">
+        <v>0</v>
+      </c>
+      <c r="D1078" t="n">
+        <v>2</v>
+      </c>
+      <c r="E1078" t="n">
+        <v>0</v>
+      </c>
+      <c r="F1078" t="inlineStr">
+        <is>
+          <t>2026-09-18</t>
+        </is>
+      </c>
+    </row>
+    <row r="1079">
+      <c r="A1079" t="inlineStr">
+        <is>
+          <t>5f47ab5b9e2edb0bb831c703</t>
+        </is>
+      </c>
+      <c r="B1079" t="n">
+        <v>-1368712</v>
+      </c>
+      <c r="C1079" t="n">
+        <v>0</v>
+      </c>
+      <c r="D1079" t="n">
+        <v>1</v>
+      </c>
+      <c r="E1079" t="n">
+        <v>0</v>
+      </c>
+      <c r="F1079" t="inlineStr">
+        <is>
+          <t>2026-09-18</t>
+        </is>
+      </c>
+    </row>
+    <row r="1080">
+      <c r="A1080" t="inlineStr">
+        <is>
+          <t>5f452f5e66dd374930eb2b71</t>
+        </is>
+      </c>
+      <c r="B1080" t="n">
+        <v>41529931</v>
+      </c>
+      <c r="C1080" t="n">
+        <v>3</v>
+      </c>
+      <c r="D1080" t="n">
+        <v>4</v>
+      </c>
+      <c r="E1080" t="n">
+        <v>4</v>
+      </c>
+      <c r="F1080" t="inlineStr">
+        <is>
+          <t>2026-09-18</t>
+        </is>
+      </c>
+    </row>
+    <row r="1081">
+      <c r="A1081" t="inlineStr">
+        <is>
+          <t>5f4530beec331549297ee6d6</t>
+        </is>
+      </c>
+      <c r="B1081" t="n">
+        <v>19090120</v>
+      </c>
+      <c r="C1081" t="n">
+        <v>0</v>
+      </c>
+      <c r="D1081" t="n">
+        <v>3</v>
+      </c>
+      <c r="E1081" t="n">
+        <v>0</v>
+      </c>
+      <c r="F1081" t="inlineStr">
+        <is>
+          <t>2026-09-18</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/datos/hechos/td_admin.xlsx
+++ b/datos/hechos/td_admin.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F1081"/>
+  <dimension ref="A1:F1089"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -26380,6 +26380,198 @@
         </is>
       </c>
     </row>
+    <row r="1082">
+      <c r="A1082" t="inlineStr">
+        <is>
+          <t>5f45324dec331549297ee971</t>
+        </is>
+      </c>
+      <c r="B1082" t="n">
+        <v>13377218</v>
+      </c>
+      <c r="C1082" t="n">
+        <v>1</v>
+      </c>
+      <c r="D1082" t="n">
+        <v>2</v>
+      </c>
+      <c r="E1082" t="n">
+        <v>1</v>
+      </c>
+      <c r="F1082" t="inlineStr">
+        <is>
+          <t>2026-09-19</t>
+        </is>
+      </c>
+    </row>
+    <row r="1083">
+      <c r="A1083" t="inlineStr">
+        <is>
+          <t>62d5bd9ad8106d3355b5bdc1</t>
+        </is>
+      </c>
+      <c r="B1083" t="n">
+        <v>5552450</v>
+      </c>
+      <c r="C1083" t="n">
+        <v>1</v>
+      </c>
+      <c r="D1083" t="n">
+        <v>2</v>
+      </c>
+      <c r="E1083" t="n">
+        <v>1</v>
+      </c>
+      <c r="F1083" t="inlineStr">
+        <is>
+          <t>2026-09-19</t>
+        </is>
+      </c>
+    </row>
+    <row r="1084">
+      <c r="A1084" t="inlineStr">
+        <is>
+          <t>5f453062ec331549297ee6b8</t>
+        </is>
+      </c>
+      <c r="B1084" t="n">
+        <v>360</v>
+      </c>
+      <c r="C1084" t="n">
+        <v>1</v>
+      </c>
+      <c r="D1084" t="n">
+        <v>3</v>
+      </c>
+      <c r="E1084" t="n">
+        <v>0</v>
+      </c>
+      <c r="F1084" t="inlineStr">
+        <is>
+          <t>2026-09-19</t>
+        </is>
+      </c>
+    </row>
+    <row r="1085">
+      <c r="A1085" t="inlineStr">
+        <is>
+          <t>5f4531e9764e7d491e029746</t>
+        </is>
+      </c>
+      <c r="B1085" t="n">
+        <v>6493503</v>
+      </c>
+      <c r="C1085" t="n">
+        <v>0</v>
+      </c>
+      <c r="D1085" t="n">
+        <v>0</v>
+      </c>
+      <c r="E1085" t="n">
+        <v>0</v>
+      </c>
+      <c r="F1085" t="inlineStr">
+        <is>
+          <t>2026-09-19</t>
+        </is>
+      </c>
+    </row>
+    <row r="1086">
+      <c r="A1086" t="inlineStr">
+        <is>
+          <t>5f47aeb6c387a50bca03dd55</t>
+        </is>
+      </c>
+      <c r="B1086" t="n">
+        <v>6323250</v>
+      </c>
+      <c r="C1086" t="n">
+        <v>0</v>
+      </c>
+      <c r="D1086" t="n">
+        <v>2</v>
+      </c>
+      <c r="E1086" t="n">
+        <v>0</v>
+      </c>
+      <c r="F1086" t="inlineStr">
+        <is>
+          <t>2026-09-19</t>
+        </is>
+      </c>
+    </row>
+    <row r="1087">
+      <c r="A1087" t="inlineStr">
+        <is>
+          <t>5f47ab5b9e2edb0bb831c703</t>
+        </is>
+      </c>
+      <c r="B1087" t="n">
+        <v>11803221</v>
+      </c>
+      <c r="C1087" t="n">
+        <v>0</v>
+      </c>
+      <c r="D1087" t="n">
+        <v>1</v>
+      </c>
+      <c r="E1087" t="n">
+        <v>0</v>
+      </c>
+      <c r="F1087" t="inlineStr">
+        <is>
+          <t>2026-09-19</t>
+        </is>
+      </c>
+    </row>
+    <row r="1088">
+      <c r="A1088" t="inlineStr">
+        <is>
+          <t>5f452f5e66dd374930eb2b71</t>
+        </is>
+      </c>
+      <c r="B1088" t="n">
+        <v>40457666</v>
+      </c>
+      <c r="C1088" t="n">
+        <v>3</v>
+      </c>
+      <c r="D1088" t="n">
+        <v>4</v>
+      </c>
+      <c r="E1088" t="n">
+        <v>4</v>
+      </c>
+      <c r="F1088" t="inlineStr">
+        <is>
+          <t>2026-09-19</t>
+        </is>
+      </c>
+    </row>
+    <row r="1089">
+      <c r="A1089" t="inlineStr">
+        <is>
+          <t>5f4530beec331549297ee6d6</t>
+        </is>
+      </c>
+      <c r="B1089" t="n">
+        <v>89685572</v>
+      </c>
+      <c r="C1089" t="n">
+        <v>0</v>
+      </c>
+      <c r="D1089" t="n">
+        <v>3</v>
+      </c>
+      <c r="E1089" t="n">
+        <v>0</v>
+      </c>
+      <c r="F1089" t="inlineStr">
+        <is>
+          <t>2026-09-19</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/datos/hechos/td_admin.xlsx
+++ b/datos/hechos/td_admin.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F1089"/>
+  <dimension ref="A1:F1097"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -26572,6 +26572,198 @@
         </is>
       </c>
     </row>
+    <row r="1090">
+      <c r="A1090" t="inlineStr">
+        <is>
+          <t>5f45324dec331549297ee971</t>
+        </is>
+      </c>
+      <c r="B1090" t="n">
+        <v>-20616591</v>
+      </c>
+      <c r="C1090" t="n">
+        <v>1</v>
+      </c>
+      <c r="D1090" t="n">
+        <v>2</v>
+      </c>
+      <c r="E1090" t="n">
+        <v>1</v>
+      </c>
+      <c r="F1090" t="inlineStr">
+        <is>
+          <t>2026-09-20</t>
+        </is>
+      </c>
+    </row>
+    <row r="1091">
+      <c r="A1091" t="inlineStr">
+        <is>
+          <t>62d5bd9ad8106d3355b5bdc1</t>
+        </is>
+      </c>
+      <c r="B1091" t="n">
+        <v>22969556</v>
+      </c>
+      <c r="C1091" t="n">
+        <v>1</v>
+      </c>
+      <c r="D1091" t="n">
+        <v>2</v>
+      </c>
+      <c r="E1091" t="n">
+        <v>1</v>
+      </c>
+      <c r="F1091" t="inlineStr">
+        <is>
+          <t>2026-09-20</t>
+        </is>
+      </c>
+    </row>
+    <row r="1092">
+      <c r="A1092" t="inlineStr">
+        <is>
+          <t>5f453062ec331549297ee6b8</t>
+        </is>
+      </c>
+      <c r="B1092" t="n">
+        <v>360</v>
+      </c>
+      <c r="C1092" t="n">
+        <v>1</v>
+      </c>
+      <c r="D1092" t="n">
+        <v>3</v>
+      </c>
+      <c r="E1092" t="n">
+        <v>0</v>
+      </c>
+      <c r="F1092" t="inlineStr">
+        <is>
+          <t>2026-09-20</t>
+        </is>
+      </c>
+    </row>
+    <row r="1093">
+      <c r="A1093" t="inlineStr">
+        <is>
+          <t>5f4531e9764e7d491e029746</t>
+        </is>
+      </c>
+      <c r="B1093" t="n">
+        <v>6493503</v>
+      </c>
+      <c r="C1093" t="n">
+        <v>0</v>
+      </c>
+      <c r="D1093" t="n">
+        <v>0</v>
+      </c>
+      <c r="E1093" t="n">
+        <v>0</v>
+      </c>
+      <c r="F1093" t="inlineStr">
+        <is>
+          <t>2026-09-20</t>
+        </is>
+      </c>
+    </row>
+    <row r="1094">
+      <c r="A1094" t="inlineStr">
+        <is>
+          <t>5f47aeb6c387a50bca03dd55</t>
+        </is>
+      </c>
+      <c r="B1094" t="n">
+        <v>1873250</v>
+      </c>
+      <c r="C1094" t="n">
+        <v>0</v>
+      </c>
+      <c r="D1094" t="n">
+        <v>2</v>
+      </c>
+      <c r="E1094" t="n">
+        <v>0</v>
+      </c>
+      <c r="F1094" t="inlineStr">
+        <is>
+          <t>2026-09-20</t>
+        </is>
+      </c>
+    </row>
+    <row r="1095">
+      <c r="A1095" t="inlineStr">
+        <is>
+          <t>5f47ab5b9e2edb0bb831c703</t>
+        </is>
+      </c>
+      <c r="B1095" t="n">
+        <v>9302211</v>
+      </c>
+      <c r="C1095" t="n">
+        <v>0</v>
+      </c>
+      <c r="D1095" t="n">
+        <v>1</v>
+      </c>
+      <c r="E1095" t="n">
+        <v>0</v>
+      </c>
+      <c r="F1095" t="inlineStr">
+        <is>
+          <t>2026-09-20</t>
+        </is>
+      </c>
+    </row>
+    <row r="1096">
+      <c r="A1096" t="inlineStr">
+        <is>
+          <t>5f452f5e66dd374930eb2b71</t>
+        </is>
+      </c>
+      <c r="B1096" t="n">
+        <v>92259374</v>
+      </c>
+      <c r="C1096" t="n">
+        <v>3</v>
+      </c>
+      <c r="D1096" t="n">
+        <v>4</v>
+      </c>
+      <c r="E1096" t="n">
+        <v>4</v>
+      </c>
+      <c r="F1096" t="inlineStr">
+        <is>
+          <t>2026-09-20</t>
+        </is>
+      </c>
+    </row>
+    <row r="1097">
+      <c r="A1097" t="inlineStr">
+        <is>
+          <t>5f4530beec331549297ee6d6</t>
+        </is>
+      </c>
+      <c r="B1097" t="n">
+        <v>81181172</v>
+      </c>
+      <c r="C1097" t="n">
+        <v>0</v>
+      </c>
+      <c r="D1097" t="n">
+        <v>3</v>
+      </c>
+      <c r="E1097" t="n">
+        <v>0</v>
+      </c>
+      <c r="F1097" t="inlineStr">
+        <is>
+          <t>2026-09-20</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/datos/hechos/td_admin.xlsx
+++ b/datos/hechos/td_admin.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F1097"/>
+  <dimension ref="A1:F1105"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -26764,6 +26764,198 @@
         </is>
       </c>
     </row>
+    <row r="1098">
+      <c r="A1098" t="inlineStr">
+        <is>
+          <t>5f45324dec331549297ee971</t>
+        </is>
+      </c>
+      <c r="B1098" t="n">
+        <v>4773439</v>
+      </c>
+      <c r="C1098" t="n">
+        <v>1</v>
+      </c>
+      <c r="D1098" t="n">
+        <v>2</v>
+      </c>
+      <c r="E1098" t="n">
+        <v>1</v>
+      </c>
+      <c r="F1098" t="inlineStr">
+        <is>
+          <t>2026-09-21</t>
+        </is>
+      </c>
+    </row>
+    <row r="1099">
+      <c r="A1099" t="inlineStr">
+        <is>
+          <t>62d5bd9ad8106d3355b5bdc1</t>
+        </is>
+      </c>
+      <c r="B1099" t="n">
+        <v>39896557</v>
+      </c>
+      <c r="C1099" t="n">
+        <v>1</v>
+      </c>
+      <c r="D1099" t="n">
+        <v>2</v>
+      </c>
+      <c r="E1099" t="n">
+        <v>1</v>
+      </c>
+      <c r="F1099" t="inlineStr">
+        <is>
+          <t>2026-09-21</t>
+        </is>
+      </c>
+    </row>
+    <row r="1100">
+      <c r="A1100" t="inlineStr">
+        <is>
+          <t>5f453062ec331549297ee6b8</t>
+        </is>
+      </c>
+      <c r="B1100" t="n">
+        <v>10866060</v>
+      </c>
+      <c r="C1100" t="n">
+        <v>1</v>
+      </c>
+      <c r="D1100" t="n">
+        <v>3</v>
+      </c>
+      <c r="E1100" t="n">
+        <v>0</v>
+      </c>
+      <c r="F1100" t="inlineStr">
+        <is>
+          <t>2026-09-21</t>
+        </is>
+      </c>
+    </row>
+    <row r="1101">
+      <c r="A1101" t="inlineStr">
+        <is>
+          <t>5f4531e9764e7d491e029746</t>
+        </is>
+      </c>
+      <c r="B1101" t="n">
+        <v>5173503</v>
+      </c>
+      <c r="C1101" t="n">
+        <v>0</v>
+      </c>
+      <c r="D1101" t="n">
+        <v>0</v>
+      </c>
+      <c r="E1101" t="n">
+        <v>0</v>
+      </c>
+      <c r="F1101" t="inlineStr">
+        <is>
+          <t>2026-09-21</t>
+        </is>
+      </c>
+    </row>
+    <row r="1102">
+      <c r="A1102" t="inlineStr">
+        <is>
+          <t>5f47aeb6c387a50bca03dd55</t>
+        </is>
+      </c>
+      <c r="B1102" t="n">
+        <v>1873250</v>
+      </c>
+      <c r="C1102" t="n">
+        <v>0</v>
+      </c>
+      <c r="D1102" t="n">
+        <v>2</v>
+      </c>
+      <c r="E1102" t="n">
+        <v>0</v>
+      </c>
+      <c r="F1102" t="inlineStr">
+        <is>
+          <t>2026-09-21</t>
+        </is>
+      </c>
+    </row>
+    <row r="1103">
+      <c r="A1103" t="inlineStr">
+        <is>
+          <t>5f47ab5b9e2edb0bb831c703</t>
+        </is>
+      </c>
+      <c r="B1103" t="n">
+        <v>9302211</v>
+      </c>
+      <c r="C1103" t="n">
+        <v>0</v>
+      </c>
+      <c r="D1103" t="n">
+        <v>1</v>
+      </c>
+      <c r="E1103" t="n">
+        <v>0</v>
+      </c>
+      <c r="F1103" t="inlineStr">
+        <is>
+          <t>2026-09-21</t>
+        </is>
+      </c>
+    </row>
+    <row r="1104">
+      <c r="A1104" t="inlineStr">
+        <is>
+          <t>5f452f5e66dd374930eb2b71</t>
+        </is>
+      </c>
+      <c r="B1104" t="n">
+        <v>107475125</v>
+      </c>
+      <c r="C1104" t="n">
+        <v>3</v>
+      </c>
+      <c r="D1104" t="n">
+        <v>4</v>
+      </c>
+      <c r="E1104" t="n">
+        <v>4</v>
+      </c>
+      <c r="F1104" t="inlineStr">
+        <is>
+          <t>2026-09-21</t>
+        </is>
+      </c>
+    </row>
+    <row r="1105">
+      <c r="A1105" t="inlineStr">
+        <is>
+          <t>5f4530beec331549297ee6d6</t>
+        </is>
+      </c>
+      <c r="B1105" t="n">
+        <v>81181172</v>
+      </c>
+      <c r="C1105" t="n">
+        <v>0</v>
+      </c>
+      <c r="D1105" t="n">
+        <v>3</v>
+      </c>
+      <c r="E1105" t="n">
+        <v>0</v>
+      </c>
+      <c r="F1105" t="inlineStr">
+        <is>
+          <t>2026-09-21</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/datos/hechos/td_admin.xlsx
+++ b/datos/hechos/td_admin.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F1105"/>
+  <dimension ref="A1:F1113"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -26956,6 +26956,198 @@
         </is>
       </c>
     </row>
+    <row r="1106">
+      <c r="A1106" t="inlineStr">
+        <is>
+          <t>5f45324dec331549297ee971</t>
+        </is>
+      </c>
+      <c r="B1106" t="n">
+        <v>6765439</v>
+      </c>
+      <c r="C1106" t="n">
+        <v>1</v>
+      </c>
+      <c r="D1106" t="n">
+        <v>2</v>
+      </c>
+      <c r="E1106" t="n">
+        <v>1</v>
+      </c>
+      <c r="F1106" t="inlineStr">
+        <is>
+          <t>2026-09-22</t>
+        </is>
+      </c>
+    </row>
+    <row r="1107">
+      <c r="A1107" t="inlineStr">
+        <is>
+          <t>5f4531e9764e7d491e029746</t>
+        </is>
+      </c>
+      <c r="B1107" t="n">
+        <v>8304503</v>
+      </c>
+      <c r="C1107" t="n">
+        <v>0</v>
+      </c>
+      <c r="D1107" t="n">
+        <v>0</v>
+      </c>
+      <c r="E1107" t="n">
+        <v>0</v>
+      </c>
+      <c r="F1107" t="inlineStr">
+        <is>
+          <t>2026-09-22</t>
+        </is>
+      </c>
+    </row>
+    <row r="1108">
+      <c r="A1108" t="inlineStr">
+        <is>
+          <t>62d5bd9ad8106d3355b5bdc1</t>
+        </is>
+      </c>
+      <c r="B1108" t="n">
+        <v>52094934</v>
+      </c>
+      <c r="C1108" t="n">
+        <v>1</v>
+      </c>
+      <c r="D1108" t="n">
+        <v>2</v>
+      </c>
+      <c r="E1108" t="n">
+        <v>1</v>
+      </c>
+      <c r="F1108" t="inlineStr">
+        <is>
+          <t>2026-09-22</t>
+        </is>
+      </c>
+    </row>
+    <row r="1109">
+      <c r="A1109" t="inlineStr">
+        <is>
+          <t>5f453062ec331549297ee6b8</t>
+        </is>
+      </c>
+      <c r="B1109" t="n">
+        <v>35356519</v>
+      </c>
+      <c r="C1109" t="n">
+        <v>1</v>
+      </c>
+      <c r="D1109" t="n">
+        <v>3</v>
+      </c>
+      <c r="E1109" t="n">
+        <v>0</v>
+      </c>
+      <c r="F1109" t="inlineStr">
+        <is>
+          <t>2026-09-22</t>
+        </is>
+      </c>
+    </row>
+    <row r="1110">
+      <c r="A1110" t="inlineStr">
+        <is>
+          <t>5f47aeb6c387a50bca03dd55</t>
+        </is>
+      </c>
+      <c r="B1110" t="n">
+        <v>4249250</v>
+      </c>
+      <c r="C1110" t="n">
+        <v>0</v>
+      </c>
+      <c r="D1110" t="n">
+        <v>2</v>
+      </c>
+      <c r="E1110" t="n">
+        <v>0</v>
+      </c>
+      <c r="F1110" t="inlineStr">
+        <is>
+          <t>2026-09-22</t>
+        </is>
+      </c>
+    </row>
+    <row r="1111">
+      <c r="A1111" t="inlineStr">
+        <is>
+          <t>5f47ab5b9e2edb0bb831c703</t>
+        </is>
+      </c>
+      <c r="B1111" t="n">
+        <v>11899211</v>
+      </c>
+      <c r="C1111" t="n">
+        <v>0</v>
+      </c>
+      <c r="D1111" t="n">
+        <v>1</v>
+      </c>
+      <c r="E1111" t="n">
+        <v>0</v>
+      </c>
+      <c r="F1111" t="inlineStr">
+        <is>
+          <t>2026-09-22</t>
+        </is>
+      </c>
+    </row>
+    <row r="1112">
+      <c r="A1112" t="inlineStr">
+        <is>
+          <t>5f452f5e66dd374930eb2b71</t>
+        </is>
+      </c>
+      <c r="B1112" t="n">
+        <v>92675400</v>
+      </c>
+      <c r="C1112" t="n">
+        <v>3</v>
+      </c>
+      <c r="D1112" t="n">
+        <v>4</v>
+      </c>
+      <c r="E1112" t="n">
+        <v>4</v>
+      </c>
+      <c r="F1112" t="inlineStr">
+        <is>
+          <t>2026-09-22</t>
+        </is>
+      </c>
+    </row>
+    <row r="1113">
+      <c r="A1113" t="inlineStr">
+        <is>
+          <t>5f4530beec331549297ee6d6</t>
+        </is>
+      </c>
+      <c r="B1113" t="n">
+        <v>83035172</v>
+      </c>
+      <c r="C1113" t="n">
+        <v>0</v>
+      </c>
+      <c r="D1113" t="n">
+        <v>3</v>
+      </c>
+      <c r="E1113" t="n">
+        <v>0</v>
+      </c>
+      <c r="F1113" t="inlineStr">
+        <is>
+          <t>2026-09-22</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/datos/hechos/td_admin.xlsx
+++ b/datos/hechos/td_admin.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F1113"/>
+  <dimension ref="A1:F1121"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -27148,6 +27148,198 @@
         </is>
       </c>
     </row>
+    <row r="1114">
+      <c r="A1114" t="inlineStr">
+        <is>
+          <t>5f45324dec331549297ee971</t>
+        </is>
+      </c>
+      <c r="B1114" t="n">
+        <v>57228435</v>
+      </c>
+      <c r="C1114" t="n">
+        <v>1</v>
+      </c>
+      <c r="D1114" t="n">
+        <v>2</v>
+      </c>
+      <c r="E1114" t="n">
+        <v>1</v>
+      </c>
+      <c r="F1114" t="inlineStr">
+        <is>
+          <t>2026-09-23</t>
+        </is>
+      </c>
+    </row>
+    <row r="1115">
+      <c r="A1115" t="inlineStr">
+        <is>
+          <t>5f4531e9764e7d491e029746</t>
+        </is>
+      </c>
+      <c r="B1115" t="n">
+        <v>21200650</v>
+      </c>
+      <c r="C1115" t="n">
+        <v>0</v>
+      </c>
+      <c r="D1115" t="n">
+        <v>0</v>
+      </c>
+      <c r="E1115" t="n">
+        <v>0</v>
+      </c>
+      <c r="F1115" t="inlineStr">
+        <is>
+          <t>2026-09-23</t>
+        </is>
+      </c>
+    </row>
+    <row r="1116">
+      <c r="A1116" t="inlineStr">
+        <is>
+          <t>62d5bd9ad8106d3355b5bdc1</t>
+        </is>
+      </c>
+      <c r="B1116" t="n">
+        <v>44532380</v>
+      </c>
+      <c r="C1116" t="n">
+        <v>1</v>
+      </c>
+      <c r="D1116" t="n">
+        <v>2</v>
+      </c>
+      <c r="E1116" t="n">
+        <v>1</v>
+      </c>
+      <c r="F1116" t="inlineStr">
+        <is>
+          <t>2026-09-23</t>
+        </is>
+      </c>
+    </row>
+    <row r="1117">
+      <c r="A1117" t="inlineStr">
+        <is>
+          <t>5f453062ec331549297ee6b8</t>
+        </is>
+      </c>
+      <c r="B1117" t="n">
+        <v>-5705973</v>
+      </c>
+      <c r="C1117" t="n">
+        <v>1</v>
+      </c>
+      <c r="D1117" t="n">
+        <v>3</v>
+      </c>
+      <c r="E1117" t="n">
+        <v>0</v>
+      </c>
+      <c r="F1117" t="inlineStr">
+        <is>
+          <t>2026-09-23</t>
+        </is>
+      </c>
+    </row>
+    <row r="1118">
+      <c r="A1118" t="inlineStr">
+        <is>
+          <t>5f47aeb6c387a50bca03dd55</t>
+        </is>
+      </c>
+      <c r="B1118" t="n">
+        <v>-14088812</v>
+      </c>
+      <c r="C1118" t="n">
+        <v>0</v>
+      </c>
+      <c r="D1118" t="n">
+        <v>2</v>
+      </c>
+      <c r="E1118" t="n">
+        <v>0</v>
+      </c>
+      <c r="F1118" t="inlineStr">
+        <is>
+          <t>2026-09-23</t>
+        </is>
+      </c>
+    </row>
+    <row r="1119">
+      <c r="A1119" t="inlineStr">
+        <is>
+          <t>5f47ab5b9e2edb0bb831c703</t>
+        </is>
+      </c>
+      <c r="B1119" t="n">
+        <v>-6789898</v>
+      </c>
+      <c r="C1119" t="n">
+        <v>0</v>
+      </c>
+      <c r="D1119" t="n">
+        <v>1</v>
+      </c>
+      <c r="E1119" t="n">
+        <v>0</v>
+      </c>
+      <c r="F1119" t="inlineStr">
+        <is>
+          <t>2026-09-23</t>
+        </is>
+      </c>
+    </row>
+    <row r="1120">
+      <c r="A1120" t="inlineStr">
+        <is>
+          <t>5f452f5e66dd374930eb2b71</t>
+        </is>
+      </c>
+      <c r="B1120" t="n">
+        <v>92675400</v>
+      </c>
+      <c r="C1120" t="n">
+        <v>3</v>
+      </c>
+      <c r="D1120" t="n">
+        <v>4</v>
+      </c>
+      <c r="E1120" t="n">
+        <v>4</v>
+      </c>
+      <c r="F1120" t="inlineStr">
+        <is>
+          <t>2026-09-23</t>
+        </is>
+      </c>
+    </row>
+    <row r="1121">
+      <c r="A1121" t="inlineStr">
+        <is>
+          <t>5f4530beec331549297ee6d6</t>
+        </is>
+      </c>
+      <c r="B1121" t="n">
+        <v>93055574</v>
+      </c>
+      <c r="C1121" t="n">
+        <v>0</v>
+      </c>
+      <c r="D1121" t="n">
+        <v>3</v>
+      </c>
+      <c r="E1121" t="n">
+        <v>0</v>
+      </c>
+      <c r="F1121" t="inlineStr">
+        <is>
+          <t>2026-09-23</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/datos/hechos/td_admin.xlsx
+++ b/datos/hechos/td_admin.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F1121"/>
+  <dimension ref="A1:F1129"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -27340,6 +27340,198 @@
         </is>
       </c>
     </row>
+    <row r="1122">
+      <c r="A1122" t="inlineStr">
+        <is>
+          <t>5f45324dec331549297ee971</t>
+        </is>
+      </c>
+      <c r="B1122" t="n">
+        <v>57228435</v>
+      </c>
+      <c r="C1122" t="n">
+        <v>1</v>
+      </c>
+      <c r="D1122" t="n">
+        <v>2</v>
+      </c>
+      <c r="E1122" t="n">
+        <v>1</v>
+      </c>
+      <c r="F1122" t="inlineStr">
+        <is>
+          <t>2026-09-24</t>
+        </is>
+      </c>
+    </row>
+    <row r="1123">
+      <c r="A1123" t="inlineStr">
+        <is>
+          <t>5f4531e9764e7d491e029746</t>
+        </is>
+      </c>
+      <c r="B1123" t="n">
+        <v>10651076</v>
+      </c>
+      <c r="C1123" t="n">
+        <v>0</v>
+      </c>
+      <c r="D1123" t="n">
+        <v>0</v>
+      </c>
+      <c r="E1123" t="n">
+        <v>0</v>
+      </c>
+      <c r="F1123" t="inlineStr">
+        <is>
+          <t>2026-09-24</t>
+        </is>
+      </c>
+    </row>
+    <row r="1124">
+      <c r="A1124" t="inlineStr">
+        <is>
+          <t>62d5bd9ad8106d3355b5bdc1</t>
+        </is>
+      </c>
+      <c r="B1124" t="n">
+        <v>23457010</v>
+      </c>
+      <c r="C1124" t="n">
+        <v>1</v>
+      </c>
+      <c r="D1124" t="n">
+        <v>2</v>
+      </c>
+      <c r="E1124" t="n">
+        <v>1</v>
+      </c>
+      <c r="F1124" t="inlineStr">
+        <is>
+          <t>2026-09-24</t>
+        </is>
+      </c>
+    </row>
+    <row r="1125">
+      <c r="A1125" t="inlineStr">
+        <is>
+          <t>5f453062ec331549297ee6b8</t>
+        </is>
+      </c>
+      <c r="B1125" t="n">
+        <v>12947360</v>
+      </c>
+      <c r="C1125" t="n">
+        <v>1</v>
+      </c>
+      <c r="D1125" t="n">
+        <v>3</v>
+      </c>
+      <c r="E1125" t="n">
+        <v>0</v>
+      </c>
+      <c r="F1125" t="inlineStr">
+        <is>
+          <t>2026-09-24</t>
+        </is>
+      </c>
+    </row>
+    <row r="1126">
+      <c r="A1126" t="inlineStr">
+        <is>
+          <t>5f47aeb6c387a50bca03dd55</t>
+        </is>
+      </c>
+      <c r="B1126" t="n">
+        <v>-4680266</v>
+      </c>
+      <c r="C1126" t="n">
+        <v>0</v>
+      </c>
+      <c r="D1126" t="n">
+        <v>2</v>
+      </c>
+      <c r="E1126" t="n">
+        <v>0</v>
+      </c>
+      <c r="F1126" t="inlineStr">
+        <is>
+          <t>2026-09-24</t>
+        </is>
+      </c>
+    </row>
+    <row r="1127">
+      <c r="A1127" t="inlineStr">
+        <is>
+          <t>5f47ab5b9e2edb0bb831c703</t>
+        </is>
+      </c>
+      <c r="B1127" t="n">
+        <v>5251804</v>
+      </c>
+      <c r="C1127" t="n">
+        <v>0</v>
+      </c>
+      <c r="D1127" t="n">
+        <v>1</v>
+      </c>
+      <c r="E1127" t="n">
+        <v>0</v>
+      </c>
+      <c r="F1127" t="inlineStr">
+        <is>
+          <t>2026-09-24</t>
+        </is>
+      </c>
+    </row>
+    <row r="1128">
+      <c r="A1128" t="inlineStr">
+        <is>
+          <t>5f452f5e66dd374930eb2b71</t>
+        </is>
+      </c>
+      <c r="B1128" t="n">
+        <v>79088648</v>
+      </c>
+      <c r="C1128" t="n">
+        <v>3</v>
+      </c>
+      <c r="D1128" t="n">
+        <v>4</v>
+      </c>
+      <c r="E1128" t="n">
+        <v>4</v>
+      </c>
+      <c r="F1128" t="inlineStr">
+        <is>
+          <t>2026-09-24</t>
+        </is>
+      </c>
+    </row>
+    <row r="1129">
+      <c r="A1129" t="inlineStr">
+        <is>
+          <t>5f4530beec331549297ee6d6</t>
+        </is>
+      </c>
+      <c r="B1129" t="n">
+        <v>83955239</v>
+      </c>
+      <c r="C1129" t="n">
+        <v>0</v>
+      </c>
+      <c r="D1129" t="n">
+        <v>3</v>
+      </c>
+      <c r="E1129" t="n">
+        <v>0</v>
+      </c>
+      <c r="F1129" t="inlineStr">
+        <is>
+          <t>2026-09-24</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/datos/hechos/td_admin.xlsx
+++ b/datos/hechos/td_admin.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F1129"/>
+  <dimension ref="A1:F1137"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -27532,6 +27532,198 @@
         </is>
       </c>
     </row>
+    <row r="1130">
+      <c r="A1130" t="inlineStr">
+        <is>
+          <t>5f45324dec331549297ee971</t>
+        </is>
+      </c>
+      <c r="B1130" t="n">
+        <v>36059729</v>
+      </c>
+      <c r="C1130" t="n">
+        <v>1</v>
+      </c>
+      <c r="D1130" t="n">
+        <v>2</v>
+      </c>
+      <c r="E1130" t="n">
+        <v>1</v>
+      </c>
+      <c r="F1130" t="inlineStr">
+        <is>
+          <t>2026-09-25</t>
+        </is>
+      </c>
+    </row>
+    <row r="1131">
+      <c r="A1131" t="inlineStr">
+        <is>
+          <t>5f4531e9764e7d491e029746</t>
+        </is>
+      </c>
+      <c r="B1131" t="n">
+        <v>10651076</v>
+      </c>
+      <c r="C1131" t="n">
+        <v>0</v>
+      </c>
+      <c r="D1131" t="n">
+        <v>0</v>
+      </c>
+      <c r="E1131" t="n">
+        <v>0</v>
+      </c>
+      <c r="F1131" t="inlineStr">
+        <is>
+          <t>2026-09-25</t>
+        </is>
+      </c>
+    </row>
+    <row r="1132">
+      <c r="A1132" t="inlineStr">
+        <is>
+          <t>62d5bd9ad8106d3355b5bdc1</t>
+        </is>
+      </c>
+      <c r="B1132" t="n">
+        <v>27556497</v>
+      </c>
+      <c r="C1132" t="n">
+        <v>1</v>
+      </c>
+      <c r="D1132" t="n">
+        <v>2</v>
+      </c>
+      <c r="E1132" t="n">
+        <v>1</v>
+      </c>
+      <c r="F1132" t="inlineStr">
+        <is>
+          <t>2026-09-25</t>
+        </is>
+      </c>
+    </row>
+    <row r="1133">
+      <c r="A1133" t="inlineStr">
+        <is>
+          <t>5f453062ec331549297ee6b8</t>
+        </is>
+      </c>
+      <c r="B1133" t="n">
+        <v>14060304</v>
+      </c>
+      <c r="C1133" t="n">
+        <v>1</v>
+      </c>
+      <c r="D1133" t="n">
+        <v>3</v>
+      </c>
+      <c r="E1133" t="n">
+        <v>0</v>
+      </c>
+      <c r="F1133" t="inlineStr">
+        <is>
+          <t>2026-09-25</t>
+        </is>
+      </c>
+    </row>
+    <row r="1134">
+      <c r="A1134" t="inlineStr">
+        <is>
+          <t>5f47aeb6c387a50bca03dd55</t>
+        </is>
+      </c>
+      <c r="B1134" t="n">
+        <v>-4680266</v>
+      </c>
+      <c r="C1134" t="n">
+        <v>0</v>
+      </c>
+      <c r="D1134" t="n">
+        <v>2</v>
+      </c>
+      <c r="E1134" t="n">
+        <v>0</v>
+      </c>
+      <c r="F1134" t="inlineStr">
+        <is>
+          <t>2026-09-25</t>
+        </is>
+      </c>
+    </row>
+    <row r="1135">
+      <c r="A1135" t="inlineStr">
+        <is>
+          <t>5f47ab5b9e2edb0bb831c703</t>
+        </is>
+      </c>
+      <c r="B1135" t="n">
+        <v>5251804</v>
+      </c>
+      <c r="C1135" t="n">
+        <v>0</v>
+      </c>
+      <c r="D1135" t="n">
+        <v>1</v>
+      </c>
+      <c r="E1135" t="n">
+        <v>0</v>
+      </c>
+      <c r="F1135" t="inlineStr">
+        <is>
+          <t>2026-09-25</t>
+        </is>
+      </c>
+    </row>
+    <row r="1136">
+      <c r="A1136" t="inlineStr">
+        <is>
+          <t>5f452f5e66dd374930eb2b71</t>
+        </is>
+      </c>
+      <c r="B1136" t="n">
+        <v>79088648</v>
+      </c>
+      <c r="C1136" t="n">
+        <v>3</v>
+      </c>
+      <c r="D1136" t="n">
+        <v>4</v>
+      </c>
+      <c r="E1136" t="n">
+        <v>4</v>
+      </c>
+      <c r="F1136" t="inlineStr">
+        <is>
+          <t>2026-09-25</t>
+        </is>
+      </c>
+    </row>
+    <row r="1137">
+      <c r="A1137" t="inlineStr">
+        <is>
+          <t>5f4530beec331549297ee6d6</t>
+        </is>
+      </c>
+      <c r="B1137" t="n">
+        <v>101024458</v>
+      </c>
+      <c r="C1137" t="n">
+        <v>0</v>
+      </c>
+      <c r="D1137" t="n">
+        <v>3</v>
+      </c>
+      <c r="E1137" t="n">
+        <v>0</v>
+      </c>
+      <c r="F1137" t="inlineStr">
+        <is>
+          <t>2026-09-25</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/datos/hechos/td_admin.xlsx
+++ b/datos/hechos/td_admin.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F1137"/>
+  <dimension ref="A1:F1145"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -27724,6 +27724,198 @@
         </is>
       </c>
     </row>
+    <row r="1138">
+      <c r="A1138" t="inlineStr">
+        <is>
+          <t>5f45324dec331549297ee971</t>
+        </is>
+      </c>
+      <c r="B1138" t="n">
+        <v>-3940271</v>
+      </c>
+      <c r="C1138" t="n">
+        <v>1</v>
+      </c>
+      <c r="D1138" t="n">
+        <v>2</v>
+      </c>
+      <c r="E1138" t="n">
+        <v>1</v>
+      </c>
+      <c r="F1138" t="inlineStr">
+        <is>
+          <t>2026-09-26</t>
+        </is>
+      </c>
+    </row>
+    <row r="1139">
+      <c r="A1139" t="inlineStr">
+        <is>
+          <t>5f4531e9764e7d491e029746</t>
+        </is>
+      </c>
+      <c r="B1139" t="n">
+        <v>10651076</v>
+      </c>
+      <c r="C1139" t="n">
+        <v>0</v>
+      </c>
+      <c r="D1139" t="n">
+        <v>0</v>
+      </c>
+      <c r="E1139" t="n">
+        <v>0</v>
+      </c>
+      <c r="F1139" t="inlineStr">
+        <is>
+          <t>2026-09-26</t>
+        </is>
+      </c>
+    </row>
+    <row r="1140">
+      <c r="A1140" t="inlineStr">
+        <is>
+          <t>62d5bd9ad8106d3355b5bdc1</t>
+        </is>
+      </c>
+      <c r="B1140" t="n">
+        <v>42586947</v>
+      </c>
+      <c r="C1140" t="n">
+        <v>1</v>
+      </c>
+      <c r="D1140" t="n">
+        <v>2</v>
+      </c>
+      <c r="E1140" t="n">
+        <v>1</v>
+      </c>
+      <c r="F1140" t="inlineStr">
+        <is>
+          <t>2026-09-26</t>
+        </is>
+      </c>
+    </row>
+    <row r="1141">
+      <c r="A1141" t="inlineStr">
+        <is>
+          <t>5f453062ec331549297ee6b8</t>
+        </is>
+      </c>
+      <c r="B1141" t="n">
+        <v>-1939696</v>
+      </c>
+      <c r="C1141" t="n">
+        <v>1</v>
+      </c>
+      <c r="D1141" t="n">
+        <v>3</v>
+      </c>
+      <c r="E1141" t="n">
+        <v>0</v>
+      </c>
+      <c r="F1141" t="inlineStr">
+        <is>
+          <t>2026-09-26</t>
+        </is>
+      </c>
+    </row>
+    <row r="1142">
+      <c r="A1142" t="inlineStr">
+        <is>
+          <t>5f47aeb6c387a50bca03dd55</t>
+        </is>
+      </c>
+      <c r="B1142" t="n">
+        <v>-6283266</v>
+      </c>
+      <c r="C1142" t="n">
+        <v>0</v>
+      </c>
+      <c r="D1142" t="n">
+        <v>2</v>
+      </c>
+      <c r="E1142" t="n">
+        <v>0</v>
+      </c>
+      <c r="F1142" t="inlineStr">
+        <is>
+          <t>2026-09-26</t>
+        </is>
+      </c>
+    </row>
+    <row r="1143">
+      <c r="A1143" t="inlineStr">
+        <is>
+          <t>5f47ab5b9e2edb0bb831c703</t>
+        </is>
+      </c>
+      <c r="B1143" t="n">
+        <v>5251804</v>
+      </c>
+      <c r="C1143" t="n">
+        <v>0</v>
+      </c>
+      <c r="D1143" t="n">
+        <v>1</v>
+      </c>
+      <c r="E1143" t="n">
+        <v>0</v>
+      </c>
+      <c r="F1143" t="inlineStr">
+        <is>
+          <t>2026-09-26</t>
+        </is>
+      </c>
+    </row>
+    <row r="1144">
+      <c r="A1144" t="inlineStr">
+        <is>
+          <t>5f452f5e66dd374930eb2b71</t>
+        </is>
+      </c>
+      <c r="B1144" t="n">
+        <v>65924639</v>
+      </c>
+      <c r="C1144" t="n">
+        <v>3</v>
+      </c>
+      <c r="D1144" t="n">
+        <v>4</v>
+      </c>
+      <c r="E1144" t="n">
+        <v>4</v>
+      </c>
+      <c r="F1144" t="inlineStr">
+        <is>
+          <t>2026-09-26</t>
+        </is>
+      </c>
+    </row>
+    <row r="1145">
+      <c r="A1145" t="inlineStr">
+        <is>
+          <t>5f4530beec331549297ee6d6</t>
+        </is>
+      </c>
+      <c r="B1145" t="n">
+        <v>101024458</v>
+      </c>
+      <c r="C1145" t="n">
+        <v>0</v>
+      </c>
+      <c r="D1145" t="n">
+        <v>3</v>
+      </c>
+      <c r="E1145" t="n">
+        <v>0</v>
+      </c>
+      <c r="F1145" t="inlineStr">
+        <is>
+          <t>2026-09-26</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/datos/hechos/td_admin.xlsx
+++ b/datos/hechos/td_admin.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F1145"/>
+  <dimension ref="A1:F1153"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -27916,6 +27916,198 @@
         </is>
       </c>
     </row>
+    <row r="1146">
+      <c r="A1146" t="inlineStr">
+        <is>
+          <t>5f45324dec331549297ee971</t>
+        </is>
+      </c>
+      <c r="B1146" t="n">
+        <v>14997447</v>
+      </c>
+      <c r="C1146" t="n">
+        <v>1</v>
+      </c>
+      <c r="D1146" t="n">
+        <v>2</v>
+      </c>
+      <c r="E1146" t="n">
+        <v>1</v>
+      </c>
+      <c r="F1146" t="inlineStr">
+        <is>
+          <t>2026-09-27</t>
+        </is>
+      </c>
+    </row>
+    <row r="1147">
+      <c r="A1147" t="inlineStr">
+        <is>
+          <t>5f4531e9764e7d491e029746</t>
+        </is>
+      </c>
+      <c r="B1147" t="n">
+        <v>10651076</v>
+      </c>
+      <c r="C1147" t="n">
+        <v>0</v>
+      </c>
+      <c r="D1147" t="n">
+        <v>0</v>
+      </c>
+      <c r="E1147" t="n">
+        <v>0</v>
+      </c>
+      <c r="F1147" t="inlineStr">
+        <is>
+          <t>2026-09-27</t>
+        </is>
+      </c>
+    </row>
+    <row r="1148">
+      <c r="A1148" t="inlineStr">
+        <is>
+          <t>62d5bd9ad8106d3355b5bdc1</t>
+        </is>
+      </c>
+      <c r="B1148" t="n">
+        <v>42586947</v>
+      </c>
+      <c r="C1148" t="n">
+        <v>1</v>
+      </c>
+      <c r="D1148" t="n">
+        <v>2</v>
+      </c>
+      <c r="E1148" t="n">
+        <v>1</v>
+      </c>
+      <c r="F1148" t="inlineStr">
+        <is>
+          <t>2026-09-27</t>
+        </is>
+      </c>
+    </row>
+    <row r="1149">
+      <c r="A1149" t="inlineStr">
+        <is>
+          <t>5f453062ec331549297ee6b8</t>
+        </is>
+      </c>
+      <c r="B1149" t="n">
+        <v>17830994</v>
+      </c>
+      <c r="C1149" t="n">
+        <v>1</v>
+      </c>
+      <c r="D1149" t="n">
+        <v>3</v>
+      </c>
+      <c r="E1149" t="n">
+        <v>0</v>
+      </c>
+      <c r="F1149" t="inlineStr">
+        <is>
+          <t>2026-09-27</t>
+        </is>
+      </c>
+    </row>
+    <row r="1150">
+      <c r="A1150" t="inlineStr">
+        <is>
+          <t>5f47aeb6c387a50bca03dd55</t>
+        </is>
+      </c>
+      <c r="B1150" t="n">
+        <v>-18826093</v>
+      </c>
+      <c r="C1150" t="n">
+        <v>0</v>
+      </c>
+      <c r="D1150" t="n">
+        <v>2</v>
+      </c>
+      <c r="E1150" t="n">
+        <v>0</v>
+      </c>
+      <c r="F1150" t="inlineStr">
+        <is>
+          <t>2026-09-27</t>
+        </is>
+      </c>
+    </row>
+    <row r="1151">
+      <c r="A1151" t="inlineStr">
+        <is>
+          <t>5f47ab5b9e2edb0bb831c703</t>
+        </is>
+      </c>
+      <c r="B1151" t="n">
+        <v>11641524</v>
+      </c>
+      <c r="C1151" t="n">
+        <v>0</v>
+      </c>
+      <c r="D1151" t="n">
+        <v>1</v>
+      </c>
+      <c r="E1151" t="n">
+        <v>0</v>
+      </c>
+      <c r="F1151" t="inlineStr">
+        <is>
+          <t>2026-09-27</t>
+        </is>
+      </c>
+    </row>
+    <row r="1152">
+      <c r="A1152" t="inlineStr">
+        <is>
+          <t>5f452f5e66dd374930eb2b71</t>
+        </is>
+      </c>
+      <c r="B1152" t="n">
+        <v>-3097178</v>
+      </c>
+      <c r="C1152" t="n">
+        <v>3</v>
+      </c>
+      <c r="D1152" t="n">
+        <v>4</v>
+      </c>
+      <c r="E1152" t="n">
+        <v>4</v>
+      </c>
+      <c r="F1152" t="inlineStr">
+        <is>
+          <t>2026-09-27</t>
+        </is>
+      </c>
+    </row>
+    <row r="1153">
+      <c r="A1153" t="inlineStr">
+        <is>
+          <t>5f4530beec331549297ee6d6</t>
+        </is>
+      </c>
+      <c r="B1153" t="n">
+        <v>101024458</v>
+      </c>
+      <c r="C1153" t="n">
+        <v>0</v>
+      </c>
+      <c r="D1153" t="n">
+        <v>3</v>
+      </c>
+      <c r="E1153" t="n">
+        <v>0</v>
+      </c>
+      <c r="F1153" t="inlineStr">
+        <is>
+          <t>2026-09-27</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/datos/hechos/td_admin.xlsx
+++ b/datos/hechos/td_admin.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F1153"/>
+  <dimension ref="A1:F1161"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -28108,6 +28108,198 @@
         </is>
       </c>
     </row>
+    <row r="1154">
+      <c r="A1154" t="inlineStr">
+        <is>
+          <t>5f45324dec331549297ee971</t>
+        </is>
+      </c>
+      <c r="B1154" t="n">
+        <v>6297447</v>
+      </c>
+      <c r="C1154" t="n">
+        <v>1</v>
+      </c>
+      <c r="D1154" t="n">
+        <v>2</v>
+      </c>
+      <c r="E1154" t="n">
+        <v>1</v>
+      </c>
+      <c r="F1154" t="inlineStr">
+        <is>
+          <t>2026-09-28</t>
+        </is>
+      </c>
+    </row>
+    <row r="1155">
+      <c r="A1155" t="inlineStr">
+        <is>
+          <t>5f4531e9764e7d491e029746</t>
+        </is>
+      </c>
+      <c r="B1155" t="n">
+        <v>10651076</v>
+      </c>
+      <c r="C1155" t="n">
+        <v>0</v>
+      </c>
+      <c r="D1155" t="n">
+        <v>0</v>
+      </c>
+      <c r="E1155" t="n">
+        <v>0</v>
+      </c>
+      <c r="F1155" t="inlineStr">
+        <is>
+          <t>2026-09-28</t>
+        </is>
+      </c>
+    </row>
+    <row r="1156">
+      <c r="A1156" t="inlineStr">
+        <is>
+          <t>62d5bd9ad8106d3355b5bdc1</t>
+        </is>
+      </c>
+      <c r="B1156" t="n">
+        <v>-4214142</v>
+      </c>
+      <c r="C1156" t="n">
+        <v>1</v>
+      </c>
+      <c r="D1156" t="n">
+        <v>2</v>
+      </c>
+      <c r="E1156" t="n">
+        <v>1</v>
+      </c>
+      <c r="F1156" t="inlineStr">
+        <is>
+          <t>2026-09-28</t>
+        </is>
+      </c>
+    </row>
+    <row r="1157">
+      <c r="A1157" t="inlineStr">
+        <is>
+          <t>5f453062ec331549297ee6b8</t>
+        </is>
+      </c>
+      <c r="B1157" t="n">
+        <v>43432084</v>
+      </c>
+      <c r="C1157" t="n">
+        <v>1</v>
+      </c>
+      <c r="D1157" t="n">
+        <v>3</v>
+      </c>
+      <c r="E1157" t="n">
+        <v>0</v>
+      </c>
+      <c r="F1157" t="inlineStr">
+        <is>
+          <t>2026-09-28</t>
+        </is>
+      </c>
+    </row>
+    <row r="1158">
+      <c r="A1158" t="inlineStr">
+        <is>
+          <t>5f47aeb6c387a50bca03dd55</t>
+        </is>
+      </c>
+      <c r="B1158" t="n">
+        <v>-18826093</v>
+      </c>
+      <c r="C1158" t="n">
+        <v>0</v>
+      </c>
+      <c r="D1158" t="n">
+        <v>2</v>
+      </c>
+      <c r="E1158" t="n">
+        <v>0</v>
+      </c>
+      <c r="F1158" t="inlineStr">
+        <is>
+          <t>2026-09-28</t>
+        </is>
+      </c>
+    </row>
+    <row r="1159">
+      <c r="A1159" t="inlineStr">
+        <is>
+          <t>5f47ab5b9e2edb0bb831c703</t>
+        </is>
+      </c>
+      <c r="B1159" t="n">
+        <v>11641524</v>
+      </c>
+      <c r="C1159" t="n">
+        <v>0</v>
+      </c>
+      <c r="D1159" t="n">
+        <v>1</v>
+      </c>
+      <c r="E1159" t="n">
+        <v>0</v>
+      </c>
+      <c r="F1159" t="inlineStr">
+        <is>
+          <t>2026-09-28</t>
+        </is>
+      </c>
+    </row>
+    <row r="1160">
+      <c r="A1160" t="inlineStr">
+        <is>
+          <t>5f452f5e66dd374930eb2b71</t>
+        </is>
+      </c>
+      <c r="B1160" t="n">
+        <v>-3097178</v>
+      </c>
+      <c r="C1160" t="n">
+        <v>3</v>
+      </c>
+      <c r="D1160" t="n">
+        <v>4</v>
+      </c>
+      <c r="E1160" t="n">
+        <v>4</v>
+      </c>
+      <c r="F1160" t="inlineStr">
+        <is>
+          <t>2026-09-28</t>
+        </is>
+      </c>
+    </row>
+    <row r="1161">
+      <c r="A1161" t="inlineStr">
+        <is>
+          <t>5f4530beec331549297ee6d6</t>
+        </is>
+      </c>
+      <c r="B1161" t="n">
+        <v>101024458</v>
+      </c>
+      <c r="C1161" t="n">
+        <v>0</v>
+      </c>
+      <c r="D1161" t="n">
+        <v>3</v>
+      </c>
+      <c r="E1161" t="n">
+        <v>0</v>
+      </c>
+      <c r="F1161" t="inlineStr">
+        <is>
+          <t>2026-09-28</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/datos/hechos/td_admin.xlsx
+++ b/datos/hechos/td_admin.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F1161"/>
+  <dimension ref="A1:F1169"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -28300,6 +28300,198 @@
         </is>
       </c>
     </row>
+    <row r="1162">
+      <c r="A1162" t="inlineStr">
+        <is>
+          <t>5f45324dec331549297ee971</t>
+        </is>
+      </c>
+      <c r="B1162" t="n">
+        <v>6297447</v>
+      </c>
+      <c r="C1162" t="n">
+        <v>1</v>
+      </c>
+      <c r="D1162" t="n">
+        <v>2</v>
+      </c>
+      <c r="E1162" t="n">
+        <v>1</v>
+      </c>
+      <c r="F1162" t="inlineStr">
+        <is>
+          <t>2026-09-29</t>
+        </is>
+      </c>
+    </row>
+    <row r="1163">
+      <c r="A1163" t="inlineStr">
+        <is>
+          <t>5f4531e9764e7d491e029746</t>
+        </is>
+      </c>
+      <c r="B1163" t="n">
+        <v>10651076</v>
+      </c>
+      <c r="C1163" t="n">
+        <v>0</v>
+      </c>
+      <c r="D1163" t="n">
+        <v>0</v>
+      </c>
+      <c r="E1163" t="n">
+        <v>0</v>
+      </c>
+      <c r="F1163" t="inlineStr">
+        <is>
+          <t>2026-09-29</t>
+        </is>
+      </c>
+    </row>
+    <row r="1164">
+      <c r="A1164" t="inlineStr">
+        <is>
+          <t>62d5bd9ad8106d3355b5bdc1</t>
+        </is>
+      </c>
+      <c r="B1164" t="n">
+        <v>-4214142</v>
+      </c>
+      <c r="C1164" t="n">
+        <v>1</v>
+      </c>
+      <c r="D1164" t="n">
+        <v>2</v>
+      </c>
+      <c r="E1164" t="n">
+        <v>1</v>
+      </c>
+      <c r="F1164" t="inlineStr">
+        <is>
+          <t>2026-09-29</t>
+        </is>
+      </c>
+    </row>
+    <row r="1165">
+      <c r="A1165" t="inlineStr">
+        <is>
+          <t>5f453062ec331549297ee6b8</t>
+        </is>
+      </c>
+      <c r="B1165" t="n">
+        <v>19432084</v>
+      </c>
+      <c r="C1165" t="n">
+        <v>1</v>
+      </c>
+      <c r="D1165" t="n">
+        <v>3</v>
+      </c>
+      <c r="E1165" t="n">
+        <v>0</v>
+      </c>
+      <c r="F1165" t="inlineStr">
+        <is>
+          <t>2026-09-29</t>
+        </is>
+      </c>
+    </row>
+    <row r="1166">
+      <c r="A1166" t="inlineStr">
+        <is>
+          <t>5f47aeb6c387a50bca03dd55</t>
+        </is>
+      </c>
+      <c r="B1166" t="n">
+        <v>-16684624</v>
+      </c>
+      <c r="C1166" t="n">
+        <v>0</v>
+      </c>
+      <c r="D1166" t="n">
+        <v>2</v>
+      </c>
+      <c r="E1166" t="n">
+        <v>0</v>
+      </c>
+      <c r="F1166" t="inlineStr">
+        <is>
+          <t>2026-09-29</t>
+        </is>
+      </c>
+    </row>
+    <row r="1167">
+      <c r="A1167" t="inlineStr">
+        <is>
+          <t>5f47ab5b9e2edb0bb831c703</t>
+        </is>
+      </c>
+      <c r="B1167" t="n">
+        <v>11641524</v>
+      </c>
+      <c r="C1167" t="n">
+        <v>0</v>
+      </c>
+      <c r="D1167" t="n">
+        <v>1</v>
+      </c>
+      <c r="E1167" t="n">
+        <v>0</v>
+      </c>
+      <c r="F1167" t="inlineStr">
+        <is>
+          <t>2026-09-29</t>
+        </is>
+      </c>
+    </row>
+    <row r="1168">
+      <c r="A1168" t="inlineStr">
+        <is>
+          <t>5f452f5e66dd374930eb2b71</t>
+        </is>
+      </c>
+      <c r="B1168" t="n">
+        <v>-3097178</v>
+      </c>
+      <c r="C1168" t="n">
+        <v>3</v>
+      </c>
+      <c r="D1168" t="n">
+        <v>4</v>
+      </c>
+      <c r="E1168" t="n">
+        <v>4</v>
+      </c>
+      <c r="F1168" t="inlineStr">
+        <is>
+          <t>2026-09-29</t>
+        </is>
+      </c>
+    </row>
+    <row r="1169">
+      <c r="A1169" t="inlineStr">
+        <is>
+          <t>5f4530beec331549297ee6d6</t>
+        </is>
+      </c>
+      <c r="B1169" t="n">
+        <v>67806458</v>
+      </c>
+      <c r="C1169" t="n">
+        <v>0</v>
+      </c>
+      <c r="D1169" t="n">
+        <v>3</v>
+      </c>
+      <c r="E1169" t="n">
+        <v>0</v>
+      </c>
+      <c r="F1169" t="inlineStr">
+        <is>
+          <t>2026-09-29</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/datos/hechos/td_admin.xlsx
+++ b/datos/hechos/td_admin.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F1169"/>
+  <dimension ref="A1:F1177"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -28492,6 +28492,198 @@
         </is>
       </c>
     </row>
+    <row r="1170">
+      <c r="A1170" t="inlineStr">
+        <is>
+          <t>5f45324dec331549297ee971</t>
+        </is>
+      </c>
+      <c r="B1170" t="n">
+        <v>6297447</v>
+      </c>
+      <c r="C1170" t="n">
+        <v>1</v>
+      </c>
+      <c r="D1170" t="n">
+        <v>2</v>
+      </c>
+      <c r="E1170" t="n">
+        <v>1</v>
+      </c>
+      <c r="F1170" t="inlineStr">
+        <is>
+          <t>2026-09-30</t>
+        </is>
+      </c>
+    </row>
+    <row r="1171">
+      <c r="A1171" t="inlineStr">
+        <is>
+          <t>5f4531e9764e7d491e029746</t>
+        </is>
+      </c>
+      <c r="B1171" t="n">
+        <v>10651076</v>
+      </c>
+      <c r="C1171" t="n">
+        <v>0</v>
+      </c>
+      <c r="D1171" t="n">
+        <v>0</v>
+      </c>
+      <c r="E1171" t="n">
+        <v>0</v>
+      </c>
+      <c r="F1171" t="inlineStr">
+        <is>
+          <t>2026-09-30</t>
+        </is>
+      </c>
+    </row>
+    <row r="1172">
+      <c r="A1172" t="inlineStr">
+        <is>
+          <t>62d5bd9ad8106d3355b5bdc1</t>
+        </is>
+      </c>
+      <c r="B1172" t="n">
+        <v>-7314141</v>
+      </c>
+      <c r="C1172" t="n">
+        <v>1</v>
+      </c>
+      <c r="D1172" t="n">
+        <v>2</v>
+      </c>
+      <c r="E1172" t="n">
+        <v>1</v>
+      </c>
+      <c r="F1172" t="inlineStr">
+        <is>
+          <t>2026-09-30</t>
+        </is>
+      </c>
+    </row>
+    <row r="1173">
+      <c r="A1173" t="inlineStr">
+        <is>
+          <t>5f453062ec331549297ee6b8</t>
+        </is>
+      </c>
+      <c r="B1173" t="n">
+        <v>-19607683</v>
+      </c>
+      <c r="C1173" t="n">
+        <v>1</v>
+      </c>
+      <c r="D1173" t="n">
+        <v>3</v>
+      </c>
+      <c r="E1173" t="n">
+        <v>0</v>
+      </c>
+      <c r="F1173" t="inlineStr">
+        <is>
+          <t>2026-09-30</t>
+        </is>
+      </c>
+    </row>
+    <row r="1174">
+      <c r="A1174" t="inlineStr">
+        <is>
+          <t>5f47aeb6c387a50bca03dd55</t>
+        </is>
+      </c>
+      <c r="B1174" t="n">
+        <v>-25984624</v>
+      </c>
+      <c r="C1174" t="n">
+        <v>0</v>
+      </c>
+      <c r="D1174" t="n">
+        <v>2</v>
+      </c>
+      <c r="E1174" t="n">
+        <v>0</v>
+      </c>
+      <c r="F1174" t="inlineStr">
+        <is>
+          <t>2026-09-30</t>
+        </is>
+      </c>
+    </row>
+    <row r="1175">
+      <c r="A1175" t="inlineStr">
+        <is>
+          <t>5f47ab5b9e2edb0bb831c703</t>
+        </is>
+      </c>
+      <c r="B1175" t="n">
+        <v>-8486819</v>
+      </c>
+      <c r="C1175" t="n">
+        <v>0</v>
+      </c>
+      <c r="D1175" t="n">
+        <v>1</v>
+      </c>
+      <c r="E1175" t="n">
+        <v>0</v>
+      </c>
+      <c r="F1175" t="inlineStr">
+        <is>
+          <t>2026-09-30</t>
+        </is>
+      </c>
+    </row>
+    <row r="1176">
+      <c r="A1176" t="inlineStr">
+        <is>
+          <t>5f452f5e66dd374930eb2b71</t>
+        </is>
+      </c>
+      <c r="B1176" t="n">
+        <v>-3097178</v>
+      </c>
+      <c r="C1176" t="n">
+        <v>3</v>
+      </c>
+      <c r="D1176" t="n">
+        <v>4</v>
+      </c>
+      <c r="E1176" t="n">
+        <v>4</v>
+      </c>
+      <c r="F1176" t="inlineStr">
+        <is>
+          <t>2026-09-30</t>
+        </is>
+      </c>
+    </row>
+    <row r="1177">
+      <c r="A1177" t="inlineStr">
+        <is>
+          <t>5f4530beec331549297ee6d6</t>
+        </is>
+      </c>
+      <c r="B1177" t="n">
+        <v>90974568</v>
+      </c>
+      <c r="C1177" t="n">
+        <v>0</v>
+      </c>
+      <c r="D1177" t="n">
+        <v>3</v>
+      </c>
+      <c r="E1177" t="n">
+        <v>0</v>
+      </c>
+      <c r="F1177" t="inlineStr">
+        <is>
+          <t>2026-09-30</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/datos/hechos/td_admin.xlsx
+++ b/datos/hechos/td_admin.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F1177"/>
+  <dimension ref="A1:F1185"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -28684,6 +28684,198 @@
         </is>
       </c>
     </row>
+    <row r="1178">
+      <c r="A1178" t="inlineStr">
+        <is>
+          <t>5f45324dec331549297ee971</t>
+        </is>
+      </c>
+      <c r="B1178" t="n">
+        <v>27822005</v>
+      </c>
+      <c r="C1178" t="n">
+        <v>1</v>
+      </c>
+      <c r="D1178" t="n">
+        <v>2</v>
+      </c>
+      <c r="E1178" t="n">
+        <v>1</v>
+      </c>
+      <c r="F1178" t="inlineStr">
+        <is>
+          <t>2026-10-01</t>
+        </is>
+      </c>
+    </row>
+    <row r="1179">
+      <c r="A1179" t="inlineStr">
+        <is>
+          <t>5f4531e9764e7d491e029746</t>
+        </is>
+      </c>
+      <c r="B1179" t="n">
+        <v>6651043</v>
+      </c>
+      <c r="C1179" t="n">
+        <v>0</v>
+      </c>
+      <c r="D1179" t="n">
+        <v>0</v>
+      </c>
+      <c r="E1179" t="n">
+        <v>0</v>
+      </c>
+      <c r="F1179" t="inlineStr">
+        <is>
+          <t>2026-10-01</t>
+        </is>
+      </c>
+    </row>
+    <row r="1180">
+      <c r="A1180" t="inlineStr">
+        <is>
+          <t>62d5bd9ad8106d3355b5bdc1</t>
+        </is>
+      </c>
+      <c r="B1180" t="n">
+        <v>-23514140</v>
+      </c>
+      <c r="C1180" t="n">
+        <v>1</v>
+      </c>
+      <c r="D1180" t="n">
+        <v>2</v>
+      </c>
+      <c r="E1180" t="n">
+        <v>1</v>
+      </c>
+      <c r="F1180" t="inlineStr">
+        <is>
+          <t>2026-10-01</t>
+        </is>
+      </c>
+    </row>
+    <row r="1181">
+      <c r="A1181" t="inlineStr">
+        <is>
+          <t>5f453062ec331549297ee6b8</t>
+        </is>
+      </c>
+      <c r="B1181" t="n">
+        <v>-19607683</v>
+      </c>
+      <c r="C1181" t="n">
+        <v>1</v>
+      </c>
+      <c r="D1181" t="n">
+        <v>3</v>
+      </c>
+      <c r="E1181" t="n">
+        <v>0</v>
+      </c>
+      <c r="F1181" t="inlineStr">
+        <is>
+          <t>2026-10-01</t>
+        </is>
+      </c>
+    </row>
+    <row r="1182">
+      <c r="A1182" t="inlineStr">
+        <is>
+          <t>5f47aeb6c387a50bca03dd55</t>
+        </is>
+      </c>
+      <c r="B1182" t="n">
+        <v>-21913263</v>
+      </c>
+      <c r="C1182" t="n">
+        <v>0</v>
+      </c>
+      <c r="D1182" t="n">
+        <v>2</v>
+      </c>
+      <c r="E1182" t="n">
+        <v>0</v>
+      </c>
+      <c r="F1182" t="inlineStr">
+        <is>
+          <t>2026-10-01</t>
+        </is>
+      </c>
+    </row>
+    <row r="1183">
+      <c r="A1183" t="inlineStr">
+        <is>
+          <t>5f47ab5b9e2edb0bb831c703</t>
+        </is>
+      </c>
+      <c r="B1183" t="n">
+        <v>-8486819</v>
+      </c>
+      <c r="C1183" t="n">
+        <v>0</v>
+      </c>
+      <c r="D1183" t="n">
+        <v>1</v>
+      </c>
+      <c r="E1183" t="n">
+        <v>0</v>
+      </c>
+      <c r="F1183" t="inlineStr">
+        <is>
+          <t>2026-10-01</t>
+        </is>
+      </c>
+    </row>
+    <row r="1184">
+      <c r="A1184" t="inlineStr">
+        <is>
+          <t>5f452f5e66dd374930eb2b71</t>
+        </is>
+      </c>
+      <c r="B1184" t="n">
+        <v>31527237</v>
+      </c>
+      <c r="C1184" t="n">
+        <v>3</v>
+      </c>
+      <c r="D1184" t="n">
+        <v>4</v>
+      </c>
+      <c r="E1184" t="n">
+        <v>4</v>
+      </c>
+      <c r="F1184" t="inlineStr">
+        <is>
+          <t>2026-10-01</t>
+        </is>
+      </c>
+    </row>
+    <row r="1185">
+      <c r="A1185" t="inlineStr">
+        <is>
+          <t>5f4530beec331549297ee6d6</t>
+        </is>
+      </c>
+      <c r="B1185" t="n">
+        <v>90974568</v>
+      </c>
+      <c r="C1185" t="n">
+        <v>0</v>
+      </c>
+      <c r="D1185" t="n">
+        <v>3</v>
+      </c>
+      <c r="E1185" t="n">
+        <v>0</v>
+      </c>
+      <c r="F1185" t="inlineStr">
+        <is>
+          <t>2026-10-01</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/datos/hechos/td_admin.xlsx
+++ b/datos/hechos/td_admin.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F1185"/>
+  <dimension ref="A1:F1193"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -28876,6 +28876,198 @@
         </is>
       </c>
     </row>
+    <row r="1186">
+      <c r="A1186" t="inlineStr">
+        <is>
+          <t>5f45324dec331549297ee971</t>
+        </is>
+      </c>
+      <c r="B1186" t="n">
+        <v>4822005</v>
+      </c>
+      <c r="C1186" t="n">
+        <v>1</v>
+      </c>
+      <c r="D1186" t="n">
+        <v>2</v>
+      </c>
+      <c r="E1186" t="n">
+        <v>1</v>
+      </c>
+      <c r="F1186" t="inlineStr">
+        <is>
+          <t>2026-10-02</t>
+        </is>
+      </c>
+    </row>
+    <row r="1187">
+      <c r="A1187" t="inlineStr">
+        <is>
+          <t>5f4531e9764e7d491e029746</t>
+        </is>
+      </c>
+      <c r="B1187" t="n">
+        <v>6651043</v>
+      </c>
+      <c r="C1187" t="n">
+        <v>0</v>
+      </c>
+      <c r="D1187" t="n">
+        <v>0</v>
+      </c>
+      <c r="E1187" t="n">
+        <v>0</v>
+      </c>
+      <c r="F1187" t="inlineStr">
+        <is>
+          <t>2026-10-02</t>
+        </is>
+      </c>
+    </row>
+    <row r="1188">
+      <c r="A1188" t="inlineStr">
+        <is>
+          <t>62d5bd9ad8106d3355b5bdc1</t>
+        </is>
+      </c>
+      <c r="B1188" t="n">
+        <v>-12736100</v>
+      </c>
+      <c r="C1188" t="n">
+        <v>1</v>
+      </c>
+      <c r="D1188" t="n">
+        <v>2</v>
+      </c>
+      <c r="E1188" t="n">
+        <v>1</v>
+      </c>
+      <c r="F1188" t="inlineStr">
+        <is>
+          <t>2026-10-02</t>
+        </is>
+      </c>
+    </row>
+    <row r="1189">
+      <c r="A1189" t="inlineStr">
+        <is>
+          <t>5f453062ec331549297ee6b8</t>
+        </is>
+      </c>
+      <c r="B1189" t="n">
+        <v>-7218044</v>
+      </c>
+      <c r="C1189" t="n">
+        <v>1</v>
+      </c>
+      <c r="D1189" t="n">
+        <v>3</v>
+      </c>
+      <c r="E1189" t="n">
+        <v>0</v>
+      </c>
+      <c r="F1189" t="inlineStr">
+        <is>
+          <t>2026-10-02</t>
+        </is>
+      </c>
+    </row>
+    <row r="1190">
+      <c r="A1190" t="inlineStr">
+        <is>
+          <t>5f47aeb6c387a50bca03dd55</t>
+        </is>
+      </c>
+      <c r="B1190" t="n">
+        <v>-12895977</v>
+      </c>
+      <c r="C1190" t="n">
+        <v>0</v>
+      </c>
+      <c r="D1190" t="n">
+        <v>2</v>
+      </c>
+      <c r="E1190" t="n">
+        <v>0</v>
+      </c>
+      <c r="F1190" t="inlineStr">
+        <is>
+          <t>2026-10-02</t>
+        </is>
+      </c>
+    </row>
+    <row r="1191">
+      <c r="A1191" t="inlineStr">
+        <is>
+          <t>5f47ab5b9e2edb0bb831c703</t>
+        </is>
+      </c>
+      <c r="B1191" t="n">
+        <v>-8486819</v>
+      </c>
+      <c r="C1191" t="n">
+        <v>0</v>
+      </c>
+      <c r="D1191" t="n">
+        <v>1</v>
+      </c>
+      <c r="E1191" t="n">
+        <v>0</v>
+      </c>
+      <c r="F1191" t="inlineStr">
+        <is>
+          <t>2026-10-02</t>
+        </is>
+      </c>
+    </row>
+    <row r="1192">
+      <c r="A1192" t="inlineStr">
+        <is>
+          <t>5f452f5e66dd374930eb2b71</t>
+        </is>
+      </c>
+      <c r="B1192" t="n">
+        <v>31527237</v>
+      </c>
+      <c r="C1192" t="n">
+        <v>3</v>
+      </c>
+      <c r="D1192" t="n">
+        <v>4</v>
+      </c>
+      <c r="E1192" t="n">
+        <v>4</v>
+      </c>
+      <c r="F1192" t="inlineStr">
+        <is>
+          <t>2026-10-02</t>
+        </is>
+      </c>
+    </row>
+    <row r="1193">
+      <c r="A1193" t="inlineStr">
+        <is>
+          <t>5f4530beec331549297ee6d6</t>
+        </is>
+      </c>
+      <c r="B1193" t="n">
+        <v>31548068</v>
+      </c>
+      <c r="C1193" t="n">
+        <v>0</v>
+      </c>
+      <c r="D1193" t="n">
+        <v>3</v>
+      </c>
+      <c r="E1193" t="n">
+        <v>0</v>
+      </c>
+      <c r="F1193" t="inlineStr">
+        <is>
+          <t>2026-10-02</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/datos/hechos/td_admin.xlsx
+++ b/datos/hechos/td_admin.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F1193"/>
+  <dimension ref="A1:F1201"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -29068,6 +29068,198 @@
         </is>
       </c>
     </row>
+    <row r="1194">
+      <c r="A1194" t="inlineStr">
+        <is>
+          <t>5f45324dec331549297ee971</t>
+        </is>
+      </c>
+      <c r="B1194" t="n">
+        <v>56098311</v>
+      </c>
+      <c r="C1194" t="n">
+        <v>1</v>
+      </c>
+      <c r="D1194" t="n">
+        <v>2</v>
+      </c>
+      <c r="E1194" t="n">
+        <v>1</v>
+      </c>
+      <c r="F1194" t="inlineStr">
+        <is>
+          <t>2026-10-03</t>
+        </is>
+      </c>
+    </row>
+    <row r="1195">
+      <c r="A1195" t="inlineStr">
+        <is>
+          <t>5f4531e9764e7d491e029746</t>
+        </is>
+      </c>
+      <c r="B1195" t="n">
+        <v>6651043</v>
+      </c>
+      <c r="C1195" t="n">
+        <v>0</v>
+      </c>
+      <c r="D1195" t="n">
+        <v>0</v>
+      </c>
+      <c r="E1195" t="n">
+        <v>0</v>
+      </c>
+      <c r="F1195" t="inlineStr">
+        <is>
+          <t>2026-10-03</t>
+        </is>
+      </c>
+    </row>
+    <row r="1196">
+      <c r="A1196" t="inlineStr">
+        <is>
+          <t>62d5bd9ad8106d3355b5bdc1</t>
+        </is>
+      </c>
+      <c r="B1196" t="n">
+        <v>-12736100</v>
+      </c>
+      <c r="C1196" t="n">
+        <v>1</v>
+      </c>
+      <c r="D1196" t="n">
+        <v>2</v>
+      </c>
+      <c r="E1196" t="n">
+        <v>1</v>
+      </c>
+      <c r="F1196" t="inlineStr">
+        <is>
+          <t>2026-10-03</t>
+        </is>
+      </c>
+    </row>
+    <row r="1197">
+      <c r="A1197" t="inlineStr">
+        <is>
+          <t>5f453062ec331549297ee6b8</t>
+        </is>
+      </c>
+      <c r="B1197" t="n">
+        <v>-7218044</v>
+      </c>
+      <c r="C1197" t="n">
+        <v>1</v>
+      </c>
+      <c r="D1197" t="n">
+        <v>3</v>
+      </c>
+      <c r="E1197" t="n">
+        <v>0</v>
+      </c>
+      <c r="F1197" t="inlineStr">
+        <is>
+          <t>2026-10-03</t>
+        </is>
+      </c>
+    </row>
+    <row r="1198">
+      <c r="A1198" t="inlineStr">
+        <is>
+          <t>5f47aeb6c387a50bca03dd55</t>
+        </is>
+      </c>
+      <c r="B1198" t="n">
+        <v>-12895977</v>
+      </c>
+      <c r="C1198" t="n">
+        <v>0</v>
+      </c>
+      <c r="D1198" t="n">
+        <v>2</v>
+      </c>
+      <c r="E1198" t="n">
+        <v>0</v>
+      </c>
+      <c r="F1198" t="inlineStr">
+        <is>
+          <t>2026-10-03</t>
+        </is>
+      </c>
+    </row>
+    <row r="1199">
+      <c r="A1199" t="inlineStr">
+        <is>
+          <t>5f47ab5b9e2edb0bb831c703</t>
+        </is>
+      </c>
+      <c r="B1199" t="n">
+        <v>-8486819</v>
+      </c>
+      <c r="C1199" t="n">
+        <v>0</v>
+      </c>
+      <c r="D1199" t="n">
+        <v>1</v>
+      </c>
+      <c r="E1199" t="n">
+        <v>0</v>
+      </c>
+      <c r="F1199" t="inlineStr">
+        <is>
+          <t>2026-10-03</t>
+        </is>
+      </c>
+    </row>
+    <row r="1200">
+      <c r="A1200" t="inlineStr">
+        <is>
+          <t>5f452f5e66dd374930eb2b71</t>
+        </is>
+      </c>
+      <c r="B1200" t="n">
+        <v>31527237</v>
+      </c>
+      <c r="C1200" t="n">
+        <v>3</v>
+      </c>
+      <c r="D1200" t="n">
+        <v>4</v>
+      </c>
+      <c r="E1200" t="n">
+        <v>4</v>
+      </c>
+      <c r="F1200" t="inlineStr">
+        <is>
+          <t>2026-10-03</t>
+        </is>
+      </c>
+    </row>
+    <row r="1201">
+      <c r="A1201" t="inlineStr">
+        <is>
+          <t>5f4530beec331549297ee6d6</t>
+        </is>
+      </c>
+      <c r="B1201" t="n">
+        <v>31548068</v>
+      </c>
+      <c r="C1201" t="n">
+        <v>0</v>
+      </c>
+      <c r="D1201" t="n">
+        <v>3</v>
+      </c>
+      <c r="E1201" t="n">
+        <v>0</v>
+      </c>
+      <c r="F1201" t="inlineStr">
+        <is>
+          <t>2026-10-03</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/datos/hechos/td_admin.xlsx
+++ b/datos/hechos/td_admin.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F1201"/>
+  <dimension ref="A1:F1209"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -29260,6 +29260,198 @@
         </is>
       </c>
     </row>
+    <row r="1202">
+      <c r="A1202" t="inlineStr">
+        <is>
+          <t>5f45324dec331549297ee971</t>
+        </is>
+      </c>
+      <c r="B1202" t="n">
+        <v>16898311</v>
+      </c>
+      <c r="C1202" t="n">
+        <v>1</v>
+      </c>
+      <c r="D1202" t="n">
+        <v>2</v>
+      </c>
+      <c r="E1202" t="n">
+        <v>1</v>
+      </c>
+      <c r="F1202" t="inlineStr">
+        <is>
+          <t>2026-10-04</t>
+        </is>
+      </c>
+    </row>
+    <row r="1203">
+      <c r="A1203" t="inlineStr">
+        <is>
+          <t>5f4531e9764e7d491e029746</t>
+        </is>
+      </c>
+      <c r="B1203" t="n">
+        <v>6651043</v>
+      </c>
+      <c r="C1203" t="n">
+        <v>0</v>
+      </c>
+      <c r="D1203" t="n">
+        <v>0</v>
+      </c>
+      <c r="E1203" t="n">
+        <v>0</v>
+      </c>
+      <c r="F1203" t="inlineStr">
+        <is>
+          <t>2026-10-04</t>
+        </is>
+      </c>
+    </row>
+    <row r="1204">
+      <c r="A1204" t="inlineStr">
+        <is>
+          <t>62d5bd9ad8106d3355b5bdc1</t>
+        </is>
+      </c>
+      <c r="B1204" t="n">
+        <v>-12736100</v>
+      </c>
+      <c r="C1204" t="n">
+        <v>1</v>
+      </c>
+      <c r="D1204" t="n">
+        <v>2</v>
+      </c>
+      <c r="E1204" t="n">
+        <v>1</v>
+      </c>
+      <c r="F1204" t="inlineStr">
+        <is>
+          <t>2026-10-04</t>
+        </is>
+      </c>
+    </row>
+    <row r="1205">
+      <c r="A1205" t="inlineStr">
+        <is>
+          <t>5f453062ec331549297ee6b8</t>
+        </is>
+      </c>
+      <c r="B1205" t="n">
+        <v>-7218044</v>
+      </c>
+      <c r="C1205" t="n">
+        <v>1</v>
+      </c>
+      <c r="D1205" t="n">
+        <v>3</v>
+      </c>
+      <c r="E1205" t="n">
+        <v>0</v>
+      </c>
+      <c r="F1205" t="inlineStr">
+        <is>
+          <t>2026-10-04</t>
+        </is>
+      </c>
+    </row>
+    <row r="1206">
+      <c r="A1206" t="inlineStr">
+        <is>
+          <t>5f47aeb6c387a50bca03dd55</t>
+        </is>
+      </c>
+      <c r="B1206" t="n">
+        <v>-10217798</v>
+      </c>
+      <c r="C1206" t="n">
+        <v>0</v>
+      </c>
+      <c r="D1206" t="n">
+        <v>2</v>
+      </c>
+      <c r="E1206" t="n">
+        <v>0</v>
+      </c>
+      <c r="F1206" t="inlineStr">
+        <is>
+          <t>2026-10-04</t>
+        </is>
+      </c>
+    </row>
+    <row r="1207">
+      <c r="A1207" t="inlineStr">
+        <is>
+          <t>5f47ab5b9e2edb0bb831c703</t>
+        </is>
+      </c>
+      <c r="B1207" t="n">
+        <v>-8486819</v>
+      </c>
+      <c r="C1207" t="n">
+        <v>0</v>
+      </c>
+      <c r="D1207" t="n">
+        <v>1</v>
+      </c>
+      <c r="E1207" t="n">
+        <v>0</v>
+      </c>
+      <c r="F1207" t="inlineStr">
+        <is>
+          <t>2026-10-04</t>
+        </is>
+      </c>
+    </row>
+    <row r="1208">
+      <c r="A1208" t="inlineStr">
+        <is>
+          <t>5f452f5e66dd374930eb2b71</t>
+        </is>
+      </c>
+      <c r="B1208" t="n">
+        <v>31527237</v>
+      </c>
+      <c r="C1208" t="n">
+        <v>3</v>
+      </c>
+      <c r="D1208" t="n">
+        <v>4</v>
+      </c>
+      <c r="E1208" t="n">
+        <v>4</v>
+      </c>
+      <c r="F1208" t="inlineStr">
+        <is>
+          <t>2026-10-04</t>
+        </is>
+      </c>
+    </row>
+    <row r="1209">
+      <c r="A1209" t="inlineStr">
+        <is>
+          <t>5f4530beec331549297ee6d6</t>
+        </is>
+      </c>
+      <c r="B1209" t="n">
+        <v>31548068</v>
+      </c>
+      <c r="C1209" t="n">
+        <v>0</v>
+      </c>
+      <c r="D1209" t="n">
+        <v>3</v>
+      </c>
+      <c r="E1209" t="n">
+        <v>0</v>
+      </c>
+      <c r="F1209" t="inlineStr">
+        <is>
+          <t>2026-10-04</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/datos/hechos/td_admin.xlsx
+++ b/datos/hechos/td_admin.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F1209"/>
+  <dimension ref="A1:F1217"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -29452,6 +29452,198 @@
         </is>
       </c>
     </row>
+    <row r="1210">
+      <c r="A1210" t="inlineStr">
+        <is>
+          <t>5f45324dec331549297ee971</t>
+        </is>
+      </c>
+      <c r="B1210" t="n">
+        <v>-5256787</v>
+      </c>
+      <c r="C1210" t="n">
+        <v>1</v>
+      </c>
+      <c r="D1210" t="n">
+        <v>2</v>
+      </c>
+      <c r="E1210" t="n">
+        <v>1</v>
+      </c>
+      <c r="F1210" t="inlineStr">
+        <is>
+          <t>2026-10-05</t>
+        </is>
+      </c>
+    </row>
+    <row r="1211">
+      <c r="A1211" t="inlineStr">
+        <is>
+          <t>5f4531e9764e7d491e029746</t>
+        </is>
+      </c>
+      <c r="B1211" t="n">
+        <v>6651043</v>
+      </c>
+      <c r="C1211" t="n">
+        <v>0</v>
+      </c>
+      <c r="D1211" t="n">
+        <v>0</v>
+      </c>
+      <c r="E1211" t="n">
+        <v>0</v>
+      </c>
+      <c r="F1211" t="inlineStr">
+        <is>
+          <t>2026-10-05</t>
+        </is>
+      </c>
+    </row>
+    <row r="1212">
+      <c r="A1212" t="inlineStr">
+        <is>
+          <t>62d5bd9ad8106d3355b5bdc1</t>
+        </is>
+      </c>
+      <c r="B1212" t="n">
+        <v>-12736100</v>
+      </c>
+      <c r="C1212" t="n">
+        <v>1</v>
+      </c>
+      <c r="D1212" t="n">
+        <v>2</v>
+      </c>
+      <c r="E1212" t="n">
+        <v>1</v>
+      </c>
+      <c r="F1212" t="inlineStr">
+        <is>
+          <t>2026-10-05</t>
+        </is>
+      </c>
+    </row>
+    <row r="1213">
+      <c r="A1213" t="inlineStr">
+        <is>
+          <t>5f453062ec331549297ee6b8</t>
+        </is>
+      </c>
+      <c r="B1213" t="n">
+        <v>-7218044</v>
+      </c>
+      <c r="C1213" t="n">
+        <v>1</v>
+      </c>
+      <c r="D1213" t="n">
+        <v>3</v>
+      </c>
+      <c r="E1213" t="n">
+        <v>0</v>
+      </c>
+      <c r="F1213" t="inlineStr">
+        <is>
+          <t>2026-10-05</t>
+        </is>
+      </c>
+    </row>
+    <row r="1214">
+      <c r="A1214" t="inlineStr">
+        <is>
+          <t>5f47aeb6c387a50bca03dd55</t>
+        </is>
+      </c>
+      <c r="B1214" t="n">
+        <v>-10217798</v>
+      </c>
+      <c r="C1214" t="n">
+        <v>0</v>
+      </c>
+      <c r="D1214" t="n">
+        <v>2</v>
+      </c>
+      <c r="E1214" t="n">
+        <v>0</v>
+      </c>
+      <c r="F1214" t="inlineStr">
+        <is>
+          <t>2026-10-05</t>
+        </is>
+      </c>
+    </row>
+    <row r="1215">
+      <c r="A1215" t="inlineStr">
+        <is>
+          <t>5f47ab5b9e2edb0bb831c703</t>
+        </is>
+      </c>
+      <c r="B1215" t="n">
+        <v>-8486819</v>
+      </c>
+      <c r="C1215" t="n">
+        <v>0</v>
+      </c>
+      <c r="D1215" t="n">
+        <v>1</v>
+      </c>
+      <c r="E1215" t="n">
+        <v>0</v>
+      </c>
+      <c r="F1215" t="inlineStr">
+        <is>
+          <t>2026-10-05</t>
+        </is>
+      </c>
+    </row>
+    <row r="1216">
+      <c r="A1216" t="inlineStr">
+        <is>
+          <t>5f452f5e66dd374930eb2b71</t>
+        </is>
+      </c>
+      <c r="B1216" t="n">
+        <v>31527237</v>
+      </c>
+      <c r="C1216" t="n">
+        <v>3</v>
+      </c>
+      <c r="D1216" t="n">
+        <v>4</v>
+      </c>
+      <c r="E1216" t="n">
+        <v>4</v>
+      </c>
+      <c r="F1216" t="inlineStr">
+        <is>
+          <t>2026-10-05</t>
+        </is>
+      </c>
+    </row>
+    <row r="1217">
+      <c r="A1217" t="inlineStr">
+        <is>
+          <t>5f4530beec331549297ee6d6</t>
+        </is>
+      </c>
+      <c r="B1217" t="n">
+        <v>31548068</v>
+      </c>
+      <c r="C1217" t="n">
+        <v>0</v>
+      </c>
+      <c r="D1217" t="n">
+        <v>3</v>
+      </c>
+      <c r="E1217" t="n">
+        <v>0</v>
+      </c>
+      <c r="F1217" t="inlineStr">
+        <is>
+          <t>2026-10-05</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/datos/hechos/td_admin.xlsx
+++ b/datos/hechos/td_admin.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F1217"/>
+  <dimension ref="A1:F1225"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -29644,6 +29644,198 @@
         </is>
       </c>
     </row>
+    <row r="1218">
+      <c r="A1218" t="inlineStr">
+        <is>
+          <t>5f45324dec331549297ee971</t>
+        </is>
+      </c>
+      <c r="B1218" t="n">
+        <v>-5256787</v>
+      </c>
+      <c r="C1218" t="n">
+        <v>1</v>
+      </c>
+      <c r="D1218" t="n">
+        <v>2</v>
+      </c>
+      <c r="E1218" t="n">
+        <v>1</v>
+      </c>
+      <c r="F1218" t="inlineStr">
+        <is>
+          <t>2026-10-06</t>
+        </is>
+      </c>
+    </row>
+    <row r="1219">
+      <c r="A1219" t="inlineStr">
+        <is>
+          <t>5f4531e9764e7d491e029746</t>
+        </is>
+      </c>
+      <c r="B1219" t="n">
+        <v>6651043</v>
+      </c>
+      <c r="C1219" t="n">
+        <v>0</v>
+      </c>
+      <c r="D1219" t="n">
+        <v>0</v>
+      </c>
+      <c r="E1219" t="n">
+        <v>0</v>
+      </c>
+      <c r="F1219" t="inlineStr">
+        <is>
+          <t>2026-10-06</t>
+        </is>
+      </c>
+    </row>
+    <row r="1220">
+      <c r="A1220" t="inlineStr">
+        <is>
+          <t>62d5bd9ad8106d3355b5bdc1</t>
+        </is>
+      </c>
+      <c r="B1220" t="n">
+        <v>-12736100</v>
+      </c>
+      <c r="C1220" t="n">
+        <v>1</v>
+      </c>
+      <c r="D1220" t="n">
+        <v>2</v>
+      </c>
+      <c r="E1220" t="n">
+        <v>1</v>
+      </c>
+      <c r="F1220" t="inlineStr">
+        <is>
+          <t>2026-10-06</t>
+        </is>
+      </c>
+    </row>
+    <row r="1221">
+      <c r="A1221" t="inlineStr">
+        <is>
+          <t>5f453062ec331549297ee6b8</t>
+        </is>
+      </c>
+      <c r="B1221" t="n">
+        <v>-7218044</v>
+      </c>
+      <c r="C1221" t="n">
+        <v>1</v>
+      </c>
+      <c r="D1221" t="n">
+        <v>3</v>
+      </c>
+      <c r="E1221" t="n">
+        <v>0</v>
+      </c>
+      <c r="F1221" t="inlineStr">
+        <is>
+          <t>2026-10-06</t>
+        </is>
+      </c>
+    </row>
+    <row r="1222">
+      <c r="A1222" t="inlineStr">
+        <is>
+          <t>5f47aeb6c387a50bca03dd55</t>
+        </is>
+      </c>
+      <c r="B1222" t="n">
+        <v>-1436367</v>
+      </c>
+      <c r="C1222" t="n">
+        <v>0</v>
+      </c>
+      <c r="D1222" t="n">
+        <v>2</v>
+      </c>
+      <c r="E1222" t="n">
+        <v>0</v>
+      </c>
+      <c r="F1222" t="inlineStr">
+        <is>
+          <t>2026-10-06</t>
+        </is>
+      </c>
+    </row>
+    <row r="1223">
+      <c r="A1223" t="inlineStr">
+        <is>
+          <t>5f47ab5b9e2edb0bb831c703</t>
+        </is>
+      </c>
+      <c r="B1223" t="n">
+        <v>-8486819</v>
+      </c>
+      <c r="C1223" t="n">
+        <v>0</v>
+      </c>
+      <c r="D1223" t="n">
+        <v>1</v>
+      </c>
+      <c r="E1223" t="n">
+        <v>0</v>
+      </c>
+      <c r="F1223" t="inlineStr">
+        <is>
+          <t>2026-10-06</t>
+        </is>
+      </c>
+    </row>
+    <row r="1224">
+      <c r="A1224" t="inlineStr">
+        <is>
+          <t>5f452f5e66dd374930eb2b71</t>
+        </is>
+      </c>
+      <c r="B1224" t="n">
+        <v>6519086</v>
+      </c>
+      <c r="C1224" t="n">
+        <v>3</v>
+      </c>
+      <c r="D1224" t="n">
+        <v>4</v>
+      </c>
+      <c r="E1224" t="n">
+        <v>4</v>
+      </c>
+      <c r="F1224" t="inlineStr">
+        <is>
+          <t>2026-10-06</t>
+        </is>
+      </c>
+    </row>
+    <row r="1225">
+      <c r="A1225" t="inlineStr">
+        <is>
+          <t>5f4530beec331549297ee6d6</t>
+        </is>
+      </c>
+      <c r="B1225" t="n">
+        <v>31548068</v>
+      </c>
+      <c r="C1225" t="n">
+        <v>0</v>
+      </c>
+      <c r="D1225" t="n">
+        <v>3</v>
+      </c>
+      <c r="E1225" t="n">
+        <v>0</v>
+      </c>
+      <c r="F1225" t="inlineStr">
+        <is>
+          <t>2026-10-06</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/datos/hechos/td_admin.xlsx
+++ b/datos/hechos/td_admin.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F1225"/>
+  <dimension ref="A1:F1233"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -29836,6 +29836,198 @@
         </is>
       </c>
     </row>
+    <row r="1226">
+      <c r="A1226" t="inlineStr">
+        <is>
+          <t>5f45324dec331549297ee971</t>
+        </is>
+      </c>
+      <c r="B1226" t="n">
+        <v>-5256787</v>
+      </c>
+      <c r="C1226" t="n">
+        <v>1</v>
+      </c>
+      <c r="D1226" t="n">
+        <v>2</v>
+      </c>
+      <c r="E1226" t="n">
+        <v>1</v>
+      </c>
+      <c r="F1226" t="inlineStr">
+        <is>
+          <t>2026-10-07</t>
+        </is>
+      </c>
+    </row>
+    <row r="1227">
+      <c r="A1227" t="inlineStr">
+        <is>
+          <t>5f4531e9764e7d491e029746</t>
+        </is>
+      </c>
+      <c r="B1227" t="n">
+        <v>6651043</v>
+      </c>
+      <c r="C1227" t="n">
+        <v>0</v>
+      </c>
+      <c r="D1227" t="n">
+        <v>0</v>
+      </c>
+      <c r="E1227" t="n">
+        <v>0</v>
+      </c>
+      <c r="F1227" t="inlineStr">
+        <is>
+          <t>2026-10-07</t>
+        </is>
+      </c>
+    </row>
+    <row r="1228">
+      <c r="A1228" t="inlineStr">
+        <is>
+          <t>62d5bd9ad8106d3355b5bdc1</t>
+        </is>
+      </c>
+      <c r="B1228" t="n">
+        <v>-12736100</v>
+      </c>
+      <c r="C1228" t="n">
+        <v>1</v>
+      </c>
+      <c r="D1228" t="n">
+        <v>2</v>
+      </c>
+      <c r="E1228" t="n">
+        <v>1</v>
+      </c>
+      <c r="F1228" t="inlineStr">
+        <is>
+          <t>2026-10-07</t>
+        </is>
+      </c>
+    </row>
+    <row r="1229">
+      <c r="A1229" t="inlineStr">
+        <is>
+          <t>5f453062ec331549297ee6b8</t>
+        </is>
+      </c>
+      <c r="B1229" t="n">
+        <v>-7218044</v>
+      </c>
+      <c r="C1229" t="n">
+        <v>1</v>
+      </c>
+      <c r="D1229" t="n">
+        <v>3</v>
+      </c>
+      <c r="E1229" t="n">
+        <v>0</v>
+      </c>
+      <c r="F1229" t="inlineStr">
+        <is>
+          <t>2026-10-07</t>
+        </is>
+      </c>
+    </row>
+    <row r="1230">
+      <c r="A1230" t="inlineStr">
+        <is>
+          <t>5f47aeb6c387a50bca03dd55</t>
+        </is>
+      </c>
+      <c r="B1230" t="n">
+        <v>-1436367</v>
+      </c>
+      <c r="C1230" t="n">
+        <v>0</v>
+      </c>
+      <c r="D1230" t="n">
+        <v>2</v>
+      </c>
+      <c r="E1230" t="n">
+        <v>0</v>
+      </c>
+      <c r="F1230" t="inlineStr">
+        <is>
+          <t>2026-10-07</t>
+        </is>
+      </c>
+    </row>
+    <row r="1231">
+      <c r="A1231" t="inlineStr">
+        <is>
+          <t>5f47ab5b9e2edb0bb831c703</t>
+        </is>
+      </c>
+      <c r="B1231" t="n">
+        <v>-11137223</v>
+      </c>
+      <c r="C1231" t="n">
+        <v>0</v>
+      </c>
+      <c r="D1231" t="n">
+        <v>1</v>
+      </c>
+      <c r="E1231" t="n">
+        <v>0</v>
+      </c>
+      <c r="F1231" t="inlineStr">
+        <is>
+          <t>2026-10-07</t>
+        </is>
+      </c>
+    </row>
+    <row r="1232">
+      <c r="A1232" t="inlineStr">
+        <is>
+          <t>5f452f5e66dd374930eb2b71</t>
+        </is>
+      </c>
+      <c r="B1232" t="n">
+        <v>6519086</v>
+      </c>
+      <c r="C1232" t="n">
+        <v>3</v>
+      </c>
+      <c r="D1232" t="n">
+        <v>4</v>
+      </c>
+      <c r="E1232" t="n">
+        <v>4</v>
+      </c>
+      <c r="F1232" t="inlineStr">
+        <is>
+          <t>2026-10-07</t>
+        </is>
+      </c>
+    </row>
+    <row r="1233">
+      <c r="A1233" t="inlineStr">
+        <is>
+          <t>5f4530beec331549297ee6d6</t>
+        </is>
+      </c>
+      <c r="B1233" t="n">
+        <v>31548068</v>
+      </c>
+      <c r="C1233" t="n">
+        <v>0</v>
+      </c>
+      <c r="D1233" t="n">
+        <v>3</v>
+      </c>
+      <c r="E1233" t="n">
+        <v>0</v>
+      </c>
+      <c r="F1233" t="inlineStr">
+        <is>
+          <t>2026-10-07</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/datos/hechos/td_admin.xlsx
+++ b/datos/hechos/td_admin.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F1233"/>
+  <dimension ref="A1:F1241"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -30028,6 +30028,198 @@
         </is>
       </c>
     </row>
+    <row r="1234">
+      <c r="A1234" t="inlineStr">
+        <is>
+          <t>5f45324dec331549297ee971</t>
+        </is>
+      </c>
+      <c r="B1234" t="n">
+        <v>-5256787</v>
+      </c>
+      <c r="C1234" t="n">
+        <v>1</v>
+      </c>
+      <c r="D1234" t="n">
+        <v>2</v>
+      </c>
+      <c r="E1234" t="n">
+        <v>1</v>
+      </c>
+      <c r="F1234" t="inlineStr">
+        <is>
+          <t>2026-10-08</t>
+        </is>
+      </c>
+    </row>
+    <row r="1235">
+      <c r="A1235" t="inlineStr">
+        <is>
+          <t>5f4531e9764e7d491e029746</t>
+        </is>
+      </c>
+      <c r="B1235" t="n">
+        <v>6651043</v>
+      </c>
+      <c r="C1235" t="n">
+        <v>0</v>
+      </c>
+      <c r="D1235" t="n">
+        <v>0</v>
+      </c>
+      <c r="E1235" t="n">
+        <v>0</v>
+      </c>
+      <c r="F1235" t="inlineStr">
+        <is>
+          <t>2026-10-08</t>
+        </is>
+      </c>
+    </row>
+    <row r="1236">
+      <c r="A1236" t="inlineStr">
+        <is>
+          <t>62d5bd9ad8106d3355b5bdc1</t>
+        </is>
+      </c>
+      <c r="B1236" t="n">
+        <v>281621</v>
+      </c>
+      <c r="C1236" t="n">
+        <v>1</v>
+      </c>
+      <c r="D1236" t="n">
+        <v>2</v>
+      </c>
+      <c r="E1236" t="n">
+        <v>1</v>
+      </c>
+      <c r="F1236" t="inlineStr">
+        <is>
+          <t>2026-10-08</t>
+        </is>
+      </c>
+    </row>
+    <row r="1237">
+      <c r="A1237" t="inlineStr">
+        <is>
+          <t>5f453062ec331549297ee6b8</t>
+        </is>
+      </c>
+      <c r="B1237" t="n">
+        <v>-994532</v>
+      </c>
+      <c r="C1237" t="n">
+        <v>1</v>
+      </c>
+      <c r="D1237" t="n">
+        <v>3</v>
+      </c>
+      <c r="E1237" t="n">
+        <v>0</v>
+      </c>
+      <c r="F1237" t="inlineStr">
+        <is>
+          <t>2026-10-08</t>
+        </is>
+      </c>
+    </row>
+    <row r="1238">
+      <c r="A1238" t="inlineStr">
+        <is>
+          <t>5f47aeb6c387a50bca03dd55</t>
+        </is>
+      </c>
+      <c r="B1238" t="n">
+        <v>-1436367</v>
+      </c>
+      <c r="C1238" t="n">
+        <v>0</v>
+      </c>
+      <c r="D1238" t="n">
+        <v>2</v>
+      </c>
+      <c r="E1238" t="n">
+        <v>0</v>
+      </c>
+      <c r="F1238" t="inlineStr">
+        <is>
+          <t>2026-10-08</t>
+        </is>
+      </c>
+    </row>
+    <row r="1239">
+      <c r="A1239" t="inlineStr">
+        <is>
+          <t>5f47ab5b9e2edb0bb831c703</t>
+        </is>
+      </c>
+      <c r="B1239" t="n">
+        <v>708884</v>
+      </c>
+      <c r="C1239" t="n">
+        <v>0</v>
+      </c>
+      <c r="D1239" t="n">
+        <v>1</v>
+      </c>
+      <c r="E1239" t="n">
+        <v>0</v>
+      </c>
+      <c r="F1239" t="inlineStr">
+        <is>
+          <t>2026-10-08</t>
+        </is>
+      </c>
+    </row>
+    <row r="1240">
+      <c r="A1240" t="inlineStr">
+        <is>
+          <t>5f452f5e66dd374930eb2b71</t>
+        </is>
+      </c>
+      <c r="B1240" t="n">
+        <v>-1602226</v>
+      </c>
+      <c r="C1240" t="n">
+        <v>3</v>
+      </c>
+      <c r="D1240" t="n">
+        <v>4</v>
+      </c>
+      <c r="E1240" t="n">
+        <v>4</v>
+      </c>
+      <c r="F1240" t="inlineStr">
+        <is>
+          <t>2026-10-08</t>
+        </is>
+      </c>
+    </row>
+    <row r="1241">
+      <c r="A1241" t="inlineStr">
+        <is>
+          <t>5f4530beec331549297ee6d6</t>
+        </is>
+      </c>
+      <c r="B1241" t="n">
+        <v>31548068</v>
+      </c>
+      <c r="C1241" t="n">
+        <v>0</v>
+      </c>
+      <c r="D1241" t="n">
+        <v>3</v>
+      </c>
+      <c r="E1241" t="n">
+        <v>0</v>
+      </c>
+      <c r="F1241" t="inlineStr">
+        <is>
+          <t>2026-10-08</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/datos/hechos/td_admin.xlsx
+++ b/datos/hechos/td_admin.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F1241"/>
+  <dimension ref="A1:F1249"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -30220,6 +30220,198 @@
         </is>
       </c>
     </row>
+    <row r="1242">
+      <c r="A1242" t="inlineStr">
+        <is>
+          <t>5f45324dec331549297ee971</t>
+        </is>
+      </c>
+      <c r="B1242" t="n">
+        <v>5395372</v>
+      </c>
+      <c r="C1242" t="n">
+        <v>1</v>
+      </c>
+      <c r="D1242" t="n">
+        <v>2</v>
+      </c>
+      <c r="E1242" t="n">
+        <v>1</v>
+      </c>
+      <c r="F1242" t="inlineStr">
+        <is>
+          <t>2026-10-09</t>
+        </is>
+      </c>
+    </row>
+    <row r="1243">
+      <c r="A1243" t="inlineStr">
+        <is>
+          <t>5f4531e9764e7d491e029746</t>
+        </is>
+      </c>
+      <c r="B1243" t="n">
+        <v>9126915</v>
+      </c>
+      <c r="C1243" t="n">
+        <v>0</v>
+      </c>
+      <c r="D1243" t="n">
+        <v>0</v>
+      </c>
+      <c r="E1243" t="n">
+        <v>0</v>
+      </c>
+      <c r="F1243" t="inlineStr">
+        <is>
+          <t>2026-10-09</t>
+        </is>
+      </c>
+    </row>
+    <row r="1244">
+      <c r="A1244" t="inlineStr">
+        <is>
+          <t>62d5bd9ad8106d3355b5bdc1</t>
+        </is>
+      </c>
+      <c r="B1244" t="n">
+        <v>1621</v>
+      </c>
+      <c r="C1244" t="n">
+        <v>1</v>
+      </c>
+      <c r="D1244" t="n">
+        <v>2</v>
+      </c>
+      <c r="E1244" t="n">
+        <v>1</v>
+      </c>
+      <c r="F1244" t="inlineStr">
+        <is>
+          <t>2026-10-09</t>
+        </is>
+      </c>
+    </row>
+    <row r="1245">
+      <c r="A1245" t="inlineStr">
+        <is>
+          <t>5f453062ec331549297ee6b8</t>
+        </is>
+      </c>
+      <c r="B1245" t="n">
+        <v>-714532</v>
+      </c>
+      <c r="C1245" t="n">
+        <v>1</v>
+      </c>
+      <c r="D1245" t="n">
+        <v>3</v>
+      </c>
+      <c r="E1245" t="n">
+        <v>0</v>
+      </c>
+      <c r="F1245" t="inlineStr">
+        <is>
+          <t>2026-10-09</t>
+        </is>
+      </c>
+    </row>
+    <row r="1246">
+      <c r="A1246" t="inlineStr">
+        <is>
+          <t>5f47aeb6c387a50bca03dd55</t>
+        </is>
+      </c>
+      <c r="B1246" t="n">
+        <v>4267683</v>
+      </c>
+      <c r="C1246" t="n">
+        <v>0</v>
+      </c>
+      <c r="D1246" t="n">
+        <v>2</v>
+      </c>
+      <c r="E1246" t="n">
+        <v>0</v>
+      </c>
+      <c r="F1246" t="inlineStr">
+        <is>
+          <t>2026-10-09</t>
+        </is>
+      </c>
+    </row>
+    <row r="1247">
+      <c r="A1247" t="inlineStr">
+        <is>
+          <t>5f47ab5b9e2edb0bb831c703</t>
+        </is>
+      </c>
+      <c r="B1247" t="n">
+        <v>678239</v>
+      </c>
+      <c r="C1247" t="n">
+        <v>0</v>
+      </c>
+      <c r="D1247" t="n">
+        <v>1</v>
+      </c>
+      <c r="E1247" t="n">
+        <v>0</v>
+      </c>
+      <c r="F1247" t="inlineStr">
+        <is>
+          <t>2026-10-09</t>
+        </is>
+      </c>
+    </row>
+    <row r="1248">
+      <c r="A1248" t="inlineStr">
+        <is>
+          <t>5f452f5e66dd374930eb2b71</t>
+        </is>
+      </c>
+      <c r="B1248" t="n">
+        <v>4743445</v>
+      </c>
+      <c r="C1248" t="n">
+        <v>3</v>
+      </c>
+      <c r="D1248" t="n">
+        <v>4</v>
+      </c>
+      <c r="E1248" t="n">
+        <v>4</v>
+      </c>
+      <c r="F1248" t="inlineStr">
+        <is>
+          <t>2026-10-09</t>
+        </is>
+      </c>
+    </row>
+    <row r="1249">
+      <c r="A1249" t="inlineStr">
+        <is>
+          <t>5f4530beec331549297ee6d6</t>
+        </is>
+      </c>
+      <c r="B1249" t="n">
+        <v>31548068</v>
+      </c>
+      <c r="C1249" t="n">
+        <v>0</v>
+      </c>
+      <c r="D1249" t="n">
+        <v>3</v>
+      </c>
+      <c r="E1249" t="n">
+        <v>0</v>
+      </c>
+      <c r="F1249" t="inlineStr">
+        <is>
+          <t>2026-10-09</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/datos/hechos/td_admin.xlsx
+++ b/datos/hechos/td_admin.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F1249"/>
+  <dimension ref="A1:F1257"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -30412,6 +30412,198 @@
         </is>
       </c>
     </row>
+    <row r="1250">
+      <c r="A1250" t="inlineStr">
+        <is>
+          <t>5f45324dec331549297ee971</t>
+        </is>
+      </c>
+      <c r="B1250" t="n">
+        <v>-25504628</v>
+      </c>
+      <c r="C1250" t="n">
+        <v>1</v>
+      </c>
+      <c r="D1250" t="n">
+        <v>2</v>
+      </c>
+      <c r="E1250" t="n">
+        <v>1</v>
+      </c>
+      <c r="F1250" t="inlineStr">
+        <is>
+          <t>2026-10-10</t>
+        </is>
+      </c>
+    </row>
+    <row r="1251">
+      <c r="A1251" t="inlineStr">
+        <is>
+          <t>5f4531e9764e7d491e029746</t>
+        </is>
+      </c>
+      <c r="B1251" t="n">
+        <v>9126915</v>
+      </c>
+      <c r="C1251" t="n">
+        <v>0</v>
+      </c>
+      <c r="D1251" t="n">
+        <v>0</v>
+      </c>
+      <c r="E1251" t="n">
+        <v>0</v>
+      </c>
+      <c r="F1251" t="inlineStr">
+        <is>
+          <t>2026-10-10</t>
+        </is>
+      </c>
+    </row>
+    <row r="1252">
+      <c r="A1252" t="inlineStr">
+        <is>
+          <t>62d5bd9ad8106d3355b5bdc1</t>
+        </is>
+      </c>
+      <c r="B1252" t="n">
+        <v>-3610523</v>
+      </c>
+      <c r="C1252" t="n">
+        <v>1</v>
+      </c>
+      <c r="D1252" t="n">
+        <v>2</v>
+      </c>
+      <c r="E1252" t="n">
+        <v>1</v>
+      </c>
+      <c r="F1252" t="inlineStr">
+        <is>
+          <t>2026-10-10</t>
+        </is>
+      </c>
+    </row>
+    <row r="1253">
+      <c r="A1253" t="inlineStr">
+        <is>
+          <t>5f453062ec331549297ee6b8</t>
+        </is>
+      </c>
+      <c r="B1253" t="n">
+        <v>841588</v>
+      </c>
+      <c r="C1253" t="n">
+        <v>1</v>
+      </c>
+      <c r="D1253" t="n">
+        <v>3</v>
+      </c>
+      <c r="E1253" t="n">
+        <v>0</v>
+      </c>
+      <c r="F1253" t="inlineStr">
+        <is>
+          <t>2026-10-10</t>
+        </is>
+      </c>
+    </row>
+    <row r="1254">
+      <c r="A1254" t="inlineStr">
+        <is>
+          <t>5f47aeb6c387a50bca03dd55</t>
+        </is>
+      </c>
+      <c r="B1254" t="n">
+        <v>4267683</v>
+      </c>
+      <c r="C1254" t="n">
+        <v>0</v>
+      </c>
+      <c r="D1254" t="n">
+        <v>2</v>
+      </c>
+      <c r="E1254" t="n">
+        <v>0</v>
+      </c>
+      <c r="F1254" t="inlineStr">
+        <is>
+          <t>2026-10-10</t>
+        </is>
+      </c>
+    </row>
+    <row r="1255">
+      <c r="A1255" t="inlineStr">
+        <is>
+          <t>5f47ab5b9e2edb0bb831c703</t>
+        </is>
+      </c>
+      <c r="B1255" t="n">
+        <v>-1331862</v>
+      </c>
+      <c r="C1255" t="n">
+        <v>0</v>
+      </c>
+      <c r="D1255" t="n">
+        <v>1</v>
+      </c>
+      <c r="E1255" t="n">
+        <v>0</v>
+      </c>
+      <c r="F1255" t="inlineStr">
+        <is>
+          <t>2026-10-10</t>
+        </is>
+      </c>
+    </row>
+    <row r="1256">
+      <c r="A1256" t="inlineStr">
+        <is>
+          <t>5f452f5e66dd374930eb2b71</t>
+        </is>
+      </c>
+      <c r="B1256" t="n">
+        <v>4743445</v>
+      </c>
+      <c r="C1256" t="n">
+        <v>3</v>
+      </c>
+      <c r="D1256" t="n">
+        <v>4</v>
+      </c>
+      <c r="E1256" t="n">
+        <v>4</v>
+      </c>
+      <c r="F1256" t="inlineStr">
+        <is>
+          <t>2026-10-10</t>
+        </is>
+      </c>
+    </row>
+    <row r="1257">
+      <c r="A1257" t="inlineStr">
+        <is>
+          <t>5f4530beec331549297ee6d6</t>
+        </is>
+      </c>
+      <c r="B1257" t="n">
+        <v>31548068</v>
+      </c>
+      <c r="C1257" t="n">
+        <v>0</v>
+      </c>
+      <c r="D1257" t="n">
+        <v>3</v>
+      </c>
+      <c r="E1257" t="n">
+        <v>0</v>
+      </c>
+      <c r="F1257" t="inlineStr">
+        <is>
+          <t>2026-10-10</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/datos/hechos/td_admin.xlsx
+++ b/datos/hechos/td_admin.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F1257"/>
+  <dimension ref="A1:F1265"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -30604,6 +30604,198 @@
         </is>
       </c>
     </row>
+    <row r="1258">
+      <c r="A1258" t="inlineStr">
+        <is>
+          <t>5f45324dec331549297ee971</t>
+        </is>
+      </c>
+      <c r="B1258" t="n">
+        <v>-6384153</v>
+      </c>
+      <c r="C1258" t="n">
+        <v>1</v>
+      </c>
+      <c r="D1258" t="n">
+        <v>2</v>
+      </c>
+      <c r="E1258" t="n">
+        <v>1</v>
+      </c>
+      <c r="F1258" t="inlineStr">
+        <is>
+          <t>2026-10-11</t>
+        </is>
+      </c>
+    </row>
+    <row r="1259">
+      <c r="A1259" t="inlineStr">
+        <is>
+          <t>5f4531e9764e7d491e029746</t>
+        </is>
+      </c>
+      <c r="B1259" t="n">
+        <v>9126915</v>
+      </c>
+      <c r="C1259" t="n">
+        <v>0</v>
+      </c>
+      <c r="D1259" t="n">
+        <v>0</v>
+      </c>
+      <c r="E1259" t="n">
+        <v>0</v>
+      </c>
+      <c r="F1259" t="inlineStr">
+        <is>
+          <t>2026-10-11</t>
+        </is>
+      </c>
+    </row>
+    <row r="1260">
+      <c r="A1260" t="inlineStr">
+        <is>
+          <t>62d5bd9ad8106d3355b5bdc1</t>
+        </is>
+      </c>
+      <c r="B1260" t="n">
+        <v>6901384</v>
+      </c>
+      <c r="C1260" t="n">
+        <v>1</v>
+      </c>
+      <c r="D1260" t="n">
+        <v>2</v>
+      </c>
+      <c r="E1260" t="n">
+        <v>1</v>
+      </c>
+      <c r="F1260" t="inlineStr">
+        <is>
+          <t>2026-10-11</t>
+        </is>
+      </c>
+    </row>
+    <row r="1261">
+      <c r="A1261" t="inlineStr">
+        <is>
+          <t>5f453062ec331549297ee6b8</t>
+        </is>
+      </c>
+      <c r="B1261" t="n">
+        <v>13938796</v>
+      </c>
+      <c r="C1261" t="n">
+        <v>1</v>
+      </c>
+      <c r="D1261" t="n">
+        <v>3</v>
+      </c>
+      <c r="E1261" t="n">
+        <v>0</v>
+      </c>
+      <c r="F1261" t="inlineStr">
+        <is>
+          <t>2026-10-11</t>
+        </is>
+      </c>
+    </row>
+    <row r="1262">
+      <c r="A1262" t="inlineStr">
+        <is>
+          <t>5f47aeb6c387a50bca03dd55</t>
+        </is>
+      </c>
+      <c r="B1262" t="n">
+        <v>-256714</v>
+      </c>
+      <c r="C1262" t="n">
+        <v>0</v>
+      </c>
+      <c r="D1262" t="n">
+        <v>2</v>
+      </c>
+      <c r="E1262" t="n">
+        <v>0</v>
+      </c>
+      <c r="F1262" t="inlineStr">
+        <is>
+          <t>2026-10-11</t>
+        </is>
+      </c>
+    </row>
+    <row r="1263">
+      <c r="A1263" t="inlineStr">
+        <is>
+          <t>5f47ab5b9e2edb0bb831c703</t>
+        </is>
+      </c>
+      <c r="B1263" t="n">
+        <v>-1331862</v>
+      </c>
+      <c r="C1263" t="n">
+        <v>0</v>
+      </c>
+      <c r="D1263" t="n">
+        <v>1</v>
+      </c>
+      <c r="E1263" t="n">
+        <v>0</v>
+      </c>
+      <c r="F1263" t="inlineStr">
+        <is>
+          <t>2026-10-11</t>
+        </is>
+      </c>
+    </row>
+    <row r="1264">
+      <c r="A1264" t="inlineStr">
+        <is>
+          <t>5f452f5e66dd374930eb2b71</t>
+        </is>
+      </c>
+      <c r="B1264" t="n">
+        <v>4743445</v>
+      </c>
+      <c r="C1264" t="n">
+        <v>3</v>
+      </c>
+      <c r="D1264" t="n">
+        <v>4</v>
+      </c>
+      <c r="E1264" t="n">
+        <v>4</v>
+      </c>
+      <c r="F1264" t="inlineStr">
+        <is>
+          <t>2026-10-11</t>
+        </is>
+      </c>
+    </row>
+    <row r="1265">
+      <c r="A1265" t="inlineStr">
+        <is>
+          <t>5f4530beec331549297ee6d6</t>
+        </is>
+      </c>
+      <c r="B1265" t="n">
+        <v>31548068</v>
+      </c>
+      <c r="C1265" t="n">
+        <v>0</v>
+      </c>
+      <c r="D1265" t="n">
+        <v>3</v>
+      </c>
+      <c r="E1265" t="n">
+        <v>0</v>
+      </c>
+      <c r="F1265" t="inlineStr">
+        <is>
+          <t>2026-10-11</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/datos/hechos/td_admin.xlsx
+++ b/datos/hechos/td_admin.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F1265"/>
+  <dimension ref="A1:F1273"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -30796,6 +30796,198 @@
         </is>
       </c>
     </row>
+    <row r="1266">
+      <c r="A1266" t="inlineStr">
+        <is>
+          <t>5f45324dec331549297ee971</t>
+        </is>
+      </c>
+      <c r="B1266" t="n">
+        <v>-2439099</v>
+      </c>
+      <c r="C1266" t="n">
+        <v>1</v>
+      </c>
+      <c r="D1266" t="n">
+        <v>2</v>
+      </c>
+      <c r="E1266" t="n">
+        <v>1</v>
+      </c>
+      <c r="F1266" t="inlineStr">
+        <is>
+          <t>2026-10-12</t>
+        </is>
+      </c>
+    </row>
+    <row r="1267">
+      <c r="A1267" t="inlineStr">
+        <is>
+          <t>5f4531e9764e7d491e029746</t>
+        </is>
+      </c>
+      <c r="B1267" t="n">
+        <v>9126915</v>
+      </c>
+      <c r="C1267" t="n">
+        <v>0</v>
+      </c>
+      <c r="D1267" t="n">
+        <v>0</v>
+      </c>
+      <c r="E1267" t="n">
+        <v>0</v>
+      </c>
+      <c r="F1267" t="inlineStr">
+        <is>
+          <t>2026-10-12</t>
+        </is>
+      </c>
+    </row>
+    <row r="1268">
+      <c r="A1268" t="inlineStr">
+        <is>
+          <t>62d5bd9ad8106d3355b5bdc1</t>
+        </is>
+      </c>
+      <c r="B1268" t="n">
+        <v>6901384</v>
+      </c>
+      <c r="C1268" t="n">
+        <v>1</v>
+      </c>
+      <c r="D1268" t="n">
+        <v>2</v>
+      </c>
+      <c r="E1268" t="n">
+        <v>1</v>
+      </c>
+      <c r="F1268" t="inlineStr">
+        <is>
+          <t>2026-10-12</t>
+        </is>
+      </c>
+    </row>
+    <row r="1269">
+      <c r="A1269" t="inlineStr">
+        <is>
+          <t>5f453062ec331549297ee6b8</t>
+        </is>
+      </c>
+      <c r="B1269" t="n">
+        <v>571599</v>
+      </c>
+      <c r="C1269" t="n">
+        <v>1</v>
+      </c>
+      <c r="D1269" t="n">
+        <v>3</v>
+      </c>
+      <c r="E1269" t="n">
+        <v>0</v>
+      </c>
+      <c r="F1269" t="inlineStr">
+        <is>
+          <t>2026-10-12</t>
+        </is>
+      </c>
+    </row>
+    <row r="1270">
+      <c r="A1270" t="inlineStr">
+        <is>
+          <t>5f47aeb6c387a50bca03dd55</t>
+        </is>
+      </c>
+      <c r="B1270" t="n">
+        <v>-256714</v>
+      </c>
+      <c r="C1270" t="n">
+        <v>0</v>
+      </c>
+      <c r="D1270" t="n">
+        <v>2</v>
+      </c>
+      <c r="E1270" t="n">
+        <v>0</v>
+      </c>
+      <c r="F1270" t="inlineStr">
+        <is>
+          <t>2026-10-12</t>
+        </is>
+      </c>
+    </row>
+    <row r="1271">
+      <c r="A1271" t="inlineStr">
+        <is>
+          <t>5f47ab5b9e2edb0bb831c703</t>
+        </is>
+      </c>
+      <c r="B1271" t="n">
+        <v>-1331862</v>
+      </c>
+      <c r="C1271" t="n">
+        <v>0</v>
+      </c>
+      <c r="D1271" t="n">
+        <v>1</v>
+      </c>
+      <c r="E1271" t="n">
+        <v>0</v>
+      </c>
+      <c r="F1271" t="inlineStr">
+        <is>
+          <t>2026-10-12</t>
+        </is>
+      </c>
+    </row>
+    <row r="1272">
+      <c r="A1272" t="inlineStr">
+        <is>
+          <t>5f452f5e66dd374930eb2b71</t>
+        </is>
+      </c>
+      <c r="B1272" t="n">
+        <v>4743445</v>
+      </c>
+      <c r="C1272" t="n">
+        <v>3</v>
+      </c>
+      <c r="D1272" t="n">
+        <v>4</v>
+      </c>
+      <c r="E1272" t="n">
+        <v>4</v>
+      </c>
+      <c r="F1272" t="inlineStr">
+        <is>
+          <t>2026-10-12</t>
+        </is>
+      </c>
+    </row>
+    <row r="1273">
+      <c r="A1273" t="inlineStr">
+        <is>
+          <t>5f4530beec331549297ee6d6</t>
+        </is>
+      </c>
+      <c r="B1273" t="n">
+        <v>31548068</v>
+      </c>
+      <c r="C1273" t="n">
+        <v>0</v>
+      </c>
+      <c r="D1273" t="n">
+        <v>3</v>
+      </c>
+      <c r="E1273" t="n">
+        <v>0</v>
+      </c>
+      <c r="F1273" t="inlineStr">
+        <is>
+          <t>2026-10-12</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/datos/hechos/td_admin.xlsx
+++ b/datos/hechos/td_admin.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F1273"/>
+  <dimension ref="A1:F1281"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -30988,6 +30988,198 @@
         </is>
       </c>
     </row>
+    <row r="1274">
+      <c r="A1274" t="inlineStr">
+        <is>
+          <t>5f45324dec331549297ee971</t>
+        </is>
+      </c>
+      <c r="B1274" t="n">
+        <v>74901.00000000047</v>
+      </c>
+      <c r="C1274" t="n">
+        <v>1</v>
+      </c>
+      <c r="D1274" t="n">
+        <v>2</v>
+      </c>
+      <c r="E1274" t="n">
+        <v>1</v>
+      </c>
+      <c r="F1274" t="inlineStr">
+        <is>
+          <t>2026-10-13</t>
+        </is>
+      </c>
+    </row>
+    <row r="1275">
+      <c r="A1275" t="inlineStr">
+        <is>
+          <t>5f4531e9764e7d491e029746</t>
+        </is>
+      </c>
+      <c r="B1275" t="n">
+        <v>10929915</v>
+      </c>
+      <c r="C1275" t="n">
+        <v>0</v>
+      </c>
+      <c r="D1275" t="n">
+        <v>0</v>
+      </c>
+      <c r="E1275" t="n">
+        <v>0</v>
+      </c>
+      <c r="F1275" t="inlineStr">
+        <is>
+          <t>2026-10-13</t>
+        </is>
+      </c>
+    </row>
+    <row r="1276">
+      <c r="A1276" t="inlineStr">
+        <is>
+          <t>62d5bd9ad8106d3355b5bdc1</t>
+        </is>
+      </c>
+      <c r="B1276" t="n">
+        <v>8821384</v>
+      </c>
+      <c r="C1276" t="n">
+        <v>1</v>
+      </c>
+      <c r="D1276" t="n">
+        <v>2</v>
+      </c>
+      <c r="E1276" t="n">
+        <v>1</v>
+      </c>
+      <c r="F1276" t="inlineStr">
+        <is>
+          <t>2026-10-13</t>
+        </is>
+      </c>
+    </row>
+    <row r="1277">
+      <c r="A1277" t="inlineStr">
+        <is>
+          <t>5f453062ec331549297ee6b8</t>
+        </is>
+      </c>
+      <c r="B1277" t="n">
+        <v>-10055402</v>
+      </c>
+      <c r="C1277" t="n">
+        <v>1</v>
+      </c>
+      <c r="D1277" t="n">
+        <v>3</v>
+      </c>
+      <c r="E1277" t="n">
+        <v>0</v>
+      </c>
+      <c r="F1277" t="inlineStr">
+        <is>
+          <t>2026-10-13</t>
+        </is>
+      </c>
+    </row>
+    <row r="1278">
+      <c r="A1278" t="inlineStr">
+        <is>
+          <t>5f47aeb6c387a50bca03dd55</t>
+        </is>
+      </c>
+      <c r="B1278" t="n">
+        <v>1375286</v>
+      </c>
+      <c r="C1278" t="n">
+        <v>0</v>
+      </c>
+      <c r="D1278" t="n">
+        <v>2</v>
+      </c>
+      <c r="E1278" t="n">
+        <v>0</v>
+      </c>
+      <c r="F1278" t="inlineStr">
+        <is>
+          <t>2026-10-13</t>
+        </is>
+      </c>
+    </row>
+    <row r="1279">
+      <c r="A1279" t="inlineStr">
+        <is>
+          <t>5f47ab5b9e2edb0bb831c703</t>
+        </is>
+      </c>
+      <c r="B1279" t="n">
+        <v>3525886</v>
+      </c>
+      <c r="C1279" t="n">
+        <v>0</v>
+      </c>
+      <c r="D1279" t="n">
+        <v>1</v>
+      </c>
+      <c r="E1279" t="n">
+        <v>0</v>
+      </c>
+      <c r="F1279" t="inlineStr">
+        <is>
+          <t>2026-10-13</t>
+        </is>
+      </c>
+    </row>
+    <row r="1280">
+      <c r="A1280" t="inlineStr">
+        <is>
+          <t>5f4530beec331549297ee6d6</t>
+        </is>
+      </c>
+      <c r="B1280" t="n">
+        <v>33804068</v>
+      </c>
+      <c r="C1280" t="n">
+        <v>0</v>
+      </c>
+      <c r="D1280" t="n">
+        <v>3</v>
+      </c>
+      <c r="E1280" t="n">
+        <v>0</v>
+      </c>
+      <c r="F1280" t="inlineStr">
+        <is>
+          <t>2026-10-13</t>
+        </is>
+      </c>
+    </row>
+    <row r="1281">
+      <c r="A1281" t="inlineStr">
+        <is>
+          <t>5f452f5e66dd374930eb2b71</t>
+        </is>
+      </c>
+      <c r="B1281" t="n">
+        <v>91134</v>
+      </c>
+      <c r="C1281" t="n">
+        <v>3</v>
+      </c>
+      <c r="D1281" t="n">
+        <v>4</v>
+      </c>
+      <c r="E1281" t="n">
+        <v>4</v>
+      </c>
+      <c r="F1281" t="inlineStr">
+        <is>
+          <t>2026-10-13</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/datos/hechos/td_admin.xlsx
+++ b/datos/hechos/td_admin.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F1281"/>
+  <dimension ref="A1:F1289"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -31180,6 +31180,198 @@
         </is>
       </c>
     </row>
+    <row r="1282">
+      <c r="A1282" t="inlineStr">
+        <is>
+          <t>5f45324dec331549297ee971</t>
+        </is>
+      </c>
+      <c r="B1282" t="n">
+        <v>74901.00000000047</v>
+      </c>
+      <c r="C1282" t="n">
+        <v>1</v>
+      </c>
+      <c r="D1282" t="n">
+        <v>2</v>
+      </c>
+      <c r="E1282" t="n">
+        <v>1</v>
+      </c>
+      <c r="F1282" t="inlineStr">
+        <is>
+          <t>2026-10-14</t>
+        </is>
+      </c>
+    </row>
+    <row r="1283">
+      <c r="A1283" t="inlineStr">
+        <is>
+          <t>5f4531e9764e7d491e029746</t>
+        </is>
+      </c>
+      <c r="B1283" t="n">
+        <v>10929915</v>
+      </c>
+      <c r="C1283" t="n">
+        <v>0</v>
+      </c>
+      <c r="D1283" t="n">
+        <v>0</v>
+      </c>
+      <c r="E1283" t="n">
+        <v>0</v>
+      </c>
+      <c r="F1283" t="inlineStr">
+        <is>
+          <t>2026-10-14</t>
+        </is>
+      </c>
+    </row>
+    <row r="1284">
+      <c r="A1284" t="inlineStr">
+        <is>
+          <t>62d5bd9ad8106d3355b5bdc1</t>
+        </is>
+      </c>
+      <c r="B1284" t="n">
+        <v>-17978614</v>
+      </c>
+      <c r="C1284" t="n">
+        <v>1</v>
+      </c>
+      <c r="D1284" t="n">
+        <v>2</v>
+      </c>
+      <c r="E1284" t="n">
+        <v>1</v>
+      </c>
+      <c r="F1284" t="inlineStr">
+        <is>
+          <t>2026-10-14</t>
+        </is>
+      </c>
+    </row>
+    <row r="1285">
+      <c r="A1285" t="inlineStr">
+        <is>
+          <t>5f453062ec331549297ee6b8</t>
+        </is>
+      </c>
+      <c r="B1285" t="n">
+        <v>-10055402</v>
+      </c>
+      <c r="C1285" t="n">
+        <v>1</v>
+      </c>
+      <c r="D1285" t="n">
+        <v>3</v>
+      </c>
+      <c r="E1285" t="n">
+        <v>0</v>
+      </c>
+      <c r="F1285" t="inlineStr">
+        <is>
+          <t>2026-10-14</t>
+        </is>
+      </c>
+    </row>
+    <row r="1286">
+      <c r="A1286" t="inlineStr">
+        <is>
+          <t>5f47aeb6c387a50bca03dd55</t>
+        </is>
+      </c>
+      <c r="B1286" t="n">
+        <v>1375286</v>
+      </c>
+      <c r="C1286" t="n">
+        <v>0</v>
+      </c>
+      <c r="D1286" t="n">
+        <v>2</v>
+      </c>
+      <c r="E1286" t="n">
+        <v>0</v>
+      </c>
+      <c r="F1286" t="inlineStr">
+        <is>
+          <t>2026-10-14</t>
+        </is>
+      </c>
+    </row>
+    <row r="1287">
+      <c r="A1287" t="inlineStr">
+        <is>
+          <t>5f47ab5b9e2edb0bb831c703</t>
+        </is>
+      </c>
+      <c r="B1287" t="n">
+        <v>-8290326</v>
+      </c>
+      <c r="C1287" t="n">
+        <v>0</v>
+      </c>
+      <c r="D1287" t="n">
+        <v>1</v>
+      </c>
+      <c r="E1287" t="n">
+        <v>0</v>
+      </c>
+      <c r="F1287" t="inlineStr">
+        <is>
+          <t>2026-10-14</t>
+        </is>
+      </c>
+    </row>
+    <row r="1288">
+      <c r="A1288" t="inlineStr">
+        <is>
+          <t>5f4530beec331549297ee6d6</t>
+        </is>
+      </c>
+      <c r="B1288" t="n">
+        <v>33804068</v>
+      </c>
+      <c r="C1288" t="n">
+        <v>0</v>
+      </c>
+      <c r="D1288" t="n">
+        <v>3</v>
+      </c>
+      <c r="E1288" t="n">
+        <v>0</v>
+      </c>
+      <c r="F1288" t="inlineStr">
+        <is>
+          <t>2026-10-14</t>
+        </is>
+      </c>
+    </row>
+    <row r="1289">
+      <c r="A1289" t="inlineStr">
+        <is>
+          <t>5f452f5e66dd374930eb2b71</t>
+        </is>
+      </c>
+      <c r="B1289" t="n">
+        <v>91134</v>
+      </c>
+      <c r="C1289" t="n">
+        <v>3</v>
+      </c>
+      <c r="D1289" t="n">
+        <v>4</v>
+      </c>
+      <c r="E1289" t="n">
+        <v>4</v>
+      </c>
+      <c r="F1289" t="inlineStr">
+        <is>
+          <t>2026-10-14</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/datos/hechos/td_admin.xlsx
+++ b/datos/hechos/td_admin.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F1289"/>
+  <dimension ref="A1:F1297"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -31372,6 +31372,198 @@
         </is>
       </c>
     </row>
+    <row r="1290">
+      <c r="A1290" t="inlineStr">
+        <is>
+          <t>5f45324dec331549297ee971</t>
+        </is>
+      </c>
+      <c r="B1290" t="n">
+        <v>-8340003</v>
+      </c>
+      <c r="C1290" t="n">
+        <v>1</v>
+      </c>
+      <c r="D1290" t="n">
+        <v>2</v>
+      </c>
+      <c r="E1290" t="n">
+        <v>1</v>
+      </c>
+      <c r="F1290" t="inlineStr">
+        <is>
+          <t>2026-10-15</t>
+        </is>
+      </c>
+    </row>
+    <row r="1291">
+      <c r="A1291" t="inlineStr">
+        <is>
+          <t>5f4531e9764e7d491e029746</t>
+        </is>
+      </c>
+      <c r="B1291" t="n">
+        <v>10929915</v>
+      </c>
+      <c r="C1291" t="n">
+        <v>0</v>
+      </c>
+      <c r="D1291" t="n">
+        <v>0</v>
+      </c>
+      <c r="E1291" t="n">
+        <v>0</v>
+      </c>
+      <c r="F1291" t="inlineStr">
+        <is>
+          <t>2026-10-15</t>
+        </is>
+      </c>
+    </row>
+    <row r="1292">
+      <c r="A1292" t="inlineStr">
+        <is>
+          <t>62d5bd9ad8106d3355b5bdc1</t>
+        </is>
+      </c>
+      <c r="B1292" t="n">
+        <v>-17978614</v>
+      </c>
+      <c r="C1292" t="n">
+        <v>1</v>
+      </c>
+      <c r="D1292" t="n">
+        <v>2</v>
+      </c>
+      <c r="E1292" t="n">
+        <v>1</v>
+      </c>
+      <c r="F1292" t="inlineStr">
+        <is>
+          <t>2026-10-15</t>
+        </is>
+      </c>
+    </row>
+    <row r="1293">
+      <c r="A1293" t="inlineStr">
+        <is>
+          <t>5f453062ec331549297ee6b8</t>
+        </is>
+      </c>
+      <c r="B1293" t="n">
+        <v>-1840039</v>
+      </c>
+      <c r="C1293" t="n">
+        <v>1</v>
+      </c>
+      <c r="D1293" t="n">
+        <v>3</v>
+      </c>
+      <c r="E1293" t="n">
+        <v>0</v>
+      </c>
+      <c r="F1293" t="inlineStr">
+        <is>
+          <t>2026-10-15</t>
+        </is>
+      </c>
+    </row>
+    <row r="1294">
+      <c r="A1294" t="inlineStr">
+        <is>
+          <t>5f47aeb6c387a50bca03dd55</t>
+        </is>
+      </c>
+      <c r="B1294" t="n">
+        <v>1375286</v>
+      </c>
+      <c r="C1294" t="n">
+        <v>0</v>
+      </c>
+      <c r="D1294" t="n">
+        <v>2</v>
+      </c>
+      <c r="E1294" t="n">
+        <v>0</v>
+      </c>
+      <c r="F1294" t="inlineStr">
+        <is>
+          <t>2026-10-15</t>
+        </is>
+      </c>
+    </row>
+    <row r="1295">
+      <c r="A1295" t="inlineStr">
+        <is>
+          <t>5f47ab5b9e2edb0bb831c703</t>
+        </is>
+      </c>
+      <c r="B1295" t="n">
+        <v>1995903</v>
+      </c>
+      <c r="C1295" t="n">
+        <v>0</v>
+      </c>
+      <c r="D1295" t="n">
+        <v>1</v>
+      </c>
+      <c r="E1295" t="n">
+        <v>0</v>
+      </c>
+      <c r="F1295" t="inlineStr">
+        <is>
+          <t>2026-10-15</t>
+        </is>
+      </c>
+    </row>
+    <row r="1296">
+      <c r="A1296" t="inlineStr">
+        <is>
+          <t>5f4530beec331549297ee6d6</t>
+        </is>
+      </c>
+      <c r="B1296" t="n">
+        <v>33804068</v>
+      </c>
+      <c r="C1296" t="n">
+        <v>0</v>
+      </c>
+      <c r="D1296" t="n">
+        <v>3</v>
+      </c>
+      <c r="E1296" t="n">
+        <v>0</v>
+      </c>
+      <c r="F1296" t="inlineStr">
+        <is>
+          <t>2026-10-15</t>
+        </is>
+      </c>
+    </row>
+    <row r="1297">
+      <c r="A1297" t="inlineStr">
+        <is>
+          <t>5f452f5e66dd374930eb2b71</t>
+        </is>
+      </c>
+      <c r="B1297" t="n">
+        <v>91134</v>
+      </c>
+      <c r="C1297" t="n">
+        <v>3</v>
+      </c>
+      <c r="D1297" t="n">
+        <v>4</v>
+      </c>
+      <c r="E1297" t="n">
+        <v>4</v>
+      </c>
+      <c r="F1297" t="inlineStr">
+        <is>
+          <t>2026-10-15</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/datos/hechos/td_admin.xlsx
+++ b/datos/hechos/td_admin.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F1297"/>
+  <dimension ref="A1:F1305"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -31564,6 +31564,198 @@
         </is>
       </c>
     </row>
+    <row r="1298">
+      <c r="A1298" t="inlineStr">
+        <is>
+          <t>5f45324dec331549297ee971</t>
+        </is>
+      </c>
+      <c r="B1298" t="n">
+        <v>2232934</v>
+      </c>
+      <c r="C1298" t="n">
+        <v>1</v>
+      </c>
+      <c r="D1298" t="n">
+        <v>2</v>
+      </c>
+      <c r="E1298" t="n">
+        <v>1</v>
+      </c>
+      <c r="F1298" t="inlineStr">
+        <is>
+          <t>2026-10-16</t>
+        </is>
+      </c>
+    </row>
+    <row r="1299">
+      <c r="A1299" t="inlineStr">
+        <is>
+          <t>5f4531e9764e7d491e029746</t>
+        </is>
+      </c>
+      <c r="B1299" t="n">
+        <v>10929915</v>
+      </c>
+      <c r="C1299" t="n">
+        <v>0</v>
+      </c>
+      <c r="D1299" t="n">
+        <v>0</v>
+      </c>
+      <c r="E1299" t="n">
+        <v>0</v>
+      </c>
+      <c r="F1299" t="inlineStr">
+        <is>
+          <t>2026-10-16</t>
+        </is>
+      </c>
+    </row>
+    <row r="1300">
+      <c r="A1300" t="inlineStr">
+        <is>
+          <t>62d5bd9ad8106d3355b5bdc1</t>
+        </is>
+      </c>
+      <c r="B1300" t="n">
+        <v>-20278613</v>
+      </c>
+      <c r="C1300" t="n">
+        <v>1</v>
+      </c>
+      <c r="D1300" t="n">
+        <v>2</v>
+      </c>
+      <c r="E1300" t="n">
+        <v>1</v>
+      </c>
+      <c r="F1300" t="inlineStr">
+        <is>
+          <t>2026-10-16</t>
+        </is>
+      </c>
+    </row>
+    <row r="1301">
+      <c r="A1301" t="inlineStr">
+        <is>
+          <t>5f453062ec331549297ee6b8</t>
+        </is>
+      </c>
+      <c r="B1301" t="n">
+        <v>18261998</v>
+      </c>
+      <c r="C1301" t="n">
+        <v>1</v>
+      </c>
+      <c r="D1301" t="n">
+        <v>3</v>
+      </c>
+      <c r="E1301" t="n">
+        <v>0</v>
+      </c>
+      <c r="F1301" t="inlineStr">
+        <is>
+          <t>2026-10-16</t>
+        </is>
+      </c>
+    </row>
+    <row r="1302">
+      <c r="A1302" t="inlineStr">
+        <is>
+          <t>5f47aeb6c387a50bca03dd55</t>
+        </is>
+      </c>
+      <c r="B1302" t="n">
+        <v>1375286</v>
+      </c>
+      <c r="C1302" t="n">
+        <v>0</v>
+      </c>
+      <c r="D1302" t="n">
+        <v>2</v>
+      </c>
+      <c r="E1302" t="n">
+        <v>0</v>
+      </c>
+      <c r="F1302" t="inlineStr">
+        <is>
+          <t>2026-10-16</t>
+        </is>
+      </c>
+    </row>
+    <row r="1303">
+      <c r="A1303" t="inlineStr">
+        <is>
+          <t>5f47ab5b9e2edb0bb831c703</t>
+        </is>
+      </c>
+      <c r="B1303" t="n">
+        <v>1995903</v>
+      </c>
+      <c r="C1303" t="n">
+        <v>0</v>
+      </c>
+      <c r="D1303" t="n">
+        <v>1</v>
+      </c>
+      <c r="E1303" t="n">
+        <v>0</v>
+      </c>
+      <c r="F1303" t="inlineStr">
+        <is>
+          <t>2026-10-16</t>
+        </is>
+      </c>
+    </row>
+    <row r="1304">
+      <c r="A1304" t="inlineStr">
+        <is>
+          <t>5f4530beec331549297ee6d6</t>
+        </is>
+      </c>
+      <c r="B1304" t="n">
+        <v>33804068</v>
+      </c>
+      <c r="C1304" t="n">
+        <v>0</v>
+      </c>
+      <c r="D1304" t="n">
+        <v>3</v>
+      </c>
+      <c r="E1304" t="n">
+        <v>0</v>
+      </c>
+      <c r="F1304" t="inlineStr">
+        <is>
+          <t>2026-10-16</t>
+        </is>
+      </c>
+    </row>
+    <row r="1305">
+      <c r="A1305" t="inlineStr">
+        <is>
+          <t>5f452f5e66dd374930eb2b71</t>
+        </is>
+      </c>
+      <c r="B1305" t="n">
+        <v>91134</v>
+      </c>
+      <c r="C1305" t="n">
+        <v>3</v>
+      </c>
+      <c r="D1305" t="n">
+        <v>4</v>
+      </c>
+      <c r="E1305" t="n">
+        <v>4</v>
+      </c>
+      <c r="F1305" t="inlineStr">
+        <is>
+          <t>2026-10-16</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/datos/hechos/td_admin.xlsx
+++ b/datos/hechos/td_admin.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F1305"/>
+  <dimension ref="A1:F1313"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -31756,6 +31756,198 @@
         </is>
       </c>
     </row>
+    <row r="1306">
+      <c r="A1306" t="inlineStr">
+        <is>
+          <t>5f45324dec331549297ee971</t>
+        </is>
+      </c>
+      <c r="B1306" t="n">
+        <v>2232934</v>
+      </c>
+      <c r="C1306" t="n">
+        <v>1</v>
+      </c>
+      <c r="D1306" t="n">
+        <v>2</v>
+      </c>
+      <c r="E1306" t="n">
+        <v>1</v>
+      </c>
+      <c r="F1306" t="inlineStr">
+        <is>
+          <t>2026-10-17</t>
+        </is>
+      </c>
+    </row>
+    <row r="1307">
+      <c r="A1307" t="inlineStr">
+        <is>
+          <t>5f4531e9764e7d491e029746</t>
+        </is>
+      </c>
+      <c r="B1307" t="n">
+        <v>10929915</v>
+      </c>
+      <c r="C1307" t="n">
+        <v>0</v>
+      </c>
+      <c r="D1307" t="n">
+        <v>0</v>
+      </c>
+      <c r="E1307" t="n">
+        <v>0</v>
+      </c>
+      <c r="F1307" t="inlineStr">
+        <is>
+          <t>2026-10-17</t>
+        </is>
+      </c>
+    </row>
+    <row r="1308">
+      <c r="A1308" t="inlineStr">
+        <is>
+          <t>62d5bd9ad8106d3355b5bdc1</t>
+        </is>
+      </c>
+      <c r="B1308" t="n">
+        <v>-15525457</v>
+      </c>
+      <c r="C1308" t="n">
+        <v>1</v>
+      </c>
+      <c r="D1308" t="n">
+        <v>2</v>
+      </c>
+      <c r="E1308" t="n">
+        <v>1</v>
+      </c>
+      <c r="F1308" t="inlineStr">
+        <is>
+          <t>2026-10-17</t>
+        </is>
+      </c>
+    </row>
+    <row r="1309">
+      <c r="A1309" t="inlineStr">
+        <is>
+          <t>5f453062ec331549297ee6b8</t>
+        </is>
+      </c>
+      <c r="B1309" t="n">
+        <v>18261998</v>
+      </c>
+      <c r="C1309" t="n">
+        <v>1</v>
+      </c>
+      <c r="D1309" t="n">
+        <v>3</v>
+      </c>
+      <c r="E1309" t="n">
+        <v>0</v>
+      </c>
+      <c r="F1309" t="inlineStr">
+        <is>
+          <t>2026-10-17</t>
+        </is>
+      </c>
+    </row>
+    <row r="1310">
+      <c r="A1310" t="inlineStr">
+        <is>
+          <t>5f47aeb6c387a50bca03dd55</t>
+        </is>
+      </c>
+      <c r="B1310" t="n">
+        <v>1375286</v>
+      </c>
+      <c r="C1310" t="n">
+        <v>0</v>
+      </c>
+      <c r="D1310" t="n">
+        <v>2</v>
+      </c>
+      <c r="E1310" t="n">
+        <v>0</v>
+      </c>
+      <c r="F1310" t="inlineStr">
+        <is>
+          <t>2026-10-17</t>
+        </is>
+      </c>
+    </row>
+    <row r="1311">
+      <c r="A1311" t="inlineStr">
+        <is>
+          <t>5f47ab5b9e2edb0bb831c703</t>
+        </is>
+      </c>
+      <c r="B1311" t="n">
+        <v>1995903</v>
+      </c>
+      <c r="C1311" t="n">
+        <v>0</v>
+      </c>
+      <c r="D1311" t="n">
+        <v>1</v>
+      </c>
+      <c r="E1311" t="n">
+        <v>0</v>
+      </c>
+      <c r="F1311" t="inlineStr">
+        <is>
+          <t>2026-10-17</t>
+        </is>
+      </c>
+    </row>
+    <row r="1312">
+      <c r="A1312" t="inlineStr">
+        <is>
+          <t>5f4530beec331549297ee6d6</t>
+        </is>
+      </c>
+      <c r="B1312" t="n">
+        <v>33804068</v>
+      </c>
+      <c r="C1312" t="n">
+        <v>0</v>
+      </c>
+      <c r="D1312" t="n">
+        <v>3</v>
+      </c>
+      <c r="E1312" t="n">
+        <v>0</v>
+      </c>
+      <c r="F1312" t="inlineStr">
+        <is>
+          <t>2026-10-17</t>
+        </is>
+      </c>
+    </row>
+    <row r="1313">
+      <c r="A1313" t="inlineStr">
+        <is>
+          <t>5f452f5e66dd374930eb2b71</t>
+        </is>
+      </c>
+      <c r="B1313" t="n">
+        <v>91134</v>
+      </c>
+      <c r="C1313" t="n">
+        <v>3</v>
+      </c>
+      <c r="D1313" t="n">
+        <v>4</v>
+      </c>
+      <c r="E1313" t="n">
+        <v>4</v>
+      </c>
+      <c r="F1313" t="inlineStr">
+        <is>
+          <t>2026-10-17</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/datos/hechos/td_admin.xlsx
+++ b/datos/hechos/td_admin.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F1313"/>
+  <dimension ref="A1:F1321"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -31948,6 +31948,198 @@
         </is>
       </c>
     </row>
+    <row r="1314">
+      <c r="A1314" t="inlineStr">
+        <is>
+          <t>5f45324dec331549297ee971</t>
+        </is>
+      </c>
+      <c r="B1314" t="n">
+        <v>2232934</v>
+      </c>
+      <c r="C1314" t="n">
+        <v>1</v>
+      </c>
+      <c r="D1314" t="n">
+        <v>2</v>
+      </c>
+      <c r="E1314" t="n">
+        <v>1</v>
+      </c>
+      <c r="F1314" t="inlineStr">
+        <is>
+          <t>2026-10-18</t>
+        </is>
+      </c>
+    </row>
+    <row r="1315">
+      <c r="A1315" t="inlineStr">
+        <is>
+          <t>5f4531e9764e7d491e029746</t>
+        </is>
+      </c>
+      <c r="B1315" t="n">
+        <v>10929915</v>
+      </c>
+      <c r="C1315" t="n">
+        <v>0</v>
+      </c>
+      <c r="D1315" t="n">
+        <v>0</v>
+      </c>
+      <c r="E1315" t="n">
+        <v>0</v>
+      </c>
+      <c r="F1315" t="inlineStr">
+        <is>
+          <t>2026-10-18</t>
+        </is>
+      </c>
+    </row>
+    <row r="1316">
+      <c r="A1316" t="inlineStr">
+        <is>
+          <t>62d5bd9ad8106d3355b5bdc1</t>
+        </is>
+      </c>
+      <c r="B1316" t="n">
+        <v>-15525457</v>
+      </c>
+      <c r="C1316" t="n">
+        <v>1</v>
+      </c>
+      <c r="D1316" t="n">
+        <v>2</v>
+      </c>
+      <c r="E1316" t="n">
+        <v>1</v>
+      </c>
+      <c r="F1316" t="inlineStr">
+        <is>
+          <t>2026-10-18</t>
+        </is>
+      </c>
+    </row>
+    <row r="1317">
+      <c r="A1317" t="inlineStr">
+        <is>
+          <t>5f453062ec331549297ee6b8</t>
+        </is>
+      </c>
+      <c r="B1317" t="n">
+        <v>-23928489</v>
+      </c>
+      <c r="C1317" t="n">
+        <v>1</v>
+      </c>
+      <c r="D1317" t="n">
+        <v>3</v>
+      </c>
+      <c r="E1317" t="n">
+        <v>0</v>
+      </c>
+      <c r="F1317" t="inlineStr">
+        <is>
+          <t>2026-10-18</t>
+        </is>
+      </c>
+    </row>
+    <row r="1318">
+      <c r="A1318" t="inlineStr">
+        <is>
+          <t>5f47aeb6c387a50bca03dd55</t>
+        </is>
+      </c>
+      <c r="B1318" t="n">
+        <v>1375286</v>
+      </c>
+      <c r="C1318" t="n">
+        <v>0</v>
+      </c>
+      <c r="D1318" t="n">
+        <v>2</v>
+      </c>
+      <c r="E1318" t="n">
+        <v>0</v>
+      </c>
+      <c r="F1318" t="inlineStr">
+        <is>
+          <t>2026-10-18</t>
+        </is>
+      </c>
+    </row>
+    <row r="1319">
+      <c r="A1319" t="inlineStr">
+        <is>
+          <t>5f47ab5b9e2edb0bb831c703</t>
+        </is>
+      </c>
+      <c r="B1319" t="n">
+        <v>1995903</v>
+      </c>
+      <c r="C1319" t="n">
+        <v>0</v>
+      </c>
+      <c r="D1319" t="n">
+        <v>1</v>
+      </c>
+      <c r="E1319" t="n">
+        <v>0</v>
+      </c>
+      <c r="F1319" t="inlineStr">
+        <is>
+          <t>2026-10-18</t>
+        </is>
+      </c>
+    </row>
+    <row r="1320">
+      <c r="A1320" t="inlineStr">
+        <is>
+          <t>5f4530beec331549297ee6d6</t>
+        </is>
+      </c>
+      <c r="B1320" t="n">
+        <v>33804068</v>
+      </c>
+      <c r="C1320" t="n">
+        <v>0</v>
+      </c>
+      <c r="D1320" t="n">
+        <v>3</v>
+      </c>
+      <c r="E1320" t="n">
+        <v>0</v>
+      </c>
+      <c r="F1320" t="inlineStr">
+        <is>
+          <t>2026-10-18</t>
+        </is>
+      </c>
+    </row>
+    <row r="1321">
+      <c r="A1321" t="inlineStr">
+        <is>
+          <t>5f452f5e66dd374930eb2b71</t>
+        </is>
+      </c>
+      <c r="B1321" t="n">
+        <v>91134</v>
+      </c>
+      <c r="C1321" t="n">
+        <v>3</v>
+      </c>
+      <c r="D1321" t="n">
+        <v>4</v>
+      </c>
+      <c r="E1321" t="n">
+        <v>4</v>
+      </c>
+      <c r="F1321" t="inlineStr">
+        <is>
+          <t>2026-10-18</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/datos/hechos/td_admin.xlsx
+++ b/datos/hechos/td_admin.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F1321"/>
+  <dimension ref="A1:F1329"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -32140,6 +32140,198 @@
         </is>
       </c>
     </row>
+    <row r="1322">
+      <c r="A1322" t="inlineStr">
+        <is>
+          <t>5f45324dec331549297ee971</t>
+        </is>
+      </c>
+      <c r="B1322" t="n">
+        <v>12319588</v>
+      </c>
+      <c r="C1322" t="n">
+        <v>1</v>
+      </c>
+      <c r="D1322" t="n">
+        <v>2</v>
+      </c>
+      <c r="E1322" t="n">
+        <v>1</v>
+      </c>
+      <c r="F1322" t="inlineStr">
+        <is>
+          <t>2026-10-19</t>
+        </is>
+      </c>
+    </row>
+    <row r="1323">
+      <c r="A1323" t="inlineStr">
+        <is>
+          <t>5f4531e9764e7d491e029746</t>
+        </is>
+      </c>
+      <c r="B1323" t="n">
+        <v>14288441</v>
+      </c>
+      <c r="C1323" t="n">
+        <v>0</v>
+      </c>
+      <c r="D1323" t="n">
+        <v>0</v>
+      </c>
+      <c r="E1323" t="n">
+        <v>0</v>
+      </c>
+      <c r="F1323" t="inlineStr">
+        <is>
+          <t>2026-10-19</t>
+        </is>
+      </c>
+    </row>
+    <row r="1324">
+      <c r="A1324" t="inlineStr">
+        <is>
+          <t>62d5bd9ad8106d3355b5bdc1</t>
+        </is>
+      </c>
+      <c r="B1324" t="n">
+        <v>-15525457</v>
+      </c>
+      <c r="C1324" t="n">
+        <v>1</v>
+      </c>
+      <c r="D1324" t="n">
+        <v>2</v>
+      </c>
+      <c r="E1324" t="n">
+        <v>1</v>
+      </c>
+      <c r="F1324" t="inlineStr">
+        <is>
+          <t>2026-10-19</t>
+        </is>
+      </c>
+    </row>
+    <row r="1325">
+      <c r="A1325" t="inlineStr">
+        <is>
+          <t>5f453062ec331549297ee6b8</t>
+        </is>
+      </c>
+      <c r="B1325" t="n">
+        <v>-4961560</v>
+      </c>
+      <c r="C1325" t="n">
+        <v>1</v>
+      </c>
+      <c r="D1325" t="n">
+        <v>3</v>
+      </c>
+      <c r="E1325" t="n">
+        <v>0</v>
+      </c>
+      <c r="F1325" t="inlineStr">
+        <is>
+          <t>2026-10-19</t>
+        </is>
+      </c>
+    </row>
+    <row r="1326">
+      <c r="A1326" t="inlineStr">
+        <is>
+          <t>5f47aeb6c387a50bca03dd55</t>
+        </is>
+      </c>
+      <c r="B1326" t="n">
+        <v>1375286</v>
+      </c>
+      <c r="C1326" t="n">
+        <v>0</v>
+      </c>
+      <c r="D1326" t="n">
+        <v>2</v>
+      </c>
+      <c r="E1326" t="n">
+        <v>0</v>
+      </c>
+      <c r="F1326" t="inlineStr">
+        <is>
+          <t>2026-10-19</t>
+        </is>
+      </c>
+    </row>
+    <row r="1327">
+      <c r="A1327" t="inlineStr">
+        <is>
+          <t>5f47ab5b9e2edb0bb831c703</t>
+        </is>
+      </c>
+      <c r="B1327" t="n">
+        <v>1995903</v>
+      </c>
+      <c r="C1327" t="n">
+        <v>0</v>
+      </c>
+      <c r="D1327" t="n">
+        <v>1</v>
+      </c>
+      <c r="E1327" t="n">
+        <v>0</v>
+      </c>
+      <c r="F1327" t="inlineStr">
+        <is>
+          <t>2026-10-19</t>
+        </is>
+      </c>
+    </row>
+    <row r="1328">
+      <c r="A1328" t="inlineStr">
+        <is>
+          <t>5f4530beec331549297ee6d6</t>
+        </is>
+      </c>
+      <c r="B1328" t="n">
+        <v>48569089</v>
+      </c>
+      <c r="C1328" t="n">
+        <v>0</v>
+      </c>
+      <c r="D1328" t="n">
+        <v>3</v>
+      </c>
+      <c r="E1328" t="n">
+        <v>0</v>
+      </c>
+      <c r="F1328" t="inlineStr">
+        <is>
+          <t>2026-10-19</t>
+        </is>
+      </c>
+    </row>
+    <row r="1329">
+      <c r="A1329" t="inlineStr">
+        <is>
+          <t>5f452f5e66dd374930eb2b71</t>
+        </is>
+      </c>
+      <c r="B1329" t="n">
+        <v>91134</v>
+      </c>
+      <c r="C1329" t="n">
+        <v>3</v>
+      </c>
+      <c r="D1329" t="n">
+        <v>4</v>
+      </c>
+      <c r="E1329" t="n">
+        <v>4</v>
+      </c>
+      <c r="F1329" t="inlineStr">
+        <is>
+          <t>2026-10-19</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/datos/hechos/td_admin.xlsx
+++ b/datos/hechos/td_admin.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F1329"/>
+  <dimension ref="A1:F1337"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -32332,6 +32332,198 @@
         </is>
       </c>
     </row>
+    <row r="1330">
+      <c r="A1330" t="inlineStr">
+        <is>
+          <t>5f45324dec331549297ee971</t>
+        </is>
+      </c>
+      <c r="B1330" t="n">
+        <v>10573821</v>
+      </c>
+      <c r="C1330" t="n">
+        <v>1</v>
+      </c>
+      <c r="D1330" t="n">
+        <v>2</v>
+      </c>
+      <c r="E1330" t="n">
+        <v>1</v>
+      </c>
+      <c r="F1330" t="inlineStr">
+        <is>
+          <t>2026-10-20</t>
+        </is>
+      </c>
+    </row>
+    <row r="1331">
+      <c r="A1331" t="inlineStr">
+        <is>
+          <t>5f4531e9764e7d491e029746</t>
+        </is>
+      </c>
+      <c r="B1331" t="n">
+        <v>58594146</v>
+      </c>
+      <c r="C1331" t="n">
+        <v>0</v>
+      </c>
+      <c r="D1331" t="n">
+        <v>0</v>
+      </c>
+      <c r="E1331" t="n">
+        <v>0</v>
+      </c>
+      <c r="F1331" t="inlineStr">
+        <is>
+          <t>2026-10-20</t>
+        </is>
+      </c>
+    </row>
+    <row r="1332">
+      <c r="A1332" t="inlineStr">
+        <is>
+          <t>62d5bd9ad8106d3355b5bdc1</t>
+        </is>
+      </c>
+      <c r="B1332" t="n">
+        <v>-17664752</v>
+      </c>
+      <c r="C1332" t="n">
+        <v>1</v>
+      </c>
+      <c r="D1332" t="n">
+        <v>2</v>
+      </c>
+      <c r="E1332" t="n">
+        <v>1</v>
+      </c>
+      <c r="F1332" t="inlineStr">
+        <is>
+          <t>2026-10-20</t>
+        </is>
+      </c>
+    </row>
+    <row r="1333">
+      <c r="A1333" t="inlineStr">
+        <is>
+          <t>5f453062ec331549297ee6b8</t>
+        </is>
+      </c>
+      <c r="B1333" t="n">
+        <v>15175182</v>
+      </c>
+      <c r="C1333" t="n">
+        <v>1</v>
+      </c>
+      <c r="D1333" t="n">
+        <v>3</v>
+      </c>
+      <c r="E1333" t="n">
+        <v>0</v>
+      </c>
+      <c r="F1333" t="inlineStr">
+        <is>
+          <t>2026-10-20</t>
+        </is>
+      </c>
+    </row>
+    <row r="1334">
+      <c r="A1334" t="inlineStr">
+        <is>
+          <t>5f47aeb6c387a50bca03dd55</t>
+        </is>
+      </c>
+      <c r="B1334" t="n">
+        <v>1375286</v>
+      </c>
+      <c r="C1334" t="n">
+        <v>0</v>
+      </c>
+      <c r="D1334" t="n">
+        <v>2</v>
+      </c>
+      <c r="E1334" t="n">
+        <v>0</v>
+      </c>
+      <c r="F1334" t="inlineStr">
+        <is>
+          <t>2026-10-20</t>
+        </is>
+      </c>
+    </row>
+    <row r="1335">
+      <c r="A1335" t="inlineStr">
+        <is>
+          <t>5f47ab5b9e2edb0bb831c703</t>
+        </is>
+      </c>
+      <c r="B1335" t="n">
+        <v>1995903</v>
+      </c>
+      <c r="C1335" t="n">
+        <v>0</v>
+      </c>
+      <c r="D1335" t="n">
+        <v>1</v>
+      </c>
+      <c r="E1335" t="n">
+        <v>0</v>
+      </c>
+      <c r="F1335" t="inlineStr">
+        <is>
+          <t>2026-10-20</t>
+        </is>
+      </c>
+    </row>
+    <row r="1336">
+      <c r="A1336" t="inlineStr">
+        <is>
+          <t>5f4530beec331549297ee6d6</t>
+        </is>
+      </c>
+      <c r="B1336" t="n">
+        <v>48569089</v>
+      </c>
+      <c r="C1336" t="n">
+        <v>0</v>
+      </c>
+      <c r="D1336" t="n">
+        <v>3</v>
+      </c>
+      <c r="E1336" t="n">
+        <v>0</v>
+      </c>
+      <c r="F1336" t="inlineStr">
+        <is>
+          <t>2026-10-20</t>
+        </is>
+      </c>
+    </row>
+    <row r="1337">
+      <c r="A1337" t="inlineStr">
+        <is>
+          <t>5f452f5e66dd374930eb2b71</t>
+        </is>
+      </c>
+      <c r="B1337" t="n">
+        <v>91134</v>
+      </c>
+      <c r="C1337" t="n">
+        <v>3</v>
+      </c>
+      <c r="D1337" t="n">
+        <v>4</v>
+      </c>
+      <c r="E1337" t="n">
+        <v>4</v>
+      </c>
+      <c r="F1337" t="inlineStr">
+        <is>
+          <t>2026-10-20</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/datos/hechos/td_admin.xlsx
+++ b/datos/hechos/td_admin.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F1337"/>
+  <dimension ref="A1:F1345"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -32524,6 +32524,198 @@
         </is>
       </c>
     </row>
+    <row r="1338">
+      <c r="A1338" t="inlineStr">
+        <is>
+          <t>5f45324dec331549297ee971</t>
+        </is>
+      </c>
+      <c r="B1338" t="n">
+        <v>13440821</v>
+      </c>
+      <c r="C1338" t="n">
+        <v>1</v>
+      </c>
+      <c r="D1338" t="n">
+        <v>2</v>
+      </c>
+      <c r="E1338" t="n">
+        <v>1</v>
+      </c>
+      <c r="F1338" t="inlineStr">
+        <is>
+          <t>2026-10-21</t>
+        </is>
+      </c>
+    </row>
+    <row r="1339">
+      <c r="A1339" t="inlineStr">
+        <is>
+          <t>62d5bd9ad8106d3355b5bdc1</t>
+        </is>
+      </c>
+      <c r="B1339" t="n">
+        <v>-15861752</v>
+      </c>
+      <c r="C1339" t="n">
+        <v>1</v>
+      </c>
+      <c r="D1339" t="n">
+        <v>2</v>
+      </c>
+      <c r="E1339" t="n">
+        <v>1</v>
+      </c>
+      <c r="F1339" t="inlineStr">
+        <is>
+          <t>2026-10-21</t>
+        </is>
+      </c>
+    </row>
+    <row r="1340">
+      <c r="A1340" t="inlineStr">
+        <is>
+          <t>5f453062ec331549297ee6b8</t>
+        </is>
+      </c>
+      <c r="B1340" t="n">
+        <v>17089182</v>
+      </c>
+      <c r="C1340" t="n">
+        <v>1</v>
+      </c>
+      <c r="D1340" t="n">
+        <v>3</v>
+      </c>
+      <c r="E1340" t="n">
+        <v>0</v>
+      </c>
+      <c r="F1340" t="inlineStr">
+        <is>
+          <t>2026-10-21</t>
+        </is>
+      </c>
+    </row>
+    <row r="1341">
+      <c r="A1341" t="inlineStr">
+        <is>
+          <t>5f4531e9764e7d491e029746</t>
+        </is>
+      </c>
+      <c r="B1341" t="n">
+        <v>59851146</v>
+      </c>
+      <c r="C1341" t="n">
+        <v>0</v>
+      </c>
+      <c r="D1341" t="n">
+        <v>0</v>
+      </c>
+      <c r="E1341" t="n">
+        <v>0</v>
+      </c>
+      <c r="F1341" t="inlineStr">
+        <is>
+          <t>2026-10-21</t>
+        </is>
+      </c>
+    </row>
+    <row r="1342">
+      <c r="A1342" t="inlineStr">
+        <is>
+          <t>5f47aeb6c387a50bca03dd55</t>
+        </is>
+      </c>
+      <c r="B1342" t="n">
+        <v>3705286</v>
+      </c>
+      <c r="C1342" t="n">
+        <v>0</v>
+      </c>
+      <c r="D1342" t="n">
+        <v>2</v>
+      </c>
+      <c r="E1342" t="n">
+        <v>0</v>
+      </c>
+      <c r="F1342" t="inlineStr">
+        <is>
+          <t>2026-10-21</t>
+        </is>
+      </c>
+    </row>
+    <row r="1343">
+      <c r="A1343" t="inlineStr">
+        <is>
+          <t>5f47ab5b9e2edb0bb831c703</t>
+        </is>
+      </c>
+      <c r="B1343" t="n">
+        <v>4802903</v>
+      </c>
+      <c r="C1343" t="n">
+        <v>0</v>
+      </c>
+      <c r="D1343" t="n">
+        <v>1</v>
+      </c>
+      <c r="E1343" t="n">
+        <v>0</v>
+      </c>
+      <c r="F1343" t="inlineStr">
+        <is>
+          <t>2026-10-21</t>
+        </is>
+      </c>
+    </row>
+    <row r="1344">
+      <c r="A1344" t="inlineStr">
+        <is>
+          <t>5f452f5e66dd374930eb2b71</t>
+        </is>
+      </c>
+      <c r="B1344" t="n">
+        <v>1837134</v>
+      </c>
+      <c r="C1344" t="n">
+        <v>3</v>
+      </c>
+      <c r="D1344" t="n">
+        <v>4</v>
+      </c>
+      <c r="E1344" t="n">
+        <v>4</v>
+      </c>
+      <c r="F1344" t="inlineStr">
+        <is>
+          <t>2026-10-21</t>
+        </is>
+      </c>
+    </row>
+    <row r="1345">
+      <c r="A1345" t="inlineStr">
+        <is>
+          <t>5f4530beec331549297ee6d6</t>
+        </is>
+      </c>
+      <c r="B1345" t="n">
+        <v>49736089</v>
+      </c>
+      <c r="C1345" t="n">
+        <v>0</v>
+      </c>
+      <c r="D1345" t="n">
+        <v>3</v>
+      </c>
+      <c r="E1345" t="n">
+        <v>0</v>
+      </c>
+      <c r="F1345" t="inlineStr">
+        <is>
+          <t>2026-10-21</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/datos/hechos/td_admin.xlsx
+++ b/datos/hechos/td_admin.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F1345"/>
+  <dimension ref="A1:F1353"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -32716,6 +32716,198 @@
         </is>
       </c>
     </row>
+    <row r="1346">
+      <c r="A1346" t="inlineStr">
+        <is>
+          <t>5f45324dec331549297ee971</t>
+        </is>
+      </c>
+      <c r="B1346" t="n">
+        <v>11331718</v>
+      </c>
+      <c r="C1346" t="n">
+        <v>1</v>
+      </c>
+      <c r="D1346" t="n">
+        <v>2</v>
+      </c>
+      <c r="E1346" t="n">
+        <v>1</v>
+      </c>
+      <c r="F1346" t="inlineStr">
+        <is>
+          <t>2026-10-22</t>
+        </is>
+      </c>
+    </row>
+    <row r="1347">
+      <c r="A1347" t="inlineStr">
+        <is>
+          <t>62d5bd9ad8106d3355b5bdc1</t>
+        </is>
+      </c>
+      <c r="B1347" t="n">
+        <v>87268</v>
+      </c>
+      <c r="C1347" t="n">
+        <v>1</v>
+      </c>
+      <c r="D1347" t="n">
+        <v>2</v>
+      </c>
+      <c r="E1347" t="n">
+        <v>1</v>
+      </c>
+      <c r="F1347" t="inlineStr">
+        <is>
+          <t>2026-10-22</t>
+        </is>
+      </c>
+    </row>
+    <row r="1348">
+      <c r="A1348" t="inlineStr">
+        <is>
+          <t>5f453062ec331549297ee6b8</t>
+        </is>
+      </c>
+      <c r="B1348" t="n">
+        <v>6089182</v>
+      </c>
+      <c r="C1348" t="n">
+        <v>1</v>
+      </c>
+      <c r="D1348" t="n">
+        <v>3</v>
+      </c>
+      <c r="E1348" t="n">
+        <v>0</v>
+      </c>
+      <c r="F1348" t="inlineStr">
+        <is>
+          <t>2026-10-22</t>
+        </is>
+      </c>
+    </row>
+    <row r="1349">
+      <c r="A1349" t="inlineStr">
+        <is>
+          <t>5f4531e9764e7d491e029746</t>
+        </is>
+      </c>
+      <c r="B1349" t="n">
+        <v>61670241</v>
+      </c>
+      <c r="C1349" t="n">
+        <v>0</v>
+      </c>
+      <c r="D1349" t="n">
+        <v>0</v>
+      </c>
+      <c r="E1349" t="n">
+        <v>0</v>
+      </c>
+      <c r="F1349" t="inlineStr">
+        <is>
+          <t>2026-10-22</t>
+        </is>
+      </c>
+    </row>
+    <row r="1350">
+      <c r="A1350" t="inlineStr">
+        <is>
+          <t>5f47aeb6c387a50bca03dd55</t>
+        </is>
+      </c>
+      <c r="B1350" t="n">
+        <v>3705286</v>
+      </c>
+      <c r="C1350" t="n">
+        <v>0</v>
+      </c>
+      <c r="D1350" t="n">
+        <v>2</v>
+      </c>
+      <c r="E1350" t="n">
+        <v>0</v>
+      </c>
+      <c r="F1350" t="inlineStr">
+        <is>
+          <t>2026-10-22</t>
+        </is>
+      </c>
+    </row>
+    <row r="1351">
+      <c r="A1351" t="inlineStr">
+        <is>
+          <t>5f47ab5b9e2edb0bb831c703</t>
+        </is>
+      </c>
+      <c r="B1351" t="n">
+        <v>4802903</v>
+      </c>
+      <c r="C1351" t="n">
+        <v>0</v>
+      </c>
+      <c r="D1351" t="n">
+        <v>1</v>
+      </c>
+      <c r="E1351" t="n">
+        <v>0</v>
+      </c>
+      <c r="F1351" t="inlineStr">
+        <is>
+          <t>2026-10-22</t>
+        </is>
+      </c>
+    </row>
+    <row r="1352">
+      <c r="A1352" t="inlineStr">
+        <is>
+          <t>5f452f5e66dd374930eb2b71</t>
+        </is>
+      </c>
+      <c r="B1352" t="n">
+        <v>1837134</v>
+      </c>
+      <c r="C1352" t="n">
+        <v>3</v>
+      </c>
+      <c r="D1352" t="n">
+        <v>4</v>
+      </c>
+      <c r="E1352" t="n">
+        <v>4</v>
+      </c>
+      <c r="F1352" t="inlineStr">
+        <is>
+          <t>2026-10-22</t>
+        </is>
+      </c>
+    </row>
+    <row r="1353">
+      <c r="A1353" t="inlineStr">
+        <is>
+          <t>5f4530beec331549297ee6d6</t>
+        </is>
+      </c>
+      <c r="B1353" t="n">
+        <v>49736089</v>
+      </c>
+      <c r="C1353" t="n">
+        <v>0</v>
+      </c>
+      <c r="D1353" t="n">
+        <v>3</v>
+      </c>
+      <c r="E1353" t="n">
+        <v>0</v>
+      </c>
+      <c r="F1353" t="inlineStr">
+        <is>
+          <t>2026-10-22</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/datos/hechos/td_admin.xlsx
+++ b/datos/hechos/td_admin.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F1353"/>
+  <dimension ref="A1:F1361"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -32908,6 +32908,198 @@
         </is>
       </c>
     </row>
+    <row r="1354">
+      <c r="A1354" t="inlineStr">
+        <is>
+          <t>5f45324dec331549297ee971</t>
+        </is>
+      </c>
+      <c r="B1354" t="n">
+        <v>-11918282</v>
+      </c>
+      <c r="C1354" t="n">
+        <v>1</v>
+      </c>
+      <c r="D1354" t="n">
+        <v>2</v>
+      </c>
+      <c r="E1354" t="n">
+        <v>1</v>
+      </c>
+      <c r="F1354" t="inlineStr">
+        <is>
+          <t>2026-10-23</t>
+        </is>
+      </c>
+    </row>
+    <row r="1355">
+      <c r="A1355" t="inlineStr">
+        <is>
+          <t>62d5bd9ad8106d3355b5bdc1</t>
+        </is>
+      </c>
+      <c r="B1355" t="n">
+        <v>1150268</v>
+      </c>
+      <c r="C1355" t="n">
+        <v>1</v>
+      </c>
+      <c r="D1355" t="n">
+        <v>2</v>
+      </c>
+      <c r="E1355" t="n">
+        <v>1</v>
+      </c>
+      <c r="F1355" t="inlineStr">
+        <is>
+          <t>2026-10-23</t>
+        </is>
+      </c>
+    </row>
+    <row r="1356">
+      <c r="A1356" t="inlineStr">
+        <is>
+          <t>5f453062ec331549297ee6b8</t>
+        </is>
+      </c>
+      <c r="B1356" t="n">
+        <v>6589182</v>
+      </c>
+      <c r="C1356" t="n">
+        <v>1</v>
+      </c>
+      <c r="D1356" t="n">
+        <v>3</v>
+      </c>
+      <c r="E1356" t="n">
+        <v>0</v>
+      </c>
+      <c r="F1356" t="inlineStr">
+        <is>
+          <t>2026-10-23</t>
+        </is>
+      </c>
+    </row>
+    <row r="1357">
+      <c r="A1357" t="inlineStr">
+        <is>
+          <t>5f4531e9764e7d491e029746</t>
+        </is>
+      </c>
+      <c r="B1357" t="n">
+        <v>61670241</v>
+      </c>
+      <c r="C1357" t="n">
+        <v>0</v>
+      </c>
+      <c r="D1357" t="n">
+        <v>0</v>
+      </c>
+      <c r="E1357" t="n">
+        <v>0</v>
+      </c>
+      <c r="F1357" t="inlineStr">
+        <is>
+          <t>2026-10-23</t>
+        </is>
+      </c>
+    </row>
+    <row r="1358">
+      <c r="A1358" t="inlineStr">
+        <is>
+          <t>5f47aeb6c387a50bca03dd55</t>
+        </is>
+      </c>
+      <c r="B1358" t="n">
+        <v>4077286</v>
+      </c>
+      <c r="C1358" t="n">
+        <v>0</v>
+      </c>
+      <c r="D1358" t="n">
+        <v>2</v>
+      </c>
+      <c r="E1358" t="n">
+        <v>0</v>
+      </c>
+      <c r="F1358" t="inlineStr">
+        <is>
+          <t>2026-10-23</t>
+        </is>
+      </c>
+    </row>
+    <row r="1359">
+      <c r="A1359" t="inlineStr">
+        <is>
+          <t>5f47ab5b9e2edb0bb831c703</t>
+        </is>
+      </c>
+      <c r="B1359" t="n">
+        <v>4802903</v>
+      </c>
+      <c r="C1359" t="n">
+        <v>0</v>
+      </c>
+      <c r="D1359" t="n">
+        <v>1</v>
+      </c>
+      <c r="E1359" t="n">
+        <v>0</v>
+      </c>
+      <c r="F1359" t="inlineStr">
+        <is>
+          <t>2026-10-23</t>
+        </is>
+      </c>
+    </row>
+    <row r="1360">
+      <c r="A1360" t="inlineStr">
+        <is>
+          <t>5f452f5e66dd374930eb2b71</t>
+        </is>
+      </c>
+      <c r="B1360" t="n">
+        <v>2209134</v>
+      </c>
+      <c r="C1360" t="n">
+        <v>3</v>
+      </c>
+      <c r="D1360" t="n">
+        <v>4</v>
+      </c>
+      <c r="E1360" t="n">
+        <v>4</v>
+      </c>
+      <c r="F1360" t="inlineStr">
+        <is>
+          <t>2026-10-23</t>
+        </is>
+      </c>
+    </row>
+    <row r="1361">
+      <c r="A1361" t="inlineStr">
+        <is>
+          <t>5f4530beec331549297ee6d6</t>
+        </is>
+      </c>
+      <c r="B1361" t="n">
+        <v>33912349</v>
+      </c>
+      <c r="C1361" t="n">
+        <v>0</v>
+      </c>
+      <c r="D1361" t="n">
+        <v>3</v>
+      </c>
+      <c r="E1361" t="n">
+        <v>0</v>
+      </c>
+      <c r="F1361" t="inlineStr">
+        <is>
+          <t>2026-10-23</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/datos/hechos/td_admin.xlsx
+++ b/datos/hechos/td_admin.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F1361"/>
+  <dimension ref="A1:F1369"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -33100,6 +33100,198 @@
         </is>
       </c>
     </row>
+    <row r="1362">
+      <c r="A1362" t="inlineStr">
+        <is>
+          <t>5f45324dec331549297ee971</t>
+        </is>
+      </c>
+      <c r="B1362" t="n">
+        <v>2345367</v>
+      </c>
+      <c r="C1362" t="n">
+        <v>1</v>
+      </c>
+      <c r="D1362" t="n">
+        <v>2</v>
+      </c>
+      <c r="E1362" t="n">
+        <v>1</v>
+      </c>
+      <c r="F1362" t="inlineStr">
+        <is>
+          <t>2026-10-24</t>
+        </is>
+      </c>
+    </row>
+    <row r="1363">
+      <c r="A1363" t="inlineStr">
+        <is>
+          <t>62d5bd9ad8106d3355b5bdc1</t>
+        </is>
+      </c>
+      <c r="B1363" t="n">
+        <v>1150268</v>
+      </c>
+      <c r="C1363" t="n">
+        <v>1</v>
+      </c>
+      <c r="D1363" t="n">
+        <v>2</v>
+      </c>
+      <c r="E1363" t="n">
+        <v>1</v>
+      </c>
+      <c r="F1363" t="inlineStr">
+        <is>
+          <t>2026-10-24</t>
+        </is>
+      </c>
+    </row>
+    <row r="1364">
+      <c r="A1364" t="inlineStr">
+        <is>
+          <t>5f453062ec331549297ee6b8</t>
+        </is>
+      </c>
+      <c r="B1364" t="n">
+        <v>6589182</v>
+      </c>
+      <c r="C1364" t="n">
+        <v>1</v>
+      </c>
+      <c r="D1364" t="n">
+        <v>3</v>
+      </c>
+      <c r="E1364" t="n">
+        <v>0</v>
+      </c>
+      <c r="F1364" t="inlineStr">
+        <is>
+          <t>2026-10-24</t>
+        </is>
+      </c>
+    </row>
+    <row r="1365">
+      <c r="A1365" t="inlineStr">
+        <is>
+          <t>5f4531e9764e7d491e029746</t>
+        </is>
+      </c>
+      <c r="B1365" t="n">
+        <v>2670176</v>
+      </c>
+      <c r="C1365" t="n">
+        <v>0</v>
+      </c>
+      <c r="D1365" t="n">
+        <v>0</v>
+      </c>
+      <c r="E1365" t="n">
+        <v>0</v>
+      </c>
+      <c r="F1365" t="inlineStr">
+        <is>
+          <t>2026-10-24</t>
+        </is>
+      </c>
+    </row>
+    <row r="1366">
+      <c r="A1366" t="inlineStr">
+        <is>
+          <t>5f47aeb6c387a50bca03dd55</t>
+        </is>
+      </c>
+      <c r="B1366" t="n">
+        <v>4077286</v>
+      </c>
+      <c r="C1366" t="n">
+        <v>0</v>
+      </c>
+      <c r="D1366" t="n">
+        <v>2</v>
+      </c>
+      <c r="E1366" t="n">
+        <v>0</v>
+      </c>
+      <c r="F1366" t="inlineStr">
+        <is>
+          <t>2026-10-24</t>
+        </is>
+      </c>
+    </row>
+    <row r="1367">
+      <c r="A1367" t="inlineStr">
+        <is>
+          <t>5f47ab5b9e2edb0bb831c703</t>
+        </is>
+      </c>
+      <c r="B1367" t="n">
+        <v>3302903</v>
+      </c>
+      <c r="C1367" t="n">
+        <v>0</v>
+      </c>
+      <c r="D1367" t="n">
+        <v>1</v>
+      </c>
+      <c r="E1367" t="n">
+        <v>0</v>
+      </c>
+      <c r="F1367" t="inlineStr">
+        <is>
+          <t>2026-10-24</t>
+        </is>
+      </c>
+    </row>
+    <row r="1368">
+      <c r="A1368" t="inlineStr">
+        <is>
+          <t>5f452f5e66dd374930eb2b71</t>
+        </is>
+      </c>
+      <c r="B1368" t="n">
+        <v>2209134</v>
+      </c>
+      <c r="C1368" t="n">
+        <v>3</v>
+      </c>
+      <c r="D1368" t="n">
+        <v>4</v>
+      </c>
+      <c r="E1368" t="n">
+        <v>4</v>
+      </c>
+      <c r="F1368" t="inlineStr">
+        <is>
+          <t>2026-10-24</t>
+        </is>
+      </c>
+    </row>
+    <row r="1369">
+      <c r="A1369" t="inlineStr">
+        <is>
+          <t>5f4530beec331549297ee6d6</t>
+        </is>
+      </c>
+      <c r="B1369" t="n">
+        <v>8727549</v>
+      </c>
+      <c r="C1369" t="n">
+        <v>0</v>
+      </c>
+      <c r="D1369" t="n">
+        <v>3</v>
+      </c>
+      <c r="E1369" t="n">
+        <v>0</v>
+      </c>
+      <c r="F1369" t="inlineStr">
+        <is>
+          <t>2026-10-24</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/datos/hechos/td_admin.xlsx
+++ b/datos/hechos/td_admin.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F1369"/>
+  <dimension ref="A1:F1377"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -33292,6 +33292,198 @@
         </is>
       </c>
     </row>
+    <row r="1370">
+      <c r="A1370" t="inlineStr">
+        <is>
+          <t>5f45324dec331549297ee971</t>
+        </is>
+      </c>
+      <c r="B1370" t="n">
+        <v>22289325</v>
+      </c>
+      <c r="C1370" t="n">
+        <v>1</v>
+      </c>
+      <c r="D1370" t="n">
+        <v>2</v>
+      </c>
+      <c r="E1370" t="n">
+        <v>1</v>
+      </c>
+      <c r="F1370" t="inlineStr">
+        <is>
+          <t>2026-10-25</t>
+        </is>
+      </c>
+    </row>
+    <row r="1371">
+      <c r="A1371" t="inlineStr">
+        <is>
+          <t>62d5bd9ad8106d3355b5bdc1</t>
+        </is>
+      </c>
+      <c r="B1371" t="n">
+        <v>2038229</v>
+      </c>
+      <c r="C1371" t="n">
+        <v>1</v>
+      </c>
+      <c r="D1371" t="n">
+        <v>2</v>
+      </c>
+      <c r="E1371" t="n">
+        <v>1</v>
+      </c>
+      <c r="F1371" t="inlineStr">
+        <is>
+          <t>2026-10-25</t>
+        </is>
+      </c>
+    </row>
+    <row r="1372">
+      <c r="A1372" t="inlineStr">
+        <is>
+          <t>5f453062ec331549297ee6b8</t>
+        </is>
+      </c>
+      <c r="B1372" t="n">
+        <v>31595052</v>
+      </c>
+      <c r="C1372" t="n">
+        <v>1</v>
+      </c>
+      <c r="D1372" t="n">
+        <v>3</v>
+      </c>
+      <c r="E1372" t="n">
+        <v>0</v>
+      </c>
+      <c r="F1372" t="inlineStr">
+        <is>
+          <t>2026-10-25</t>
+        </is>
+      </c>
+    </row>
+    <row r="1373">
+      <c r="A1373" t="inlineStr">
+        <is>
+          <t>5f4531e9764e7d491e029746</t>
+        </is>
+      </c>
+      <c r="B1373" t="n">
+        <v>2670176</v>
+      </c>
+      <c r="C1373" t="n">
+        <v>0</v>
+      </c>
+      <c r="D1373" t="n">
+        <v>0</v>
+      </c>
+      <c r="E1373" t="n">
+        <v>0</v>
+      </c>
+      <c r="F1373" t="inlineStr">
+        <is>
+          <t>2026-10-25</t>
+        </is>
+      </c>
+    </row>
+    <row r="1374">
+      <c r="A1374" t="inlineStr">
+        <is>
+          <t>5f47aeb6c387a50bca03dd55</t>
+        </is>
+      </c>
+      <c r="B1374" t="n">
+        <v>4077286</v>
+      </c>
+      <c r="C1374" t="n">
+        <v>0</v>
+      </c>
+      <c r="D1374" t="n">
+        <v>2</v>
+      </c>
+      <c r="E1374" t="n">
+        <v>0</v>
+      </c>
+      <c r="F1374" t="inlineStr">
+        <is>
+          <t>2026-10-25</t>
+        </is>
+      </c>
+    </row>
+    <row r="1375">
+      <c r="A1375" t="inlineStr">
+        <is>
+          <t>5f47ab5b9e2edb0bb831c703</t>
+        </is>
+      </c>
+      <c r="B1375" t="n">
+        <v>3302903</v>
+      </c>
+      <c r="C1375" t="n">
+        <v>0</v>
+      </c>
+      <c r="D1375" t="n">
+        <v>1</v>
+      </c>
+      <c r="E1375" t="n">
+        <v>0</v>
+      </c>
+      <c r="F1375" t="inlineStr">
+        <is>
+          <t>2026-10-25</t>
+        </is>
+      </c>
+    </row>
+    <row r="1376">
+      <c r="A1376" t="inlineStr">
+        <is>
+          <t>5f452f5e66dd374930eb2b71</t>
+        </is>
+      </c>
+      <c r="B1376" t="n">
+        <v>1135485</v>
+      </c>
+      <c r="C1376" t="n">
+        <v>3</v>
+      </c>
+      <c r="D1376" t="n">
+        <v>4</v>
+      </c>
+      <c r="E1376" t="n">
+        <v>4</v>
+      </c>
+      <c r="F1376" t="inlineStr">
+        <is>
+          <t>2026-10-25</t>
+        </is>
+      </c>
+    </row>
+    <row r="1377">
+      <c r="A1377" t="inlineStr">
+        <is>
+          <t>5f4530beec331549297ee6d6</t>
+        </is>
+      </c>
+      <c r="B1377" t="n">
+        <v>9965604</v>
+      </c>
+      <c r="C1377" t="n">
+        <v>0</v>
+      </c>
+      <c r="D1377" t="n">
+        <v>3</v>
+      </c>
+      <c r="E1377" t="n">
+        <v>0</v>
+      </c>
+      <c r="F1377" t="inlineStr">
+        <is>
+          <t>2026-10-25</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/datos/hechos/td_admin.xlsx
+++ b/datos/hechos/td_admin.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F1377"/>
+  <dimension ref="A1:F1385"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -33484,6 +33484,198 @@
         </is>
       </c>
     </row>
+    <row r="1378">
+      <c r="A1378" t="inlineStr">
+        <is>
+          <t>5f45324dec331549297ee971</t>
+        </is>
+      </c>
+      <c r="B1378" t="n">
+        <v>18775378</v>
+      </c>
+      <c r="C1378" t="n">
+        <v>1</v>
+      </c>
+      <c r="D1378" t="n">
+        <v>2</v>
+      </c>
+      <c r="E1378" t="n">
+        <v>1</v>
+      </c>
+      <c r="F1378" t="inlineStr">
+        <is>
+          <t>2026-10-26</t>
+        </is>
+      </c>
+    </row>
+    <row r="1379">
+      <c r="A1379" t="inlineStr">
+        <is>
+          <t>62d5bd9ad8106d3355b5bdc1</t>
+        </is>
+      </c>
+      <c r="B1379" t="n">
+        <v>-22961770</v>
+      </c>
+      <c r="C1379" t="n">
+        <v>1</v>
+      </c>
+      <c r="D1379" t="n">
+        <v>2</v>
+      </c>
+      <c r="E1379" t="n">
+        <v>1</v>
+      </c>
+      <c r="F1379" t="inlineStr">
+        <is>
+          <t>2026-10-26</t>
+        </is>
+      </c>
+    </row>
+    <row r="1380">
+      <c r="A1380" t="inlineStr">
+        <is>
+          <t>5f453062ec331549297ee6b8</t>
+        </is>
+      </c>
+      <c r="B1380" t="n">
+        <v>66127545</v>
+      </c>
+      <c r="C1380" t="n">
+        <v>1</v>
+      </c>
+      <c r="D1380" t="n">
+        <v>3</v>
+      </c>
+      <c r="E1380" t="n">
+        <v>0</v>
+      </c>
+      <c r="F1380" t="inlineStr">
+        <is>
+          <t>2026-10-26</t>
+        </is>
+      </c>
+    </row>
+    <row r="1381">
+      <c r="A1381" t="inlineStr">
+        <is>
+          <t>5f4531e9764e7d491e029746</t>
+        </is>
+      </c>
+      <c r="B1381" t="n">
+        <v>5734147</v>
+      </c>
+      <c r="C1381" t="n">
+        <v>0</v>
+      </c>
+      <c r="D1381" t="n">
+        <v>0</v>
+      </c>
+      <c r="E1381" t="n">
+        <v>0</v>
+      </c>
+      <c r="F1381" t="inlineStr">
+        <is>
+          <t>2026-10-26</t>
+        </is>
+      </c>
+    </row>
+    <row r="1382">
+      <c r="A1382" t="inlineStr">
+        <is>
+          <t>5f47aeb6c387a50bca03dd55</t>
+        </is>
+      </c>
+      <c r="B1382" t="n">
+        <v>4077286</v>
+      </c>
+      <c r="C1382" t="n">
+        <v>0</v>
+      </c>
+      <c r="D1382" t="n">
+        <v>2</v>
+      </c>
+      <c r="E1382" t="n">
+        <v>0</v>
+      </c>
+      <c r="F1382" t="inlineStr">
+        <is>
+          <t>2026-10-26</t>
+        </is>
+      </c>
+    </row>
+    <row r="1383">
+      <c r="A1383" t="inlineStr">
+        <is>
+          <t>5f47ab5b9e2edb0bb831c703</t>
+        </is>
+      </c>
+      <c r="B1383" t="n">
+        <v>3302903</v>
+      </c>
+      <c r="C1383" t="n">
+        <v>0</v>
+      </c>
+      <c r="D1383" t="n">
+        <v>1</v>
+      </c>
+      <c r="E1383" t="n">
+        <v>0</v>
+      </c>
+      <c r="F1383" t="inlineStr">
+        <is>
+          <t>2026-10-26</t>
+        </is>
+      </c>
+    </row>
+    <row r="1384">
+      <c r="A1384" t="inlineStr">
+        <is>
+          <t>5f452f5e66dd374930eb2b71</t>
+        </is>
+      </c>
+      <c r="B1384" t="n">
+        <v>1135485</v>
+      </c>
+      <c r="C1384" t="n">
+        <v>3</v>
+      </c>
+      <c r="D1384" t="n">
+        <v>4</v>
+      </c>
+      <c r="E1384" t="n">
+        <v>4</v>
+      </c>
+      <c r="F1384" t="inlineStr">
+        <is>
+          <t>2026-10-26</t>
+        </is>
+      </c>
+    </row>
+    <row r="1385">
+      <c r="A1385" t="inlineStr">
+        <is>
+          <t>5f4530beec331549297ee6d6</t>
+        </is>
+      </c>
+      <c r="B1385" t="n">
+        <v>9965604</v>
+      </c>
+      <c r="C1385" t="n">
+        <v>0</v>
+      </c>
+      <c r="D1385" t="n">
+        <v>3</v>
+      </c>
+      <c r="E1385" t="n">
+        <v>0</v>
+      </c>
+      <c r="F1385" t="inlineStr">
+        <is>
+          <t>2026-10-26</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/datos/hechos/td_admin.xlsx
+++ b/datos/hechos/td_admin.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F1385"/>
+  <dimension ref="A1:F1393"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -33676,6 +33676,198 @@
         </is>
       </c>
     </row>
+    <row r="1386">
+      <c r="A1386" t="inlineStr">
+        <is>
+          <t>5f45324dec331549297ee971</t>
+        </is>
+      </c>
+      <c r="B1386" t="n">
+        <v>13248174</v>
+      </c>
+      <c r="C1386" t="n">
+        <v>1</v>
+      </c>
+      <c r="D1386" t="n">
+        <v>2</v>
+      </c>
+      <c r="E1386" t="n">
+        <v>1</v>
+      </c>
+      <c r="F1386" t="inlineStr">
+        <is>
+          <t>2026-10-27</t>
+        </is>
+      </c>
+    </row>
+    <row r="1387">
+      <c r="A1387" t="inlineStr">
+        <is>
+          <t>62d5bd9ad8106d3355b5bdc1</t>
+        </is>
+      </c>
+      <c r="B1387" t="n">
+        <v>-22961770</v>
+      </c>
+      <c r="C1387" t="n">
+        <v>1</v>
+      </c>
+      <c r="D1387" t="n">
+        <v>2</v>
+      </c>
+      <c r="E1387" t="n">
+        <v>1</v>
+      </c>
+      <c r="F1387" t="inlineStr">
+        <is>
+          <t>2026-10-27</t>
+        </is>
+      </c>
+    </row>
+    <row r="1388">
+      <c r="A1388" t="inlineStr">
+        <is>
+          <t>5f453062ec331549297ee6b8</t>
+        </is>
+      </c>
+      <c r="B1388" t="n">
+        <v>66127545</v>
+      </c>
+      <c r="C1388" t="n">
+        <v>1</v>
+      </c>
+      <c r="D1388" t="n">
+        <v>3</v>
+      </c>
+      <c r="E1388" t="n">
+        <v>0</v>
+      </c>
+      <c r="F1388" t="inlineStr">
+        <is>
+          <t>2026-10-27</t>
+        </is>
+      </c>
+    </row>
+    <row r="1389">
+      <c r="A1389" t="inlineStr">
+        <is>
+          <t>5f4531e9764e7d491e029746</t>
+        </is>
+      </c>
+      <c r="B1389" t="n">
+        <v>5734147</v>
+      </c>
+      <c r="C1389" t="n">
+        <v>0</v>
+      </c>
+      <c r="D1389" t="n">
+        <v>0</v>
+      </c>
+      <c r="E1389" t="n">
+        <v>0</v>
+      </c>
+      <c r="F1389" t="inlineStr">
+        <is>
+          <t>2026-10-27</t>
+        </is>
+      </c>
+    </row>
+    <row r="1390">
+      <c r="A1390" t="inlineStr">
+        <is>
+          <t>5f47aeb6c387a50bca03dd55</t>
+        </is>
+      </c>
+      <c r="B1390" t="n">
+        <v>4077286</v>
+      </c>
+      <c r="C1390" t="n">
+        <v>0</v>
+      </c>
+      <c r="D1390" t="n">
+        <v>2</v>
+      </c>
+      <c r="E1390" t="n">
+        <v>0</v>
+      </c>
+      <c r="F1390" t="inlineStr">
+        <is>
+          <t>2026-10-27</t>
+        </is>
+      </c>
+    </row>
+    <row r="1391">
+      <c r="A1391" t="inlineStr">
+        <is>
+          <t>5f47ab5b9e2edb0bb831c703</t>
+        </is>
+      </c>
+      <c r="B1391" t="n">
+        <v>3302903</v>
+      </c>
+      <c r="C1391" t="n">
+        <v>0</v>
+      </c>
+      <c r="D1391" t="n">
+        <v>1</v>
+      </c>
+      <c r="E1391" t="n">
+        <v>0</v>
+      </c>
+      <c r="F1391" t="inlineStr">
+        <is>
+          <t>2026-10-27</t>
+        </is>
+      </c>
+    </row>
+    <row r="1392">
+      <c r="A1392" t="inlineStr">
+        <is>
+          <t>5f452f5e66dd374930eb2b71</t>
+        </is>
+      </c>
+      <c r="B1392" t="n">
+        <v>-1864616</v>
+      </c>
+      <c r="C1392" t="n">
+        <v>3</v>
+      </c>
+      <c r="D1392" t="n">
+        <v>4</v>
+      </c>
+      <c r="E1392" t="n">
+        <v>4</v>
+      </c>
+      <c r="F1392" t="inlineStr">
+        <is>
+          <t>2026-10-27</t>
+        </is>
+      </c>
+    </row>
+    <row r="1393">
+      <c r="A1393" t="inlineStr">
+        <is>
+          <t>5f4530beec331549297ee6d6</t>
+        </is>
+      </c>
+      <c r="B1393" t="n">
+        <v>38844816</v>
+      </c>
+      <c r="C1393" t="n">
+        <v>0</v>
+      </c>
+      <c r="D1393" t="n">
+        <v>3</v>
+      </c>
+      <c r="E1393" t="n">
+        <v>0</v>
+      </c>
+      <c r="F1393" t="inlineStr">
+        <is>
+          <t>2026-10-27</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/datos/hechos/td_admin.xlsx
+++ b/datos/hechos/td_admin.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F1393"/>
+  <dimension ref="A1:F1401"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -33868,6 +33868,198 @@
         </is>
       </c>
     </row>
+    <row r="1394">
+      <c r="A1394" t="inlineStr">
+        <is>
+          <t>5f45324dec331549297ee971</t>
+        </is>
+      </c>
+      <c r="B1394" t="n">
+        <v>8995163</v>
+      </c>
+      <c r="C1394" t="n">
+        <v>1</v>
+      </c>
+      <c r="D1394" t="n">
+        <v>2</v>
+      </c>
+      <c r="E1394" t="n">
+        <v>1</v>
+      </c>
+      <c r="F1394" t="inlineStr">
+        <is>
+          <t>2026-10-28</t>
+        </is>
+      </c>
+    </row>
+    <row r="1395">
+      <c r="A1395" t="inlineStr">
+        <is>
+          <t>5f453062ec331549297ee6b8</t>
+        </is>
+      </c>
+      <c r="B1395" t="n">
+        <v>5753545</v>
+      </c>
+      <c r="C1395" t="n">
+        <v>1</v>
+      </c>
+      <c r="D1395" t="n">
+        <v>3</v>
+      </c>
+      <c r="E1395" t="n">
+        <v>0</v>
+      </c>
+      <c r="F1395" t="inlineStr">
+        <is>
+          <t>2026-10-28</t>
+        </is>
+      </c>
+    </row>
+    <row r="1396">
+      <c r="A1396" t="inlineStr">
+        <is>
+          <t>62d5bd9ad8106d3355b5bdc1</t>
+        </is>
+      </c>
+      <c r="B1396" t="n">
+        <v>-20508770</v>
+      </c>
+      <c r="C1396" t="n">
+        <v>1</v>
+      </c>
+      <c r="D1396" t="n">
+        <v>2</v>
+      </c>
+      <c r="E1396" t="n">
+        <v>1</v>
+      </c>
+      <c r="F1396" t="inlineStr">
+        <is>
+          <t>2026-10-28</t>
+        </is>
+      </c>
+    </row>
+    <row r="1397">
+      <c r="A1397" t="inlineStr">
+        <is>
+          <t>5f47aeb6c387a50bca03dd55</t>
+        </is>
+      </c>
+      <c r="B1397" t="n">
+        <v>6659286</v>
+      </c>
+      <c r="C1397" t="n">
+        <v>0</v>
+      </c>
+      <c r="D1397" t="n">
+        <v>2</v>
+      </c>
+      <c r="E1397" t="n">
+        <v>0</v>
+      </c>
+      <c r="F1397" t="inlineStr">
+        <is>
+          <t>2026-10-28</t>
+        </is>
+      </c>
+    </row>
+    <row r="1398">
+      <c r="A1398" t="inlineStr">
+        <is>
+          <t>5f4531e9764e7d491e029746</t>
+        </is>
+      </c>
+      <c r="B1398" t="n">
+        <v>7225147</v>
+      </c>
+      <c r="C1398" t="n">
+        <v>0</v>
+      </c>
+      <c r="D1398" t="n">
+        <v>0</v>
+      </c>
+      <c r="E1398" t="n">
+        <v>0</v>
+      </c>
+      <c r="F1398" t="inlineStr">
+        <is>
+          <t>2026-10-28</t>
+        </is>
+      </c>
+    </row>
+    <row r="1399">
+      <c r="A1399" t="inlineStr">
+        <is>
+          <t>5f47ab5b9e2edb0bb831c703</t>
+        </is>
+      </c>
+      <c r="B1399" t="n">
+        <v>5396903</v>
+      </c>
+      <c r="C1399" t="n">
+        <v>0</v>
+      </c>
+      <c r="D1399" t="n">
+        <v>1</v>
+      </c>
+      <c r="E1399" t="n">
+        <v>0</v>
+      </c>
+      <c r="F1399" t="inlineStr">
+        <is>
+          <t>2026-10-28</t>
+        </is>
+      </c>
+    </row>
+    <row r="1400">
+      <c r="A1400" t="inlineStr">
+        <is>
+          <t>5f452f5e66dd374930eb2b71</t>
+        </is>
+      </c>
+      <c r="B1400" t="n">
+        <v>355384</v>
+      </c>
+      <c r="C1400" t="n">
+        <v>3</v>
+      </c>
+      <c r="D1400" t="n">
+        <v>4</v>
+      </c>
+      <c r="E1400" t="n">
+        <v>4</v>
+      </c>
+      <c r="F1400" t="inlineStr">
+        <is>
+          <t>2026-10-28</t>
+        </is>
+      </c>
+    </row>
+    <row r="1401">
+      <c r="A1401" t="inlineStr">
+        <is>
+          <t>5f4530beec331549297ee6d6</t>
+        </is>
+      </c>
+      <c r="B1401" t="n">
+        <v>329016</v>
+      </c>
+      <c r="C1401" t="n">
+        <v>0</v>
+      </c>
+      <c r="D1401" t="n">
+        <v>3</v>
+      </c>
+      <c r="E1401" t="n">
+        <v>0</v>
+      </c>
+      <c r="F1401" t="inlineStr">
+        <is>
+          <t>2026-10-28</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/datos/hechos/td_admin.xlsx
+++ b/datos/hechos/td_admin.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F1401"/>
+  <dimension ref="A1:F1409"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -34060,6 +34060,198 @@
         </is>
       </c>
     </row>
+    <row r="1402">
+      <c r="A1402" t="inlineStr">
+        <is>
+          <t>5f45324dec331549297ee971</t>
+        </is>
+      </c>
+      <c r="B1402" t="n">
+        <v>8926493</v>
+      </c>
+      <c r="C1402" t="n">
+        <v>1</v>
+      </c>
+      <c r="D1402" t="n">
+        <v>2</v>
+      </c>
+      <c r="E1402" t="n">
+        <v>1</v>
+      </c>
+      <c r="F1402" t="inlineStr">
+        <is>
+          <t>2026-10-29</t>
+        </is>
+      </c>
+    </row>
+    <row r="1403">
+      <c r="A1403" t="inlineStr">
+        <is>
+          <t>5f453062ec331549297ee6b8</t>
+        </is>
+      </c>
+      <c r="B1403" t="n">
+        <v>-15246455</v>
+      </c>
+      <c r="C1403" t="n">
+        <v>1</v>
+      </c>
+      <c r="D1403" t="n">
+        <v>3</v>
+      </c>
+      <c r="E1403" t="n">
+        <v>0</v>
+      </c>
+      <c r="F1403" t="inlineStr">
+        <is>
+          <t>2026-10-29</t>
+        </is>
+      </c>
+    </row>
+    <row r="1404">
+      <c r="A1404" t="inlineStr">
+        <is>
+          <t>62d5bd9ad8106d3355b5bdc1</t>
+        </is>
+      </c>
+      <c r="B1404" t="n">
+        <v>-20508770</v>
+      </c>
+      <c r="C1404" t="n">
+        <v>1</v>
+      </c>
+      <c r="D1404" t="n">
+        <v>2</v>
+      </c>
+      <c r="E1404" t="n">
+        <v>1</v>
+      </c>
+      <c r="F1404" t="inlineStr">
+        <is>
+          <t>2026-10-29</t>
+        </is>
+      </c>
+    </row>
+    <row r="1405">
+      <c r="A1405" t="inlineStr">
+        <is>
+          <t>5f47aeb6c387a50bca03dd55</t>
+        </is>
+      </c>
+      <c r="B1405" t="n">
+        <v>6659286</v>
+      </c>
+      <c r="C1405" t="n">
+        <v>0</v>
+      </c>
+      <c r="D1405" t="n">
+        <v>2</v>
+      </c>
+      <c r="E1405" t="n">
+        <v>0</v>
+      </c>
+      <c r="F1405" t="inlineStr">
+        <is>
+          <t>2026-10-29</t>
+        </is>
+      </c>
+    </row>
+    <row r="1406">
+      <c r="A1406" t="inlineStr">
+        <is>
+          <t>5f4531e9764e7d491e029746</t>
+        </is>
+      </c>
+      <c r="B1406" t="n">
+        <v>7225147</v>
+      </c>
+      <c r="C1406" t="n">
+        <v>0</v>
+      </c>
+      <c r="D1406" t="n">
+        <v>0</v>
+      </c>
+      <c r="E1406" t="n">
+        <v>0</v>
+      </c>
+      <c r="F1406" t="inlineStr">
+        <is>
+          <t>2026-10-29</t>
+        </is>
+      </c>
+    </row>
+    <row r="1407">
+      <c r="A1407" t="inlineStr">
+        <is>
+          <t>5f47ab5b9e2edb0bb831c703</t>
+        </is>
+      </c>
+      <c r="B1407" t="n">
+        <v>5396903</v>
+      </c>
+      <c r="C1407" t="n">
+        <v>0</v>
+      </c>
+      <c r="D1407" t="n">
+        <v>1</v>
+      </c>
+      <c r="E1407" t="n">
+        <v>0</v>
+      </c>
+      <c r="F1407" t="inlineStr">
+        <is>
+          <t>2026-10-29</t>
+        </is>
+      </c>
+    </row>
+    <row r="1408">
+      <c r="A1408" t="inlineStr">
+        <is>
+          <t>5f452f5e66dd374930eb2b71</t>
+        </is>
+      </c>
+      <c r="B1408" t="n">
+        <v>355384</v>
+      </c>
+      <c r="C1408" t="n">
+        <v>3</v>
+      </c>
+      <c r="D1408" t="n">
+        <v>4</v>
+      </c>
+      <c r="E1408" t="n">
+        <v>4</v>
+      </c>
+      <c r="F1408" t="inlineStr">
+        <is>
+          <t>2026-10-29</t>
+        </is>
+      </c>
+    </row>
+    <row r="1409">
+      <c r="A1409" t="inlineStr">
+        <is>
+          <t>5f4530beec331549297ee6d6</t>
+        </is>
+      </c>
+      <c r="B1409" t="n">
+        <v>329016</v>
+      </c>
+      <c r="C1409" t="n">
+        <v>0</v>
+      </c>
+      <c r="D1409" t="n">
+        <v>3</v>
+      </c>
+      <c r="E1409" t="n">
+        <v>0</v>
+      </c>
+      <c r="F1409" t="inlineStr">
+        <is>
+          <t>2026-10-29</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/datos/hechos/td_admin.xlsx
+++ b/datos/hechos/td_admin.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F1409"/>
+  <dimension ref="A1:F1417"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -34252,6 +34252,198 @@
         </is>
       </c>
     </row>
+    <row r="1410">
+      <c r="A1410" t="inlineStr">
+        <is>
+          <t>5f45324dec331549297ee971</t>
+        </is>
+      </c>
+      <c r="B1410" t="n">
+        <v>8926493</v>
+      </c>
+      <c r="C1410" t="n">
+        <v>1</v>
+      </c>
+      <c r="D1410" t="n">
+        <v>2</v>
+      </c>
+      <c r="E1410" t="n">
+        <v>1</v>
+      </c>
+      <c r="F1410" t="inlineStr">
+        <is>
+          <t>2026-10-30</t>
+        </is>
+      </c>
+    </row>
+    <row r="1411">
+      <c r="A1411" t="inlineStr">
+        <is>
+          <t>5f453062ec331549297ee6b8</t>
+        </is>
+      </c>
+      <c r="B1411" t="n">
+        <v>5948566</v>
+      </c>
+      <c r="C1411" t="n">
+        <v>1</v>
+      </c>
+      <c r="D1411" t="n">
+        <v>3</v>
+      </c>
+      <c r="E1411" t="n">
+        <v>0</v>
+      </c>
+      <c r="F1411" t="inlineStr">
+        <is>
+          <t>2026-10-30</t>
+        </is>
+      </c>
+    </row>
+    <row r="1412">
+      <c r="A1412" t="inlineStr">
+        <is>
+          <t>62d5bd9ad8106d3355b5bdc1</t>
+        </is>
+      </c>
+      <c r="B1412" t="n">
+        <v>-20508770</v>
+      </c>
+      <c r="C1412" t="n">
+        <v>1</v>
+      </c>
+      <c r="D1412" t="n">
+        <v>2</v>
+      </c>
+      <c r="E1412" t="n">
+        <v>1</v>
+      </c>
+      <c r="F1412" t="inlineStr">
+        <is>
+          <t>2026-10-30</t>
+        </is>
+      </c>
+    </row>
+    <row r="1413">
+      <c r="A1413" t="inlineStr">
+        <is>
+          <t>5f47aeb6c387a50bca03dd55</t>
+        </is>
+      </c>
+      <c r="B1413" t="n">
+        <v>6659286</v>
+      </c>
+      <c r="C1413" t="n">
+        <v>0</v>
+      </c>
+      <c r="D1413" t="n">
+        <v>2</v>
+      </c>
+      <c r="E1413" t="n">
+        <v>0</v>
+      </c>
+      <c r="F1413" t="inlineStr">
+        <is>
+          <t>2026-10-30</t>
+        </is>
+      </c>
+    </row>
+    <row r="1414">
+      <c r="A1414" t="inlineStr">
+        <is>
+          <t>5f4531e9764e7d491e029746</t>
+        </is>
+      </c>
+      <c r="B1414" t="n">
+        <v>7225147</v>
+      </c>
+      <c r="C1414" t="n">
+        <v>0</v>
+      </c>
+      <c r="D1414" t="n">
+        <v>0</v>
+      </c>
+      <c r="E1414" t="n">
+        <v>0</v>
+      </c>
+      <c r="F1414" t="inlineStr">
+        <is>
+          <t>2026-10-30</t>
+        </is>
+      </c>
+    </row>
+    <row r="1415">
+      <c r="A1415" t="inlineStr">
+        <is>
+          <t>5f47ab5b9e2edb0bb831c703</t>
+        </is>
+      </c>
+      <c r="B1415" t="n">
+        <v>5396903</v>
+      </c>
+      <c r="C1415" t="n">
+        <v>0</v>
+      </c>
+      <c r="D1415" t="n">
+        <v>1</v>
+      </c>
+      <c r="E1415" t="n">
+        <v>0</v>
+      </c>
+      <c r="F1415" t="inlineStr">
+        <is>
+          <t>2026-10-30</t>
+        </is>
+      </c>
+    </row>
+    <row r="1416">
+      <c r="A1416" t="inlineStr">
+        <is>
+          <t>5f452f5e66dd374930eb2b71</t>
+        </is>
+      </c>
+      <c r="B1416" t="n">
+        <v>355384</v>
+      </c>
+      <c r="C1416" t="n">
+        <v>3</v>
+      </c>
+      <c r="D1416" t="n">
+        <v>4</v>
+      </c>
+      <c r="E1416" t="n">
+        <v>4</v>
+      </c>
+      <c r="F1416" t="inlineStr">
+        <is>
+          <t>2026-10-30</t>
+        </is>
+      </c>
+    </row>
+    <row r="1417">
+      <c r="A1417" t="inlineStr">
+        <is>
+          <t>5f4530beec331549297ee6d6</t>
+        </is>
+      </c>
+      <c r="B1417" t="n">
+        <v>329016</v>
+      </c>
+      <c r="C1417" t="n">
+        <v>0</v>
+      </c>
+      <c r="D1417" t="n">
+        <v>3</v>
+      </c>
+      <c r="E1417" t="n">
+        <v>0</v>
+      </c>
+      <c r="F1417" t="inlineStr">
+        <is>
+          <t>2026-10-30</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/datos/hechos/td_admin.xlsx
+++ b/datos/hechos/td_admin.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F1417"/>
+  <dimension ref="A1:F1425"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -34444,6 +34444,198 @@
         </is>
       </c>
     </row>
+    <row r="1418">
+      <c r="A1418" t="inlineStr">
+        <is>
+          <t>5f45324dec331549297ee971</t>
+        </is>
+      </c>
+      <c r="B1418" t="n">
+        <v>8926493</v>
+      </c>
+      <c r="C1418" t="n">
+        <v>1</v>
+      </c>
+      <c r="D1418" t="n">
+        <v>2</v>
+      </c>
+      <c r="E1418" t="n">
+        <v>1</v>
+      </c>
+      <c r="F1418" t="inlineStr">
+        <is>
+          <t>2026-10-31</t>
+        </is>
+      </c>
+    </row>
+    <row r="1419">
+      <c r="A1419" t="inlineStr">
+        <is>
+          <t>5f453062ec331549297ee6b8</t>
+        </is>
+      </c>
+      <c r="B1419" t="n">
+        <v>-1051434</v>
+      </c>
+      <c r="C1419" t="n">
+        <v>1</v>
+      </c>
+      <c r="D1419" t="n">
+        <v>3</v>
+      </c>
+      <c r="E1419" t="n">
+        <v>0</v>
+      </c>
+      <c r="F1419" t="inlineStr">
+        <is>
+          <t>2026-10-31</t>
+        </is>
+      </c>
+    </row>
+    <row r="1420">
+      <c r="A1420" t="inlineStr">
+        <is>
+          <t>62d5bd9ad8106d3355b5bdc1</t>
+        </is>
+      </c>
+      <c r="B1420" t="n">
+        <v>2779346</v>
+      </c>
+      <c r="C1420" t="n">
+        <v>1</v>
+      </c>
+      <c r="D1420" t="n">
+        <v>2</v>
+      </c>
+      <c r="E1420" t="n">
+        <v>1</v>
+      </c>
+      <c r="F1420" t="inlineStr">
+        <is>
+          <t>2026-10-31</t>
+        </is>
+      </c>
+    </row>
+    <row r="1421">
+      <c r="A1421" t="inlineStr">
+        <is>
+          <t>5f47aeb6c387a50bca03dd55</t>
+        </is>
+      </c>
+      <c r="B1421" t="n">
+        <v>6659286</v>
+      </c>
+      <c r="C1421" t="n">
+        <v>0</v>
+      </c>
+      <c r="D1421" t="n">
+        <v>2</v>
+      </c>
+      <c r="E1421" t="n">
+        <v>0</v>
+      </c>
+      <c r="F1421" t="inlineStr">
+        <is>
+          <t>2026-10-31</t>
+        </is>
+      </c>
+    </row>
+    <row r="1422">
+      <c r="A1422" t="inlineStr">
+        <is>
+          <t>5f4531e9764e7d491e029746</t>
+        </is>
+      </c>
+      <c r="B1422" t="n">
+        <v>7225147</v>
+      </c>
+      <c r="C1422" t="n">
+        <v>0</v>
+      </c>
+      <c r="D1422" t="n">
+        <v>0</v>
+      </c>
+      <c r="E1422" t="n">
+        <v>0</v>
+      </c>
+      <c r="F1422" t="inlineStr">
+        <is>
+          <t>2026-10-31</t>
+        </is>
+      </c>
+    </row>
+    <row r="1423">
+      <c r="A1423" t="inlineStr">
+        <is>
+          <t>5f47ab5b9e2edb0bb831c703</t>
+        </is>
+      </c>
+      <c r="B1423" t="n">
+        <v>5396903</v>
+      </c>
+      <c r="C1423" t="n">
+        <v>0</v>
+      </c>
+      <c r="D1423" t="n">
+        <v>1</v>
+      </c>
+      <c r="E1423" t="n">
+        <v>0</v>
+      </c>
+      <c r="F1423" t="inlineStr">
+        <is>
+          <t>2026-10-31</t>
+        </is>
+      </c>
+    </row>
+    <row r="1424">
+      <c r="A1424" t="inlineStr">
+        <is>
+          <t>5f452f5e66dd374930eb2b71</t>
+        </is>
+      </c>
+      <c r="B1424" t="n">
+        <v>355384</v>
+      </c>
+      <c r="C1424" t="n">
+        <v>3</v>
+      </c>
+      <c r="D1424" t="n">
+        <v>4</v>
+      </c>
+      <c r="E1424" t="n">
+        <v>4</v>
+      </c>
+      <c r="F1424" t="inlineStr">
+        <is>
+          <t>2026-10-31</t>
+        </is>
+      </c>
+    </row>
+    <row r="1425">
+      <c r="A1425" t="inlineStr">
+        <is>
+          <t>5f4530beec331549297ee6d6</t>
+        </is>
+      </c>
+      <c r="B1425" t="n">
+        <v>329016</v>
+      </c>
+      <c r="C1425" t="n">
+        <v>0</v>
+      </c>
+      <c r="D1425" t="n">
+        <v>3</v>
+      </c>
+      <c r="E1425" t="n">
+        <v>0</v>
+      </c>
+      <c r="F1425" t="inlineStr">
+        <is>
+          <t>2026-10-31</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
